--- a/output/20_北塩原村第10期_確認事項一覧.xlsx
+++ b/output/20_北塩原村第10期_確認事項一覧.xlsx
@@ -2341,7 +2341,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>★令和8年度の市町村分 全国一覧表と評価指標42頁を突合し、新たな予算や施設を要さず取得できる項目を61点分特定した（doc42§3）。447点→508点で全国1,005位→525位、県内34位→18位になる。内訳は認知症施策推進計画の策定着手5点／成年後見の要綱改正4点／難聴の普及啓発・早期発見10点／在宅医療連携の4場面の設定と対応策10点／相談内容の取りまとめ2点／給付適正化の福祉用具・住宅改修16点／ケアプラン点検の村外施設分8点／主要3事業の全実施6点。素案への反映には村の意向確認を要する。</t>
+          <t>★令和8年度の市町村分 全国一覧表と評価指標42頁を突合し、新たな予算や施設を要さず取得できる項目を61点分特定した（doc42§3）。447点→508点で全国1,005位→525位、県内34位→18位になる。内訳は認知症施策推進計画の策定着手5点／成年後見の要綱改正4点／難聴の普及啓発・早期発見10点／在宅医療連携の4場面の設定と対応策10点／相談内容の取りまとめ2点／給付適正化の福祉用具・住宅改修16点／ケアプラン点検の村外施設分8点／主要3事業の全実施6点。素案への反映には村の意向確認を要する。★10/24：その後の精査（doc110）により、計画への記載と実施・記録で取得をめざす11項目は62点、認知症施策推進計画の5点を加えて67点（447点→514点、全国491位・県内17位の機械的な試算）に改めている。第2回資料7-3cの本文に61点・525位が残っていたため直した（doc119）。点は国の該当状況調査への回答と実施・記録の結果により決まり、計画に書くことで点が確定するものではない。</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">

--- a/output/20_北塩原村第10期_確認事項一覧.xlsx
+++ b/output/20_北塩原村第10期_確認事項一覧.xlsx
@@ -12,7 +12,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="解決済" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未解決'!$A$1:$L$181</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'未解決'!$A$1:$L$184</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'解決済'!$A$1:$H$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -499,7 +499,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>180件</t>
+          <t>183件</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L181"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2336,7 +2336,7 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>★交付金で61点が取れる未得点項目11件の取組可否（計画への記載・要綱改正・手順の明文化のみで取得できるもの）</t>
+          <t>★交付金で取得をめざす未得点項目11件62点の取組可否（計画への記載・要綱改正・手順の明文化と実施・記録によるもの）</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -2840,22 +2840,22 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>地域支援事業費・総合事業費の決算の複数年の推移（可能な範囲で5か年以上）</t>
+          <t>★国の推計ワークシートの介護給付費準備基金の令和8年度末見込額42,128,183円の積算根拠</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>地域支援事業費・総合事業費の決算の複数年の推移（可能な範囲で5か年以上）をご提供いただきたい。素案5-6は令和5年度決算（地域支援事業費39,886千円・総合事業費16,463千円）を3か年据え置いている。手元にある決算は令和4・5年度の2か年のみで、趨勢か単年度の振れかを判断できない。補助給付等についても対標準給付費比が令和4年度9.02%から令和5年度7.67%へ1.35ポイント下がっており（主因は特定入所者介護サービス費等の18.3%減）、据え置きが外れると保険料基準額は月額で最大96円動く（素案5-6）。★10/7 優先度を上げた：国の推計ワークシートは令和9年度47,686千円・令和10年度49,218千円・令和11年度50,751千円（年3.2%の伸び）で入っており、当方の据え置き（39,886千円×3）と3か年で27,996千円・23.4%開く。据え置きが外れたため、決算の推移の確認が据え置きの妥当性の検証から伸びの根拠の確認に変わった。</t>
+          <t>★10/24 外部レビュー（Red Team）R05により起票。決算による令和6年度末の残高は20,461,007円であり、見込額に届くには令和7・8年度で21,667,176円の積増しが要る。令和6年度の歳入歳出差引残額35,608,849円（精算返還前）の積立てで説明できる可能性があるが、国庫負担金等の精算返還を差し引くと届かない恐れがある。令和7年度の積立額・取崩額・精算返還額と、令和8年度の積立予定額をご教示いただきたい。保険料の3案（取崩0円・24,000千円・40,000千円）の成り立ちに直接関わる。</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56,Ⅱ-106</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>doc47§5,doc66§3-3</t>
+          <t>doc118,doc120</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -2898,22 +2898,22 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>★高齢者の移動支援と配食サービスの実態（素案の記述と高齢者サービスの手引きが食い違う）</t>
+          <t>★認知症対応型共同生活介護の利用者数の系列（国の推計ワークシート27・28・29人と県の整備量見込みシート27人のどちらにそろえるか）</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>★移動支援の利用人数と運行の状況、配食サービスの1回あたりの配達先の数をご教示いただきたい。10/10 起票：高齢者サービスの手引き（令和8年度版）により、素案4-6(2)の記述が実態と違うことが分かった。①移動支援：素案は「公共交通担当部局と連携し、介護予防・生活支援サービス事業による移動支援の創設を検討する」としているが、手引きによれば村民向け路線バスICカードを発行して喜多方⇔裏磐梯・猪苗代⇔裏磐梯の路線バスが無料であり、路線バス運行区域以外でも無料のコミュニティバスが運行している（総務企画課防災係）。すでにある仕組みを「創設を検討」と書くのは実態と違うため、「既存の仕組みの活用と周知、および路線バスが届かない範囲の補い方の検討」に改めたい。ご異存がないかと、路線バスが届かない地区・時間帯があるかをご教示いただきたい。②配食サービス：素案は「村の委託により現在の体制を維持する」としているが、手引きによれば赤十字奉仕団によるひとり暮らし高齢者弁当配達サービスで年4回予定である。年4回を「配食サービス」として量の目標を置くのは無理があるため、毎日の食事の確保という課題に対して現状が年4回であることを課題として書きたい。この整理でよいかをご確認いただきたい。★10/10：ご回答を待たずに素案を直した。すでにある仕組みを「創設を検討」と書いた計画書は、委員から見て村の実態を把握していない資料に見えるためである。直した内容は次のとおりである。①移動支援：4-6(2)の事業名を「高齢者の移動支援（路線バスICカード・コミュニティバス）」に改め、確保の方策を「村民向けの路線バスICカードの発行と無料のコミュニティバスの運行を継続し、周知を図る。これらで届かない範囲について、介護予防・生活支援サービス事業による補い方を検討する」とした。施策2-1の本文に既存の仕組みを書き、取組を4項目に改め（課題の把握／周知／届かない範囲の補い方／連携の継続）、指標に「路線バスICカードの交付を受けた方の人数」を加えた。②配食：4-6(2)の事業名を「ひとり暮らし高齢者弁当配達サービス」に改め、単位を「回／年」、目標を令和9〜11年度いずれも4回とした。総合事業の配食（未実施）とは別の事業であることを注記し、毎日の食事の確保という課題に対しては年4回では足りないため総合事業による配食の創設を施策1-2で検討する旨を書いた。★素案を直したため、ご確認いただきたいことは次のとおりに絞られる。・路線バスICカードとコミュニティバスの所管は総務企画課防災係でよいか。・路線バスICカードの交付を受けた方の人数と、コミュニティバスの利用の状況（地区別）。施策2-1の「移動に関する課題の把握」が国の評価指標で0点にとどまっているため、既存の仕組みが届いていない範囲を示す材料として要する。・弁当配達サービスの年4回は令和9年度以降も同じ回数を予定するか。あわせて1回あたりの配達先の数（利用人数）をご教示いただきたい。量の目標に置けているのは「回／年」だけであり、どれだけの方に届いているかが分からない。★当方の扱い：人数・利用の状況・回数のご回答がない場合、実績の欄は空欄、移動支援の目標は「―」のまま、弁当配達は年4回を据え置いてお示しする。</t>
+          <t>★10/24 外部レビュー（Red Team）R02により判明。いずれも村が県に提出したもので、令和10・11年度に1〜2人の差がある。給付費・保険料はワークシートの値（28・29人）で算定され、素案5-4(2)の施設・居住系の人数の表は県シートの値（27人）である。村内の定員は27人であり、28・29人は村外のグループホームの利用を見込んだものか、入力の違いかをご教示いただきたい。</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-110,Ⅱ-54</t>
+          <t>Ⅱ-55,Ⅱ-63</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>doc76§1-3,素案4-6(2),素案 施策2-1</t>
+          <t>doc120</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>記載待ち</t>
+          <t>仮置き</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>高齢者サービスの手引きは受領済みであり、当方が突き合わせる。実態の確定のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -2951,32 +2951,32 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>★高齢者サービスの手引きにあって素案に載っていない村単独事業9件を計画に掲げるか</t>
+          <t>要介護認定の更新の前後の要介護度（令和6〜8年度。要介護度の層別の状態変化の指標の基礎）</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>★村単独事業9件について、本計画に掲げる範囲をご判断いただきたい。★10/20 当方の先行：例規集のドメインを加えていただき、北塩原村例規集（内容現在 令和8年6月26日）の第8類 厚生 第1章 社会福祉 第4節 老人福祉の32件と突き合わせた。ア 9件のうち4件は根拠となる例規を確かめた。寝具洗濯サービスは北塩原村寝たきり老人等寝具丸洗い事業実施要綱（平成14年告示第19号）、訪問理美容サービスは同訪問理美容サービス事業実施要綱（平成15年訓令第1号）、健康長寿祝金は同健康長寿祝金条例（令和6年条例第9号）および同条例施行規則（令和6年規則第13号）である。火災警報器の配布は北塩原村老人日常生活用具給付等事業実施要綱（平成8年訓令第6号）による可能性が高いが、対象品目を確かめていない。イ 名称の食い違いがある。手引きは「寝具洗濯サービス」、例規は「寝具丸洗い」である。素案は手引きの呼び方を用い、根拠例規の名称を注記に書いた。ウ 残る5件（なりすまし詐欺抑止装置・長寿を祝う会・防犯カメラ等の助成・地域健康づくり活動活性化助成金・帯状疱疹予防接種）は第4節 老人福祉になく、他の章（防災・保健衛生等）にあるとみられる。例規集への接続が再び拒まれたため当方では確かめられていない。エ 逆向きの突合せでより重いものが見つかった。例規にあって素案4-6に対応がない老人福祉法上の事業・施設が3件ある。1つめは老人介護支援センター（北塩原村在宅介護支援センター条例 平成11年条例第5号・同運営事業実施要綱 平成18年要綱第5号）。老人福祉法第5条の3の老人福祉施設であり、第20条の8第2項第1号が定めることを求める施設にあたる。2つめは老人日常生活用具給付等（平成8年訓令第6号）で、同法第10条の4第1項第3号の事業である。3つめは短期入所のやむを得ない事由による措置（平成10年要綱第1号）で、同項第4号の措置であり、介護保険の短期入所生活介護とは別のものである。オ 3件を素案4-6(2)に加えた。ただし要綱が効力を有することと事業が現に行われていることとは別であるため、実績と目標は【要確認】としている。とくに在宅介護支援センターは、地域包括支援センターの設置（平成18年）により役割が移っている可能性がある。カ これによりご確認いただきたいことが3点増えた。★10/20 当方の先行（2回目）：老人福祉法の原文（e-gov 法令検索）に当たったところ、ご判断いただきたいことの前提そのものが変わった。キ 「老人福祉事業」は法律上の定義語である。第20条の8第1項は「老人居宅生活支援事業及び老人福祉施設による事業」を老人福祉事業と定義しており、第2項の量の目標はこの13区分（第5条の2第1項の6事業・第5条の3の7施設）についてのものである。村単独事業はこの定義に含まれない。したがって「村単独事業を老人福祉事業の量の目標に掲げるか」は法定記載事項の問題ではなく、任意の記載の問題である。素案4-6を、13区分の量の目標の所在を示す対応表と、(1)老人福祉施設および措置による確保、(2)村が実施する高齢者福祉サービスの構成に組み直した。ク 当方の条項の引用に2か所の誤りがあった。老人日常生活用具給付等は第10条の4第1項第3号ではなく同条第2項、短期入所の措置は同項第4号ではなく第3号である（第4号は小規模多機能型居宅介護）。原文で確かめて直した。ケ 例規の一覧から、村が老人福祉法上の施設を条例により設置していることが分かった。北塩原村デイサービスセンター条例（平成17年条例第35号）・同管理規則（平成17年規則第14号）・デイサービス運営事業実施要綱（平成11年要綱第5号）である。老人デイサービスセンターは第20条の2の2の老人福祉施設であり、量の目標の対象である。公表システムで確かめた村内の通所介護2か所はいずれも社会福祉法人の運営であり、うち1か所が村の条例による施設にあたるとみられる。コ 同様に、ホームヘルパー派遣手数料条例（平成3年条例第8号）・同施行規則（平成3年規則第5号）・登録ヘルパー事務処理要領（平成11年要領第1号）・ホームヘルプサービスチーム運営方式実施要綱（平成11年要綱第6号）があり、第10条の4第1項第1号の措置の枠組みが整っている。短期入所についても手数料徴収条例（平成5年条例第10号）・同施行規則（平成5年規則第11号）がある。いずれも素案は把握していなかった。サ 老人福祉センターは第4節に例規がない。ただし北塩原村活性化センター設置及び管理に関する条例（平成24年条例第12号）が第4節 老人福祉に置かれているため、同センターが老人福祉センターに相当する可能性がある。シ 手続の欠落が1つ見つかった。老人福祉法第20条の8第9項は、量の目標を定め、または変更しようとするときに、あらかじめ都道府県の意見を聴かなければならないとしている。素案1-6は介護保険法第117条第14項の意見聴取のみを書いていた。根拠も対象も違う別の義務であるため1-6に加えた。ス 残る5件のうち4件（なりすまし詐欺抑止装置・長寿を祝う会・防犯カメラ等の助成・活動活性化助成金）は第4節 老人福祉に根拠例規がなく、例規集への接続が拒まれたため他の章を当たれていない。帯状疱疹予防接種は予防接種法に基づく定期の予防接種であり、4-6には掲げない。10/10 起票：なりすまし詐欺抑止装置の無償貸与、火災警報器無償配布、在宅介護高齢者等寝具洗濯サービス、在宅介護高齢者等訪問理美容サービス、健康長寿祝金、長寿を祝う会（旧 敬老会）、防犯カメラ等の助成、地域・健康づくり活動活性化助成金、帯状疱疹予防接種の9件である。とくに防犯カメラ・なりすまし詐欺抑止装置・火災警報器の3件は施策2-4（安全・安心な暮らしの確保）の裏づけになる。素案は同施策を緊急通報システムだけで組み立てており、村はもっと広く手当している。老人福祉法第20条の8第2項の「確保すべき老人福祉事業の量の目標」として掲げるものと、施策の説明にとどめるものを分ける必要があるため、計画に掲げる範囲をご判断いただきたい。なお緊急通報システムとなりすまし詐欺抑止装置はいずれも「固定電話をお持ちの方」が要件である。固定電話のない高齢者世帯がどれだけあるかを把握していないため、見守りの網から漏れる層が生じ得る。把握されていればご教示いただきたい。★10/10：ご回答を待たずに素案を直した。老人福祉法第20条の8第2項は確保すべき老人福祉事業の量の目標を定めることを求めており、村が現に実施している事業を落とすと法定記載事項を欠くためである。9件のうち8件を4-6(2)の量の目標に加え、在宅福祉サービスを9事業から17事業に改めた（寝具洗濯サービス・訪問理美容サービス・なりすまし詐欺抑止装置の貸与・火災警報器の配布・防犯カメラ等の設置助成・長寿を祝う会・健康長寿祝金・地域・健康づくり活動活性化助成金）。帯状疱疹予防接種は予防接種による健康の保持の事業と考え、量の目標には掲げていない。あわせて、なりすまし詐欺抑止装置・火災警報器・防犯カメラの3件を施策2-4（日常生活の安全確保）の取組に加え、本文に村が緊急通報システムのほかにも広く手当していることを書いた。固定電話の要件についても、施策2-4の取組に「固定電話のない高齢者世帯の状況を把握し、代わりの手立てを検討します」を加え、指標を「未把握→把握」とした。★ご確認いただきたいのは次の10点である。①(2)に掲げた17のサービスは法律上の「老人福祉事業」ではない。村が現に行うものとして本節に掲げてよいか。掲げる範囲を狭めるご判断もあり得る。②このうち5事業（寝具洗濯・訪問理美容・長寿を祝う会・健康長寿祝金・活動活性化助成金）は第4章の施策体系に対応する施策がない。施策を新設するか、既存の施策に含めるか、量のみとするかのご判断をいただきたい。③固定電話のない高齢者世帯の数、または把握しているかどうか。④老人デイサービスセンター（平成17年条例第35号）は現に運営されているか。村内の通所介護2か所のうちどちらにあたるか。指定管理か委託か直営か。⑤老人介護支援センター（平成11年条例第5号）は現に設置されているか。地域包括支援センターとの関係はどうなっているか。⑥老人福祉センターとして設置された施設はあるか。活性化センター（平成24年条例第12号）がこれに相当するか。⑦老人福祉法第10条の4の3つの措置（第2項の日常生活用具給付等・第1項第1号のホームヘルパー派遣・第1項第3号の短期入所）の実績。火災警報器の配布は日常生活用具給付等事業によるものか。⑧養護老人ホーム（第11条第1項第1号）・特別養護老人ホーム（同項第2号）の措置の実績。養護受託者への養護委託（同項第3号）の実績。⑨第9期計画の策定にあたり、老人福祉法第20条の8第9項の県の意見聴取をどのように行ったか。介護保険法第117条第14項の意見聴取とあわせて1回で行えるか。⑩なりすまし詐欺抑止装置・長寿を祝う会・防犯カメラ等の助成・活動活性化助成金の4事業の実施の根拠。★10/21 当方の先行（3回目）：例規集への接続が通るようになったため、全70分野・569件（重複を除く）を当たった。ア 上記4事業の根拠となる例規は例規集にない。「詐欺」「なりすまし」「防犯カメラ」「健康づくり」「地域づくり」は0件、「長寿」は健康長寿祝金条例とその施行規則の2件のみ、「活性化」は活性化センター設置条例のみである。本村は補助金の交付要綱を例規集に登載する運用であり（骨髄移植ドナー支援事業助成金交付要綱・生ごみ処理機購入費補助金の交付等に関する要綱ほか）、また「北塩原村　事業補助金等の交付等に関する要綱（標準）」（昭和62年訓令第6号）を置いている。標準の要綱と予算措置により実施している可能性が高い。お尋ねするのは実施の根拠の1点である。イ あわせて第8類第4章 介護保険の22件と突き合わせたところ、素案に無い事業が2件あった。家族介護慰労金支給要綱（平成13年要綱第1号。要介護4・5で過去1年間施設サービスを受けなかった方を在宅で介護する家族に月額12,000円）と、住宅改修費の申請書に添付する理由書作成事業実施要綱（平成18年要綱第4号。60歳以上で認定を受けていない方。1件2,000円）である。いずれも4-6(2)に【要確認】で加えた。ウ 帯状疱疹予防接種は例規集に根拠がない。予防接種法に基づく定期の予防接種であるため当然である（4-6の注記のとおり）。★当方の扱い：ご回答がない場合は、13区分の対応表と(1)(2)の構成のまま、実績・目標を【要確認】として第2回策定委員会にお示しする。</t>
+          <t>★10/24 外部レビュー（Red Team）R06により起票。交付金の成果指標（要介護3〜5の2指標が0点）とは別に、認定の更新の前後で同じ方の要介護度が下がった・同じ・上がった人数を、要支援1・2／要介護1・2／要介護3〜5の層ごとに把握する指標を素案6-3に定義した。更新認定の件数と前後の要介護度、死亡・転出・更新の申請なしの件数（個人を特定しない集計で可）をご提供いただきたい。目標値はこの実績により設定する。</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-110,Ⅱ-54,Ⅱ-67</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>doc76§1-4,§1-5,素案4-6(2),素案 施策2-4</t>
+          <t>doc120</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>手引きにある事業は当方が洗い出す。計画に掲げるかの判断のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>★任意後見制度の周知の数え方（成年後見センターとの共催の催しを含めるか）</t>
+          <t>地域支援事業費・総合事業費の決算の複数年の推移（可能な範囲で5か年以上）</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>★成年後見センターとの共催の催しを任意後見制度の周知の実績に数えてよいかをご整理いただきたい。10/10 起票：素案4-7は国の取組状況調査（市町村票）の回答により「任意後見制度については、周知・広報を実施していません」としている。一方、令和8年10月23日・24日に会津権利擁護・成年後見センターと11市町村の共催で創作劇とトークセッションが開かれ、北塩原村が主催者に名を連ねている。創作劇はエンディングノートや後見契約を通じて「老い」と向き合う筋立てであり、判断能力が低下する前の備えを伝える取組が現に広域で行われている。調査票でこれを「周知・広報」と数えていないのは、数え方の問題か、村単独の周知を指して「実施していない」と答えたものか。後者であれば素案4-7を「村単独の周知は行っていないが、広域の取組に参画している」と書き改めたい。あわせて、この催しへの村民の参加状況（申込み・参加人数）が分かればご教示いただきたい。施策4-7の指標の基準値に使える。★同日追記：村公式HPの整理により、会津圏域11市町村と会津権利擁護・成年後見センターが共同で作成した「わたしの思いノート」（本人の医療・介護等への希望や考えを書き留めるツール）が村HPに載っていることが分かった。これも判断能力が低下する前の備えを伝える取組に当たり得る。催しと思いノートの2件をあわせて、周知の実績としてどう数えるかをご整理いただきたい。</t>
+          <t>地域支援事業費・総合事業費の決算の複数年の推移（可能な範囲で5か年以上）をご提供いただきたい。素案5-6は令和5年度決算（地域支援事業費39,886千円・総合事業費16,463千円）を3か年据え置いている。手元にある決算は令和4・5年度の2か年のみで、趨勢か単年度の振れかを判断できない。補助給付等についても対標準給付費比が令和4年度9.02%から令和5年度7.67%へ1.35ポイント下がっており（主因は特定入所者介護サービス費等の18.3%減）、据え置きが外れると保険料基準額は月額で最大96円動く（素案5-6）。★10/7 優先度を上げた：国の推計ワークシートは令和9年度47,686千円・令和10年度49,218千円・令和11年度50,751千円（年3.2%の伸び）で入っており、当方の据え置き（39,886千円×3）と3か年で27,996千円・23.4%開く。据え置きが外れたため、決算の推移の確認が据え置きの妥当性の検証から伸びの根拠の確認に変わった。</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-69,Ⅱ-68</t>
+          <t>Ⅱ-55,Ⅱ-56,Ⅱ-106</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>doc76§3,§7</t>
+          <t>doc47§5,doc66§3-3</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -3043,11 +3043,11 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>記載待ち</t>
+          <t>仮置き</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>★村公式HPに載っている高齢者福祉の取組のうち、本計画に書き込むものの確認</t>
+          <t>★高齢者の移動支援と配食サービスの実態（素案の記述と高齢者サービスの手引きが食い違う）</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>★10/10 起票：第8期障がい福祉計画の検討のために村公式HPを整理した資料の提供を受けた。本計画に関わる記述が次のとおりある。いずれも村HPの二次的な整理であり原典ではなく、当方の環境から村HPを開けないため（proxyが403）素案には書き込んでいない。原典（村HPまたは村の資料）でご確認いただくか、記載の可否をご教示いただきたい。①生活支援ハウスの名称は「シャルムハウス」か。素案4-6(1)は「生活支援ハウス」としか書いていない。②「除雪サービス登録事業者募集」を行っているか。素案の施策2-6は除雪支援について「担い手の確保が制約となる」としており、登録事業者を募る仕組みがあればその裏づけになる。③「わたしの思いノート」（会津圏域11市町村と会津権利擁護・成年後見センターが共同で作成した、本人の医療・介護等への希望や考えを書き留めるツール）の配布・活用の状況。施策4-3（在宅医療・介護連携）のACP・人生会議と、施策4-7（成年後見制度の利用促進）の判断能力が低下する前の備えの周知の、両方の裏づけになる。④「みんなの人権110番」（法務局職員・人権擁護委員が差別・虐待等の相談に対応）を施策4-1（高齢者虐待への対応）の相談経路として書いてよいか。⑤ヘルプマーク・ヘルプカード・耳マーク・おもいやり駐車場を、村全体の地域共生・合理的配慮の施策として本計画に触れてよいか。</t>
+          <t>★移動支援の利用人数と運行の状況、配食サービスの1回あたりの配達先の数をご教示いただきたい。10/10 起票：高齢者サービスの手引き（令和8年度版）により、素案4-6(2)の記述が実態と違うことが分かった。①移動支援：素案は「公共交通担当部局と連携し、介護予防・生活支援サービス事業による移動支援の創設を検討する」としているが、手引きによれば村民向け路線バスICカードを発行して喜多方⇔裏磐梯・猪苗代⇔裏磐梯の路線バスが無料であり、路線バス運行区域以外でも無料のコミュニティバスが運行している（総務企画課防災係）。すでにある仕組みを「創設を検討」と書くのは実態と違うため、「既存の仕組みの活用と周知、および路線バスが届かない範囲の補い方の検討」に改めたい。ご異存がないかと、路線バスが届かない地区・時間帯があるかをご教示いただきたい。②配食サービス：素案は「村の委託により現在の体制を維持する」としているが、手引きによれば赤十字奉仕団によるひとり暮らし高齢者弁当配達サービスで年4回予定である。年4回を「配食サービス」として量の目標を置くのは無理があるため、毎日の食事の確保という課題に対して現状が年4回であることを課題として書きたい。この整理でよいかをご確認いただきたい。★10/10：ご回答を待たずに素案を直した。すでにある仕組みを「創設を検討」と書いた計画書は、委員から見て村の実態を把握していない資料に見えるためである。直した内容は次のとおりである。①移動支援：4-6(2)の事業名を「高齢者の移動支援（路線バスICカード・コミュニティバス）」に改め、確保の方策を「村民向けの路線バスICカードの発行と無料のコミュニティバスの運行を継続し、周知を図る。これらで届かない範囲について、介護予防・生活支援サービス事業による補い方を検討する」とした。施策2-1の本文に既存の仕組みを書き、取組を4項目に改め（課題の把握／周知／届かない範囲の補い方／連携の継続）、指標に「路線バスICカードの交付を受けた方の人数」を加えた。②配食：4-6(2)の事業名を「ひとり暮らし高齢者弁当配達サービス」に改め、単位を「回／年」、目標を令和9〜11年度いずれも4回とした。総合事業の配食（未実施）とは別の事業であることを注記し、毎日の食事の確保という課題に対しては年4回では足りないため総合事業による配食の創設を施策1-2で検討する旨を書いた。★素案を直したため、ご確認いただきたいことは次のとおりに絞られる。・路線バスICカードとコミュニティバスの所管は総務企画課防災係でよいか。・路線バスICカードの交付を受けた方の人数と、コミュニティバスの利用の状況（地区別）。施策2-1の「移動に関する課題の把握」が国の評価指標で0点にとどまっているため、既存の仕組みが届いていない範囲を示す材料として要する。・弁当配達サービスの年4回は令和9年度以降も同じ回数を予定するか。あわせて1回あたりの配達先の数（利用人数）をご教示いただきたい。量の目標に置けているのは「回／年」だけであり、どれだけの方に届いているかが分からない。★当方の扱い：人数・利用の状況・回数のご回答がない場合、実績の欄は空欄、移動支援の目標は「―」のまま、弁当配達は年4回を据え置いてお示しする。</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-110,Ⅱ-69</t>
+          <t>Ⅱ-110,Ⅱ-54</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>doc76§7</t>
+          <t>doc76§1-3,素案4-6(2),素案 施策2-1</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
@@ -3100,8 +3100,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I46" s="4" t="inlineStr"/>
-      <c r="J46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
           <t>Ｃ</t>
@@ -3109,7 +3115,7 @@
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>村公式HPは当方が通読して拾う。拾い漏れと誤りのみ伺う</t>
+          <t>高齢者サービスの手引きは受領済みであり、当方が突き合わせる。実態の確定のみ伺う</t>
         </is>
       </c>
     </row>
@@ -3124,22 +3130,22 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>★緊急連絡カードの計画上の位置づけと、当方が取り扱う予定の有無</t>
+          <t>★高齢者サービスの手引きにあって素案に載っていない村単独事業9件を計画に掲げるか</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>★10/10 起票：緊急連絡カード（2人分の様式）の提供を受けた。素案に記載がない。①施策2-4（安全・安心な暮らしの確保）に位置づけてよいか。緊急通報システムは「固定電話をお持ちの方」が要件であるのに対し、緊急連絡カードは固定電話がない世帯にも届く手段であり、要件の穴を補う位置にある。配布の実績（配布数・設置の確認）が分かればご教示いただきたい。②記入後のカードは持病・お薬・かかりつけ医・血液型という要配慮個人情報を含む。doc16 §1（本業務で取り扱う個人情報）の一覧に入っていない。当方がこのカードを取り扱う予定があるか、記入済みのカードが調査票と一緒に届くことがないかをご確認いただきたい。</t>
+          <t>★村単独事業9件について、本計画に掲げる範囲をご判断いただきたい。★10/20 当方の先行：例規集のドメインを加えていただき、北塩原村例規集（内容現在 令和8年6月26日）の第8類 厚生 第1章 社会福祉 第4節 老人福祉の32件と突き合わせた。ア 9件のうち4件は根拠となる例規を確かめた。寝具洗濯サービスは北塩原村寝たきり老人等寝具丸洗い事業実施要綱（平成14年告示第19号）、訪問理美容サービスは同訪問理美容サービス事業実施要綱（平成15年訓令第1号）、健康長寿祝金は同健康長寿祝金条例（令和6年条例第9号）および同条例施行規則（令和6年規則第13号）である。火災警報器の配布は北塩原村老人日常生活用具給付等事業実施要綱（平成8年訓令第6号）による可能性が高いが、対象品目を確かめていない。イ 名称の食い違いがある。手引きは「寝具洗濯サービス」、例規は「寝具丸洗い」である。素案は手引きの呼び方を用い、根拠例規の名称を注記に書いた。ウ 残る5件（なりすまし詐欺抑止装置・長寿を祝う会・防犯カメラ等の助成・地域健康づくり活動活性化助成金・帯状疱疹予防接種）は第4節 老人福祉になく、他の章（防災・保健衛生等）にあるとみられる。例規集への接続が再び拒まれたため当方では確かめられていない。エ 逆向きの突合せでより重いものが見つかった。例規にあって素案4-6に対応がない老人福祉法上の事業・施設が3件ある。1つめは老人介護支援センター（北塩原村在宅介護支援センター条例 平成11年条例第5号・同運営事業実施要綱 平成18年要綱第5号）。老人福祉法第5条の3の老人福祉施設であり、第20条の8第2項第1号が定めることを求める施設にあたる。2つめは老人日常生活用具給付等（平成8年訓令第6号）で、同法第10条の4第1項第3号の事業である。3つめは短期入所のやむを得ない事由による措置（平成10年要綱第1号）で、同項第4号の措置であり、介護保険の短期入所生活介護とは別のものである。オ 3件を素案4-6(2)に加えた。ただし要綱が効力を有することと事業が現に行われていることとは別であるため、実績と目標は【要確認】としている。とくに在宅介護支援センターは、地域包括支援センターの設置（平成18年）により役割が移っている可能性がある。カ これによりご確認いただきたいことが3点増えた。★10/20 当方の先行（2回目）：老人福祉法の原文（e-gov 法令検索）に当たったところ、ご判断いただきたいことの前提そのものが変わった。キ 「老人福祉事業」は法律上の定義語である。第20条の8第1項は「老人居宅生活支援事業及び老人福祉施設による事業」を老人福祉事業と定義しており、第2項の量の目標はこの13区分（第5条の2第1項の6事業・第5条の3の7施設）についてのものである。村単独事業はこの定義に含まれない。したがって「村単独事業を老人福祉事業の量の目標に掲げるか」は法定記載事項の問題ではなく、任意の記載の問題である。素案4-6を、13区分の量の目標の所在を示す対応表と、(1)老人福祉施設および措置による確保、(2)村が実施する高齢者福祉サービスの構成に組み直した。ク 当方の条項の引用に2か所の誤りがあった。老人日常生活用具給付等は第10条の4第1項第3号ではなく同条第2項、短期入所の措置は同項第4号ではなく第3号である（第4号は小規模多機能型居宅介護）。原文で確かめて直した。ケ 例規の一覧から、村が老人福祉法上の施設を条例により設置していることが分かった。北塩原村デイサービスセンター条例（平成17年条例第35号）・同管理規則（平成17年規則第14号）・デイサービス運営事業実施要綱（平成11年要綱第5号）である。老人デイサービスセンターは第20条の2の2の老人福祉施設であり、量の目標の対象である。公表システムで確かめた村内の通所介護2か所はいずれも社会福祉法人の運営であり、うち1か所が村の条例による施設にあたるとみられる。コ 同様に、ホームヘルパー派遣手数料条例（平成3年条例第8号）・同施行規則（平成3年規則第5号）・登録ヘルパー事務処理要領（平成11年要領第1号）・ホームヘルプサービスチーム運営方式実施要綱（平成11年要綱第6号）があり、第10条の4第1項第1号の措置の枠組みが整っている。短期入所についても手数料徴収条例（平成5年条例第10号）・同施行規則（平成5年規則第11号）がある。いずれも素案は把握していなかった。サ 老人福祉センターは第4節に例規がない。ただし北塩原村活性化センター設置及び管理に関する条例（平成24年条例第12号）が第4節 老人福祉に置かれているため、同センターが老人福祉センターに相当する可能性がある。シ 手続の欠落が1つ見つかった。老人福祉法第20条の8第9項は、量の目標を定め、または変更しようとするときに、あらかじめ都道府県の意見を聴かなければならないとしている。素案1-6は介護保険法第117条第14項の意見聴取のみを書いていた。根拠も対象も違う別の義務であるため1-6に加えた。ス 残る5件のうち4件（なりすまし詐欺抑止装置・長寿を祝う会・防犯カメラ等の助成・活動活性化助成金）は第4節 老人福祉に根拠例規がなく、例規集への接続が拒まれたため他の章を当たれていない。帯状疱疹予防接種は予防接種法に基づく定期の予防接種であり、4-6には掲げない。10/10 起票：なりすまし詐欺抑止装置の無償貸与、火災警報器無償配布、在宅介護高齢者等寝具洗濯サービス、在宅介護高齢者等訪問理美容サービス、健康長寿祝金、長寿を祝う会（旧 敬老会）、防犯カメラ等の助成、地域・健康づくり活動活性化助成金、帯状疱疹予防接種の9件である。とくに防犯カメラ・なりすまし詐欺抑止装置・火災警報器の3件は施策2-4（安全・安心な暮らしの確保）の裏づけになる。素案は同施策を緊急通報システムだけで組み立てており、村はもっと広く手当している。老人福祉法第20条の8第2項の「確保すべき老人福祉事業の量の目標」として掲げるものと、施策の説明にとどめるものを分ける必要があるため、計画に掲げる範囲をご判断いただきたい。なお緊急通報システムとなりすまし詐欺抑止装置はいずれも「固定電話をお持ちの方」が要件である。固定電話のない高齢者世帯がどれだけあるかを把握していないため、見守りの網から漏れる層が生じ得る。把握されていればご教示いただきたい。★10/10：ご回答を待たずに素案を直した。老人福祉法第20条の8第2項は確保すべき老人福祉事業の量の目標を定めることを求めており、村が現に実施している事業を落とすと法定記載事項を欠くためである。9件のうち8件を4-6(2)の量の目標に加え、在宅福祉サービスを9事業から17事業に改めた（寝具洗濯サービス・訪問理美容サービス・なりすまし詐欺抑止装置の貸与・火災警報器の配布・防犯カメラ等の設置助成・長寿を祝う会・健康長寿祝金・地域・健康づくり活動活性化助成金）。帯状疱疹予防接種は予防接種による健康の保持の事業と考え、量の目標には掲げていない。あわせて、なりすまし詐欺抑止装置・火災警報器・防犯カメラの3件を施策2-4（日常生活の安全確保）の取組に加え、本文に村が緊急通報システムのほかにも広く手当していることを書いた。固定電話の要件についても、施策2-4の取組に「固定電話のない高齢者世帯の状況を把握し、代わりの手立てを検討します」を加え、指標を「未把握→把握」とした。★ご確認いただきたいのは次の10点である。①(2)に掲げた17のサービスは法律上の「老人福祉事業」ではない。村が現に行うものとして本節に掲げてよいか。掲げる範囲を狭めるご判断もあり得る。②このうち5事業（寝具洗濯・訪問理美容・長寿を祝う会・健康長寿祝金・活動活性化助成金）は第4章の施策体系に対応する施策がない。施策を新設するか、既存の施策に含めるか、量のみとするかのご判断をいただきたい。③固定電話のない高齢者世帯の数、または把握しているかどうか。④老人デイサービスセンター（平成17年条例第35号）は現に運営されているか。村内の通所介護2か所のうちどちらにあたるか。指定管理か委託か直営か。⑤老人介護支援センター（平成11年条例第5号）は現に設置されているか。地域包括支援センターとの関係はどうなっているか。⑥老人福祉センターとして設置された施設はあるか。活性化センター（平成24年条例第12号）がこれに相当するか。⑦老人福祉法第10条の4の3つの措置（第2項の日常生活用具給付等・第1項第1号のホームヘルパー派遣・第1項第3号の短期入所）の実績。火災警報器の配布は日常生活用具給付等事業によるものか。⑧養護老人ホーム（第11条第1項第1号）・特別養護老人ホーム（同項第2号）の措置の実績。養護受託者への養護委託（同項第3号）の実績。⑨第9期計画の策定にあたり、老人福祉法第20条の8第9項の県の意見聴取をどのように行ったか。介護保険法第117条第14項の意見聴取とあわせて1回で行えるか。⑩なりすまし詐欺抑止装置・長寿を祝う会・防犯カメラ等の助成・活動活性化助成金の4事業の実施の根拠。★10/21 当方の先行（3回目）：例規集への接続が通るようになったため、全70分野・569件（重複を除く）を当たった。ア 上記4事業の根拠となる例規は例規集にない。「詐欺」「なりすまし」「防犯カメラ」「健康づくり」「地域づくり」は0件、「長寿」は健康長寿祝金条例とその施行規則の2件のみ、「活性化」は活性化センター設置条例のみである。本村は補助金の交付要綱を例規集に登載する運用であり（骨髄移植ドナー支援事業助成金交付要綱・生ごみ処理機購入費補助金の交付等に関する要綱ほか）、また「北塩原村　事業補助金等の交付等に関する要綱（標準）」（昭和62年訓令第6号）を置いている。標準の要綱と予算措置により実施している可能性が高い。お尋ねするのは実施の根拠の1点である。イ あわせて第8類第4章 介護保険の22件と突き合わせたところ、素案に無い事業が2件あった。家族介護慰労金支給要綱（平成13年要綱第1号。要介護4・5で過去1年間施設サービスを受けなかった方を在宅で介護する家族に月額12,000円）と、住宅改修費の申請書に添付する理由書作成事業実施要綱（平成18年要綱第4号。60歳以上で認定を受けていない方。1件2,000円）である。いずれも4-6(2)に【要確認】で加えた。ウ 帯状疱疹予防接種は例規集に根拠がない。予防接種法に基づく定期の予防接種であるため当然である（4-6の注記のとおり）。★当方の扱い：ご回答がない場合は、13区分の対応表と(1)(2)の構成のまま、実績・目標を【要確認】として第2回策定委員会にお示しする。</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅴ-97</t>
+          <t>Ⅱ-110,Ⅱ-54,Ⅱ-67</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>doc76§2</t>
+          <t>doc76§1-4,§1-5,素案4-6(2),素案 施策2-4</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -3162,12 +3168,12 @@
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>手引きにある事業は当方が洗い出す。計画に掲げるかの判断のみ伺う</t>
         </is>
       </c>
     </row>
@@ -3177,32 +3183,32 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
+          <t>★任意後見制度の周知の数え方（成年後見センターとの共催の催しを含めるか）</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>★会津地方介護福祉士養成貸付事業ほか県の制度について、本村からの利用実績の有無をご教示いただきたい。★10/20 当方の先行：県のサイトに接続できるようになったため、県の事業の内容を確かめた。ア 会津地方介護福祉士養成貸付事業がある。会津地方に住所があり、養成施設卒業後に会津地方で介護職として働く意欲のある方が対象で、対象地域に北塩原村が明記されている（会津若松市・喜多方市・下郷町・檜枝岐村・只見町・南会津町・北塩原村・西会津町・磐梯町・猪苗代町・会津坂下町・湯川村・柳津町・三島町・金山町・昭和村・会津美里町）。イ 貸付は住居費 月額3万6千円以内、または公共交通機関の通学定期代の実費。修学期間中と就労期間中は無利子。会津地方の介護施設に就職して介護業務に3年以上従事すると返還が免除される。3年未満での退職は最長3年以内の月賦返還、退学や卒業後1年以内に会津地方の介護施設に就職できなかった場合は一括返還。ウ 募集人員は5名程度（予定）。申込みは在学する養成施設等を通じて福島県社会福祉協議会に行う。所管は県社会福祉課（福祉・介護人材担当）。エ ほかに介護福祉士修学資金等貸付事業（修学資金 月5万円以内、入学準備金・就職準備金 各20万円以内）があり、復職資金や他分野からの転職準備金も扱う。オ 以上を素案の施策4-6に取組として書いた。お尋ねするのは本村からの利用実績の有無の1点に絞られた。ご回答がない場合は、実績に触れず制度の周知を続ける旨のみを記す。★介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と、本村からの利用実績をご教示いただきたい。令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。</t>
+          <t>★成年後見センターとの共催の催しを任意後見制度の周知の実績に数えてよいかをご整理いただきたい。10/10 起票：素案4-7は国の取組状況調査（市町村票）の回答により「任意後見制度については、周知・広報を実施していません」としている。一方、令和8年10月23日・24日に会津権利擁護・成年後見センターと11市町村の共催で創作劇とトークセッションが開かれ、北塩原村が主催者に名を連ねている。創作劇はエンディングノートや後見契約を通じて「老い」と向き合う筋立てであり、判断能力が低下する前の備えを伝える取組が現に広域で行われている。調査票でこれを「周知・広報」と数えていないのは、数え方の問題か、村単独の周知を指して「実施していない」と答えたものか。後者であれば素案4-7を「村単独の周知は行っていないが、広域の取組に参画している」と書き改めたい。あわせて、この催しへの村民の参加状況（申込み・参加人数）が分かればご教示いただきたい。施策4-7の指標の基準値に使える。★同日追記：村公式HPの整理により、会津圏域11市町村と会津権利擁護・成年後見センターが共同で作成した「わたしの思いノート」（本人の医療・介護等への希望や考えを書き留めるツール）が村HPに載っていることが分かった。これも判断能力が低下する前の備えを伝える取組に当たり得る。催しと思いノートの2件をあわせて、周知の実績としてどう数えるかをご整理いただきたい。</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-54</t>
+          <t>Ⅱ-69,Ⅱ-68</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>doc41§3</t>
+          <t>doc76§3,§7</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
@@ -3210,16 +3216,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I48" s="4" t="inlineStr"/>
-      <c r="J48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>県の事業の内容は公表されている。本村からの利用実績のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -3229,27 +3241,27 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>計画書・報告書の頁数の実測（Word＋游ゴシックで開いた実際の頁数）</t>
+          <t>★村公式HPに載っている高齢者福祉の取組のうち、本計画に書き込むものの確認</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>★計画書・報告書をWordで開いた実際の頁数をご確認いただきたい。10/10 当方でも docx→PDF 変換ができるようになり、紙面を実測した（doc83）。★10/12 障がい福祉計画との突合で書き足したため測り直した。★10/15 法定記載事項の反映と、課長会議資料・県計画の照合で書き足したため測り直した。★10/21 例規集の全分野と突き合わせて施策1-2・施策4-6・4-6(2)・5-9を直したため測り直した。協議用の計画書は実測で推定より3頁多かった（10/21）。同日の2度目の実測では、素案が150頁から151頁に伸びたのに計画書は7通りとも1頁減った。表が前の頁に収まり、空きかけていた頁が1つ畳まれたためである。3度目（他3町のブランチとの突合せで交付金の試算を直し、素案2-8に条件の近い団体との比較を加えた）では7通りとも1〜2頁増えた。公表用は別に測っている（案なし121頁・案をすべて行って107頁）。ただし游ゴシックは当方の環境に無く、IPAゴシックに置き換えて組んだ値である。★10/23 書体を BIZ UDPゴシック（障がい福祉計画と同じ。Windows 10 以降に標準）に改め、当方の環境にも入れて測り直した（doc114）。書体を改めた直後は協議用133頁・公表用（案なし）119頁であった。同日、事業所別の5か年推移を反映して協議用135頁・公表用121頁、10/24に令和5・6年度の決算を反映して協議用は本文133頁＋前付4頁＝137頁、公表用は本文119頁＋前付4頁＝123頁になった（doc116・doc118）。村の Word と字の形・幅は同じになったが、改頁の位置は Word で確かめる。行送りは lineRule=exact で固定したためフォントによらないが、欧文の字送りと禁則処理の違いでなお±1〜2頁動き得る。村側で Word で開いて実際の頁数をご確認いただきたい。分量を目安に収める削減案は別に起票している（成果品 削減案A〜Nの採否）。施策体系図（図3-1）とSDGsの対応表は素案3-4・3-5に追加済みである。</t>
+          <t>★10/10 起票：第8期障がい福祉計画の検討のために村公式HPを整理した資料の提供を受けた。本計画に関わる記述が次のとおりある。いずれも村HPの二次的な整理であり原典ではなく、当方の環境から村HPを開けないため（proxyが403）素案には書き込んでいない。原典（村HPまたは村の資料）でご確認いただくか、記載の可否をご教示いただきたい。①生活支援ハウスの名称は「シャルムハウス」か。素案4-6(1)は「生活支援ハウス」としか書いていない。②「除雪サービス登録事業者募集」を行っているか。素案の施策2-6は除雪支援について「担い手の確保が制約となる」としており、登録事業者を募る仕組みがあればその裏づけになる。③「わたしの思いノート」（会津圏域11市町村と会津権利擁護・成年後見センターが共同で作成した、本人の医療・介護等への希望や考えを書き留めるツール）の配布・活用の状況。施策4-3（在宅医療・介護連携）のACP・人生会議と、施策4-7（成年後見制度の利用促進）の判断能力が低下する前の備えの周知の、両方の裏づけになる。④「みんなの人権110番」（法務局職員・人権擁護委員が差別・虐待等の相談に対応）を施策4-1（高齢者虐待への対応）の相談経路として書いてよいか。⑤ヘルプマーク・ヘルプカード・耳マーク・おもいやり駐車場を、村全体の地域共生・合理的配慮の施策として本計画に触れてよいか。</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅱ-67,Ⅱ-110,Ⅱ-69</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>doc40§1-4,doc83</t>
+          <t>doc76§7</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -3271,7 +3283,7 @@
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>当方で紙面を実測済みである。村のWordで開いた頁数のみ伺う</t>
+          <t>村公式HPは当方が通読して拾う。拾い漏れと誤りのみ伺う</t>
         </is>
       </c>
     </row>
@@ -3281,32 +3293,32 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
+          <t>★緊急連絡カードの計画上の位置づけと、当方が取り扱う予定の有無</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
+          <t>★10/10 起票：緊急連絡カード（2人分の様式）の提供を受けた。素案に記載がない。①施策2-4（安全・安心な暮らしの確保）に位置づけてよいか。緊急通報システムは「固定電話をお持ちの方」が要件であるのに対し、緊急連絡カードは固定電話がない世帯にも届く手段であり、要件の穴を補う位置にある。配布の実績（配布数・設置の確認）が分かればご教示いただきたい。②記入後のカードは持病・お薬・かかりつけ医・血液型という要配慮個人情報を含む。doc16 §1（本業務で取り扱う個人情報）の一覧に入っていない。当方がこのカードを取り扱う予定があるか、記入済みのカードが調査票と一緒に届くことがないかをご確認いただきたい。</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅳ-89</t>
+          <t>Ⅱ-67,Ⅴ-97</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>doc01-10</t>
+          <t>doc76§2</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
@@ -3314,8 +3326,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I50" s="4" t="inlineStr"/>
-      <c r="J50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -3333,27 +3351,27 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
+          <t>介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と本村からの利用実績</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
+          <t>★会津地方介護福祉士養成貸付事業ほか県の制度について、本村からの利用実績の有無をご教示いただきたい。★10/20 当方の先行：県のサイトに接続できるようになったため、県の事業の内容を確かめた。ア 会津地方介護福祉士養成貸付事業がある。会津地方に住所があり、養成施設卒業後に会津地方で介護職として働く意欲のある方が対象で、対象地域に北塩原村が明記されている（会津若松市・喜多方市・下郷町・檜枝岐村・只見町・南会津町・北塩原村・西会津町・磐梯町・猪苗代町・会津坂下町・湯川村・柳津町・三島町・金山町・昭和村・会津美里町）。イ 貸付は住居費 月額3万6千円以内、または公共交通機関の通学定期代の実費。修学期間中と就労期間中は無利子。会津地方の介護施設に就職して介護業務に3年以上従事すると返還が免除される。3年未満での退職は最長3年以内の月賦返還、退学や卒業後1年以内に会津地方の介護施設に就職できなかった場合は一括返還。ウ 募集人員は5名程度（予定）。申込みは在学する養成施設等を通じて福島県社会福祉協議会に行う。所管は県社会福祉課（福祉・介護人材担当）。エ ほかに介護福祉士修学資金等貸付事業（修学資金 月5万円以内、入学準備金・就職準備金 各20万円以内）があり、復職資金や他分野からの転職準備金も扱う。オ 以上を素案の施策4-6に取組として書いた。お尋ねするのは本村からの利用実績の有無の1点に絞られた。ご回答がない場合は、実績に触れず制度の周知を続ける旨のみを記す。★介護人材の確保に関する福島県の事業（介護人材確保対策・修学資金貸付）の内容と、本村からの利用実績をご教示いただきたい。令和8年度の交付金（都道府県分）により、介護人材の確保・サービス提供基盤の整備は福島県が全国平均を13.1点下回る県全体の課題であることが判明した（本村は▲4.8点）。本村単独では動かしにくいため、施策4-6は県の事業と定住自立圏（喜多方市・西会津町）の研修費用助成を活用する形に組み立てたい。</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-67,Ⅱ-54</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>doc15,doc18</t>
+          <t>doc41§3</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
@@ -3370,12 +3388,12 @@
       <c r="J51" s="4" t="inlineStr"/>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>県の事業の内容は公表されている。本村からの利用実績のみ伺う</t>
         </is>
       </c>
     </row>
@@ -3385,27 +3403,27 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
+          <t>計画書・報告書の頁数の実測（Word＋游ゴシックで開いた実際の頁数）</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
+          <t>★計画書・報告書をWordで開いた実際の頁数をご確認いただきたい。10/10 当方でも docx→PDF 変換ができるようになり、紙面を実測した（doc83）。★10/12 障がい福祉計画との突合で書き足したため測り直した。★10/15 法定記載事項の反映と、課長会議資料・県計画の照合で書き足したため測り直した。★10/21 例規集の全分野と突き合わせて施策1-2・施策4-6・4-6(2)・5-9を直したため測り直した。協議用の計画書は実測で推定より3頁多かった（10/21）。同日の2度目の実測では、素案が150頁から151頁に伸びたのに計画書は7通りとも1頁減った。表が前の頁に収まり、空きかけていた頁が1つ畳まれたためである。3度目（他3町のブランチとの突合せで交付金の試算を直し、素案2-8に条件の近い団体との比較を加えた）では7通りとも1〜2頁増えた。公表用は別に測っている（案なし121頁・案をすべて行って107頁）。ただし游ゴシックは当方の環境に無く、IPAゴシックに置き換えて組んだ値である。★10/23 書体を BIZ UDPゴシック（障がい福祉計画と同じ。Windows 10 以降に標準）に改め、当方の環境にも入れて測り直した（doc114）。書体を改めた直後は協議用133頁・公表用（案なし）119頁であった。同日、事業所別の5か年推移を反映して協議用135頁・公表用121頁、10/24に令和5・6年度の決算を反映して協議用は本文133頁＋前付4頁＝137頁、公表用は本文119頁＋前付4頁＝123頁になった（doc116・doc118）。★10/24 外部レビュー（Red Team）の指摘を反映し、協議用素案は本文155頁、協議用の計画書は本文135頁＋前付4頁＝139頁、公表用は本文122頁＋前付4頁＝126頁になった（doc120）。村の Word と字の形・幅は同じになったが、改頁の位置は Word で確かめる。行送りは lineRule=exact で固定したためフォントによらないが、欧文の字送りと禁則処理の違いでなお±1〜2頁動き得る。村側で Word で開いて実際の頁数をご確認いただきたい。分量を目安に収める削減案は別に起票している（成果品 削減案A〜Nの採否）。施策体系図（図3-1）とSDGsの対応表は素案3-4・3-5に追加済みである。</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>doc14§5,doc18 3-1</t>
+          <t>doc40§1-4,doc83</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
@@ -3422,12 +3440,12 @@
       <c r="J52" s="4" t="inlineStr"/>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>当方で紙面を実測済みである。村のWordで開いた頁数のみ伺う</t>
         </is>
       </c>
     </row>
@@ -3437,32 +3455,32 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>素案</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
+          <t>計画書の判型・レイアウト・表紙デザインの踏襲可否</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
+          <t>第9期はA4・本文104頁・全6章＋資料編。</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-71,Ⅱ-75</t>
+          <t>Ⅱ-113,Ⅳ-89</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>doc14§5,doc15,doc18 4-5</t>
+          <t>doc01-10</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
@@ -3494,12 +3512,12 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
+          <t>章構成を第9期（全6章＋資料編）から踏襲することの可否</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
+          <t>素案は踏襲を前提。第2章に「2-8 保険者機能の評価」「2-9 第9期計画の進捗と評価」の2節を新設している。</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -3509,7 +3527,7 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>doc17 B-3,doc18 4-3</t>
+          <t>doc15,doc18</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -3546,22 +3564,22 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
+          <t>基本理念・基本目標の枠組みを第9期から継承することの可否</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
+          <t>素案は継承を前提に構成。変更する場合は第3章・第4章の全面的な組み替えが必要になる。</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 2-9</t>
+          <t>doc14§5,doc18 3-1</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3598,22 +3616,22 @@
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
+          <t>基本目標5「計画の推進と進捗管理」を独立させるか、各基本目標に横断的に組み込むか</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
+          <t>第9期で3年連続0点だったPDCAへの対応。独立を推奨するが構成上の選択であり村の意向による。</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-64,Ⅱ-75</t>
+          <t>Ⅱ-71,Ⅱ-75</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>doc17 A-1,doc18 5-7</t>
+          <t>doc14§5,doc15,doc18 4-5</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3645,27 +3663,27 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
+          <t>施設サービスの記載を「村外施設サービスの利用支援」に改めることの可否</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
+          <t>村内に該当施設がゼロ。第9期は特養〜介護医療院の4類型を列挙する記載で実態と乖離していた。</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-65</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>doc13§6</t>
+          <t>doc17 B-3,doc18 4-3</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3697,37 +3715,37 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
+          <t>計画本文に第9期の推計乖離（第1号被保険者数6.6%）を記載することの可否</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
+          <t>素案の2-9・5-1に記載。次期計画で本計画の推計精度を検証できるようにする趣旨だが、自らの誤差を公表することになるため村の判断を要する。</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-29,Ⅰ-32</t>
+          <t>Ⅱ-75</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>doc19 指-1／doc22 A-4</t>
+          <t>doc17 A-1,doc18 2-9</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>再提起</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr"/>
@@ -3749,32 +3767,32 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>素案</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
+          <t>第9期保険料の再算定試算（6,761円→約6,346円）の取扱い</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
+          <t>第1号被保険者数のみを実績に置換した試算で、福島県平均6,340円とほぼ一致する。素案5-7に記載しているが、公表資料での扱いは村の判断による。</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-16,Ⅰ-18</t>
+          <t>Ⅱ-64,Ⅱ-75</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-3</t>
+          <t>doc17 A-1,doc18 5-7</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
@@ -3801,32 +3819,32 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
+          <t>成果目標・活動指標の目標値の設定方針（認定率を据置とするか／トレンド継続か／政策効果を織り込むか）</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
+          <t>doc13§6で3案を提示。政策効果を織り込む案を採る場合は、その根拠を指標に置く必要がある。</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-20,Ⅰ-21</t>
+          <t>Ⅱ-60,Ⅱ-65</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>doc19 S-5</t>
+          <t>doc13§6</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
@@ -3858,22 +3876,22 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>依頼状の差出人名義（村名義／村長名）</t>
+          <t>★発送日の確定（9/17前倒し／9/18のまま／9/24後ろ倒し）と回収期限</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
+          <t>★議事録は「9月18日頃」とするのみで、5連休の論点に触れていない。9/17（木）への前倒し可否と回収期限を9/3の第1稿提出時に併せて提起する。</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-29,Ⅰ-32</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-4／doc23§5</t>
+          <t>doc19 指-1／doc22 A-4</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -3883,7 +3901,7 @@
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>再提起</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr"/>
@@ -3910,22 +3928,22 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>調査票の印刷部数（予備を何部見込むか）</t>
+          <t>★ウェブ回答フォームにGoogleフォームを用いることの可否</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
+          <t>★通信の暗号化とデータの保存先は別の論点。回答データが村外サーバに保存される。個人情報保護条例上の取扱いと、重複排除の実装・エクスポート後の元データ削除・公開期間管理の確認が必要。</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-21,Ⅰ-22</t>
+          <t>Ⅰ-16,Ⅰ-18</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-5</t>
+          <t>doc19 追-3</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -3962,22 +3980,22 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>在宅介護実態調査 問8・問9の基準月</t>
+          <t>調査票の印刷頁数の調整方針（仕様書はニーズ約12頁／在宅約8頁）</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>発送月の前月が通常。発送日の確定とセット。</t>
+          <t>現在の調査票案は設問数が多く、レイアウト調整か設問の絞り込みが必要になる可能性。オプション項目の採否と一体。</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-20,Ⅰ-21</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-2</t>
+          <t>doc19 S-5</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -4009,27 +4027,27 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>宛名ラベル・配布用封筒の提供期限の前倒し可否（9/14→9/11）</t>
+          <t>依頼状の差出人名義（村名義／村長名）</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>★提供が1日遅れると発送が5連休に食い込む。村作業の遅延に対する余裕がない。</t>
+          <t>★第1稿は「北塩原村長　遠藤　和夫」と村長名で作成済み。名義の可否と、あわせて現職の村長名が正しいかの確認が必要（当方が保有する平成30年の資料では別の方が村長）。</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-25,Ⅰ-26</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>doc19 指-2</t>
+          <t>doc19 追-4／doc23§5</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -4039,7 +4057,7 @@
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr"/>
@@ -4066,27 +4084,27 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
+          <t>調査票の印刷部数（予備を何部見込むか）</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
+          <t>約1,000部＋予備。発送後の追加印刷は工程上困難。</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-31</t>
+          <t>Ⅰ-21,Ⅰ-22</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-6</t>
+          <t>doc19 追-5</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H65" s="4" t="inlineStr">
@@ -4118,27 +4136,27 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
+          <t>在宅介護実態調査 問8・問9の基準月</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
+          <t>発送月の前月が通常。発送日の確定とセット。</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-40,Ⅰ-42</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-7</t>
+          <t>doc19 追-2</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H66" s="4" t="inlineStr">
@@ -4165,32 +4183,32 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
+          <t>宛名ラベル・配布用封筒の提供期限の前倒し可否（9/14→9/11）</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>★見込量推計の停止要因。見える化にサービス種類別の受給者数の系列はないが、第1号被保険者1人あたり給付月額（D13系列）に第1号被保険者数を乗じ、受給者1人あたり給付月額（D17系列）で除せば受給者数を算出できる。通所介護で検算したところ素案の値（令和5年度37.2・令和6年度42.2・令和7年度38.9人／月）と一致した。D17系列があるのは15サービスで、居住系の認知症対応型共同生活介護・特定施設入居者生活介護を含む。★10/7：したがって停止しているのは施設サービス3種（介護老人福祉施設・介護老人保健施設・介護医療院）のみで、この3種はD17系列がないため按分した参考値のままである。確定値にするには月報 第2表・第3表の実数が要る。居住系2種は算出に切り替える（素案5-4(3)）。</t>
+          <t>★提供が1日遅れると発送が5連休に食い込む。村作業の遅延に対する余裕がない。</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅰ-25,Ⅰ-26</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>doc30§5-3</t>
+          <t>doc19 指-2</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H67" s="4" t="inlineStr">
@@ -4217,27 +4235,27 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
+          <t>督促（リマインド）の実施可否と追加郵送費の扱い</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
+          <t>第9期の在宅調査は回収率45.8%（72人中33人）。150人でも同率なら約69件で、クロス集計に耐えない可能性。</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅰ-31</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-6</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -4269,27 +4287,27 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
+          <t>集計・分析で村が最も確認したい事項（クロス集計の設計）</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
+          <t>資料5の論点表から落とす。地区別（北山・大塩・桧原・裏磐梯）は第9期報告書が全設問で実施しており踏襲が前提だが、多重クロスは特定リスクがあるため細分の程度を確認。</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅰ-40,Ⅰ-42</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>doc30§5-1</t>
+          <t>doc19 追-7</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -4326,22 +4344,22 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
+          <t>介護保険事業状況報告 月報 第2表・第3表（サービス種類別の受給者数）</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
+          <t>★見込量推計の停止要因。見える化にサービス種類別の受給者数の系列はないが、第1号被保険者1人あたり給付月額（D13系列）に第1号被保険者数を乗じ、受給者1人あたり給付月額（D17系列）で除せば受給者数を算出できる。通所介護で検算したところ素案の値（令和5年度37.2・令和6年度42.2・令和7年度38.9人／月）と一致した。D17系列があるのは15サービスで、居住系の認知症対応型共同生活介護・特定施設入居者生活介護を含む。★10/7：したがって停止しているのは施設サービス3種（介護老人福祉施設・介護老人保健施設・介護医療院）のみで、この3種はD17系列がないため按分した参考値のままである。確定値にするには月報 第2表・第3表の実数が要る。居住系2種は算出に切り替える（素案5-4(3)）。</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>doc38§A-2,doc18 5-4(9)</t>
+          <t>doc30§5-3</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -4351,7 +4369,7 @@
       </c>
       <c r="H70" s="4" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="I70" s="4" t="inlineStr"/>
@@ -4373,27 +4391,27 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
+          <t>介護給付と予防給付を分けたサービス種類別の受給者数・給付費</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
+          <t>★計画の様式は介護給付と予防給付を分けて記載する。見える化は両者を合算した値のみ。要支援1・2の在宅受給者は48.3人／月で在宅全体の43%を占めるため、分離しないと予防給付の見込量が立てられない。</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>doc30§4-2,doc18 5-4</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -4425,32 +4443,32 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問4(15)(16)（社会的役割）を削除するかどうか</t>
+          <t>特定福祉用具販売・住宅改修の件数（令和5〜7年度）</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>★★印刷前に要決定。国の手引きは問4(13)〜(16)の4項目すべてが「いいえ」で「社会的役割の低下」と判定する。(16)は削除済み、(15)は0909校正で削除の指示。2項目が欠けるとR09が算出できず、見える化への登録も全国・県との比較も不可。R99が10領域→9領域に減るため第9期調査との比較も成立しない。左余白の「見える化関係」の書き込みは(10)〜(14)を指すとみられるが(15)(16)も登録対象である。</t>
+          <t>計画の様式は「件／年」で記載する。見える化は給付費のみで件数の系列がない。</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-15,Ⅰ-102</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>doc34§1-1</t>
+          <t>doc30§5-1</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H72" s="4" t="inlineStr">
@@ -4482,32 +4500,32 @@
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>★返信用封筒の差出有効期間の延長</t>
+          <t>居宅介護支援・介護予防支援の受給者数（居宅と予防の内訳）</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>★★印刷前に要対応。版下は「差出有効期間 2026年10月16日まで」で回収期限（10月16日）と同日。期限翌日以降に投函された回答は料金受取人払が効かず届かない。通常は回収期限＋2週間程度。回収率に直結する。</t>
+          <t>★9/24：合計人数は見える化の2系列から逆算して解決した（D13-r×B1÷D17-l）。令和3〜7年度の逆算値86.7／91.3／98.0／112.0／111.1人は在宅サービス受給者数と0.1人以内で一致する。残るのは居宅介護支援と介護予防支援の内訳のみ。見える化では分けられない。</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-23,Ⅰ-102</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>doc34§1-2</t>
+          <t>doc38§A-2,doc18 5-4(9)</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H73" s="4" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>一部回答</t>
         </is>
       </c>
       <c r="I73" s="4" t="inlineStr"/>
@@ -4529,32 +4547,32 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>★調査票の印刷前修正5件（p2投函期限の空欄・問7-1の「問6」・問10の記号K L・A票問15の分岐・URLとQRコード）</t>
+          <t>認知症対応型共同生活介護の定員（27人）を超える需要への対応方針</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>★いずれも0909校正版で残っている。問7-1の参照先の誤りは分析編の中核クロス（X-15）に、A票問15の分岐はB票の回答対象者の確定に関わる。</t>
+          <t>★令和7年度の居住系受給者は26.9人／月で、村内GHの定員27人に対する稼働率は93%。第10期に居住系の利用が増える見込みだが村内に受け皿の余地がない。施設整備の意向、村外施設での対応、在宅での対応のいずれを取るかで見込量と施策の両方が変わる。</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-15,Ⅰ-102</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>doc34§1</t>
+          <t>doc30§4-2,doc18 5-4</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H74" s="4" t="inlineStr">
@@ -4581,32 +4599,32 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
+          <t>★ニーズ調査 問4(15)(16)（社会的役割）を削除するかどうか</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>★国勢調査を住まいの種類の代替として用いてよいかをご確認いただき、あわせて村営住宅の高齢者の入居の実績をご提供いただきたい。★10/20 当方の先行：総務省統計局のサイトに接続できるようになったため、代替になる公表資料を当方で当たった。ア 住宅・土地統計調査は使えない。同調査の結果表章は「市区及び人口1万5千人以上の町村」に限られる（令和5年調査の結果の概要の注記。人口は令和2年国勢調査時点）。本村の人口は2,315人であり、対象外である。イ 国勢調査であれば市町村単位で得られる。令和2年国勢調査の「65歳以上世帯員に係る世帯の状態」に、表31-8「65歳以上世帯員の有無による世帯の類型，住宅の所有の関係，住宅の建て方・世帯が住んでいる階別一般世帯の1世帯当たり人員－全国，都道府県，市区町村」があり、同じ分類に表29-6・29-7・30-4がある。また「住宅の所有関係・住宅の建て方」の表18-7、「世帯の家族類型，住宅の所有の関係別一般世帯数」の表22-3・22-4も市区町村単位である。ウ したがって、公営住宅・借家に住む高齢者の把握は国勢調査で代えられる。ただし国勢調査は住宅の所有の関係であって、公営住宅に限った数ではない。公営住宅の高齢者の入居の実績は村の住宅施策の資料でなければ分からない。エ お尋ねするのは次の2点に絞られる。①国勢調査（令和2年。令和7年調査の結果が出れば差し替える）を代替として用いてよいか。②村営住宅の高齢者の入居の実績（戸数・世帯数）があればご提供いただきたい。基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
+          <t>★★印刷前に要決定。国の手引きは問4(13)〜(16)の4項目すべてが「いいえ」で「社会的役割の低下」と判定する。(16)は削除済み、(15)は0909校正で削除の指示。2項目が欠けるとR09が算出できず、見える化への登録も全国・県との比較も不可。R99が10領域→9領域に減るため第9期調査との比較も成立しない。左余白の「見える化関係」の書き込みは(10)〜(14)を指すとみられるが(15)(16)も登録対象である。</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅰ-15,Ⅰ-102</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>doc34§3-3</t>
+          <t>doc34§1-1</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H75" s="4" t="inlineStr">
@@ -4618,12 +4636,12 @@
       <c r="J75" s="4" t="inlineStr"/>
       <c r="K75" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
-          <t>住宅・土地統計調査等の公表資料で当方が代替を探す。得られない場合のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -4633,32 +4651,32 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
+          <t>★返信用封筒の差出有効期間の延長</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。★10/15 全国介護保険担当課長会議資料（令和8年7月15日）により、基準の見方が分かった。「75歳以上人口密度」「75歳以上人口」は足下のデータ（例：2025年）、「75歳以上人口変化率」は直近3年間の変化率（例：2022年→2025年）による。素案1-8の4は増減を将来推計（令和12年まで増加）で見ていたため、直近3年間の見方に直した。本村の75歳以上人口は社人研推計で2020年441人→2025年480人と増えており、直近3年間でも減少していないため、結論（密度要件による該当）は変わらない。ただし国の基準は住民基本台帳等の足下のデータで見るものと思われるため、令和4年と令和7年の75歳以上人口（住民基本台帳）の実績値をご教示いただきたい。あわせて対象の③は「特定のサービス類型の事業所が地域に存在しない、事業所が僅少かつ当該事業所が廃止を検討しているなど、現に指定サービス等を前提としたサービス基盤の維持が困難である地域」であり、村内で提供されているサービスが3種類にとどまる本村はこれにも当たる見込みである。同資料は、中山間・人口減少地域の実情に応じたサービス提供体制の在り方の方向性を第10期計画に記載することを求めている。県（市町村で該当し得る地域を選定する立場）に、本村を対象として選定する見込みの有無をご確認いただきたい。</t>
+          <t>★★印刷前に要対応。版下は「差出有効期間 2026年10月16日まで」で回収期限（10月16日）と同日。期限翌日以降に投函された回答は料金受取人払が効かず届かない。通常は回収期限＋2週間程度。回収率に直結する。</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅰ-23,Ⅰ-102</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>doc33§3-5</t>
+          <t>doc34§1-2</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H76" s="4" t="inlineStr">
@@ -4666,14 +4684,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I76" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+      <c r="I76" s="4" t="inlineStr"/>
+      <c r="J76" s="4" t="inlineStr"/>
       <c r="K76" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -4691,32 +4703,32 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
+          <t>★調査票の印刷前修正5件（p2投函期限の空欄・問7-1の「問6」・問10の記号K L・A票問15の分岐・URLとQRコード）</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
+          <t>★いずれも0909校正版で残っている。問7-1の参照先の誤りは分析編の中核クロス（X-15）に、A票問15の分岐はB票の回答対象者の確定に関わる。</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅰ-15,Ⅰ-102</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>doc32§5-1</t>
+          <t>doc34§1</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H77" s="4" t="inlineStr">
@@ -4748,12 +4760,12 @@
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
+          <t>ニーズ調査 問1(4)（住まいの種類）を削除したままとする場合の代替資料</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
+          <t>★国勢調査を住まいの種類の代替として用いてよいかをご確認いただき、あわせて村営住宅の高齢者の入居の実績をご提供いただきたい。★10/20 当方の先行：総務省統計局のサイトに接続できるようになったため、代替になる公表資料を当方で当たった。ア 住宅・土地統計調査は使えない。同調査の結果表章は「市区及び人口1万5千人以上の町村」に限られる（令和5年調査の結果の概要の注記。人口は令和2年国勢調査時点）。本村の人口は2,315人であり、対象外である。イ 国勢調査であれば市町村単位で得られる。令和2年国勢調査の「65歳以上世帯員に係る世帯の状態」に、表31-8「65歳以上世帯員の有無による世帯の類型，住宅の所有の関係，住宅の建て方・世帯が住んでいる階別一般世帯の1世帯当たり人員－全国，都道府県，市区町村」があり、同じ分類に表29-6・29-7・30-4がある。また「住宅の所有関係・住宅の建て方」の表18-7、「世帯の家族類型，住宅の所有の関係別一般世帯数」の表22-3・22-4も市区町村単位である。ウ したがって、公営住宅・借家に住む高齢者の把握は国勢調査で代えられる。ただし国勢調査は住宅の所有の関係であって、公営住宅に限った数ではない。公営住宅の高齢者の入居の実績は村の住宅施策の資料でなければ分からない。エ お尋ねするのは次の2点に絞られる。①国勢調査（令和2年。令和7年調査の結果が出れば差し替える）を代替として用いてよいか。②村営住宅の高齢者の入居の実績（戸数・世帯数）があればご提供いただきたい。基本指針が求める「高齢者の居住安定に係る施策との連携」と施策2-3の根拠になる唯一の設問だった。公営住宅・借家の高齢者を把握する手段がなくなるため、村の住宅施策の資料で補う。</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
@@ -4763,7 +4775,7 @@
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>doc32§4-1</t>
+          <t>doc34§3-3</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -4780,12 +4792,12 @@
       <c r="J78" s="4" t="inlineStr"/>
       <c r="K78" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L78" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>住宅・土地統計調査等の公表資料で当方が代替を探す。得られない場合のみ伺う</t>
         </is>
       </c>
     </row>
@@ -4795,32 +4807,32 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
+          <t>中山間・人口減少地域（特定地域）の指定を受ける意向</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
+          <t>★令和8年法律第51号により令和9年4月1日創設。本村は75歳以上人口526人・密度5人/km²未満で指定基準②に該当する見込み（面積が105.2km²を超えれば該当し、本村はこれを大きく上回る）。特定地域サービスと特定地域居宅サービス等事業は、28サービスのうち12種類に実績がない本村への対応手段になる。指定は村の意向を踏まえ都道府県が定めるため計画への記載が起点。★10/15 全国介護保険担当課長会議資料（令和8年7月15日）により、基準の見方が分かった。「75歳以上人口密度」「75歳以上人口」は足下のデータ（例：2025年）、「75歳以上人口変化率」は直近3年間の変化率（例：2022年→2025年）による。素案1-8の4は増減を将来推計（令和12年まで増加）で見ていたため、直近3年間の見方に直した。本村の75歳以上人口は社人研推計で2020年441人→2025年480人と増えており、直近3年間でも減少していないため、結論（密度要件による該当）は変わらない。ただし国の基準は住民基本台帳等の足下のデータで見るものと思われるため、令和4年と令和7年の75歳以上人口（住民基本台帳）の実績値をご教示いただきたい。あわせて対象の③は「特定のサービス類型の事業所が地域に存在しない、事業所が僅少かつ当該事業所が廃止を検討しているなど、現に指定サービス等を前提としたサービス基盤の維持が困難である地域」であり、村内で提供されているサービスが3種類にとどまる本村はこれにも当たる見込みである。同資料は、中山間・人口減少地域の実情に応じたサービス提供体制の在り方の方向性を第10期計画に記載することを求めている。県（市町村で該当し得る地域を選定する立場）に、本村を対象として選定する見込みの有無をご確認いただきたい。</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>doc32§5-2</t>
+          <t>doc33§3-5</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H79" s="4" t="inlineStr">
@@ -4828,16 +4840,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I79" s="4" t="inlineStr"/>
-      <c r="J79" s="4" t="inlineStr"/>
+      <c r="I79" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K79" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
-          <t>介護サービス情報公表システムで当方が拾う。村内事業所の最新の状況のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -4847,32 +4865,32 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
+          <t>高齢者虐待への対応実績（相談・通報件数、虐待と判断した件数、措置件数）</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>策定委員会の委員に認知症の本人・家族が含まれるかをご確認いただき、含まれない場合は家族会・認知症カフェ等での意見聴取の機会を設けるかどうかをお決めいただきたい。認知症基本法第13条は市町村計画の策定にあたり認知症の人および家族等の意見を聴くことを求めている（努力義務）。記述の追加では埋まらず策定過程そのものに関わるため、第2回策定委員会（11月）までに方針を決める必要がある。機会を設ける場合は日程の確保が要るため、早めのご判断をお願いしたい。★当方の扱い：ご回答がない場合、策定委員会とパブリックコメント、アンケート調査により意見を聴取した旨のみを記載し、認知症の人および家族等の意見を聴いた旨は書かない。</t>
+          <t>★国の基本指針が権利擁護として記載を求める事項。素案には「虐待」の語が1度もなかった（doc32 §5-1）。地域包括支援センターの権利擁護業務の中核でもある。</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-57</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>doc32§7</t>
+          <t>doc32§5-1</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H80" s="4" t="inlineStr">
@@ -4880,14 +4898,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I80" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>工程外</t>
-        </is>
-      </c>
+      <c r="I80" s="4" t="inlineStr"/>
+      <c r="J80" s="4" t="inlineStr"/>
       <c r="K80" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -4910,22 +4922,22 @@
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
+          <t>老人福祉事業の量の実績（養護老人ホーム措置・軽費老人ホーム・老人クラブ）</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
+          <t>★老人福祉法第20条の8第2項が「定めるものとする」とする義務的記載事項。素案に量の目標の表がなかったため4-6を新設したが、実績値がないと目標が置けない。</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§4-1</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -4962,22 +4974,22 @@
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
+          <t>介護サービス事業所のBCP・要配慮者利用施設の避難確保計画の策定状況</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
+          <t>★基本指針が求める災害・感染症対策の体制整備。村内2事業所（GH・通所介護）が対象になり得る。</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§5-2</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -4994,12 +5006,12 @@
       <c r="J82" s="4" t="inlineStr"/>
       <c r="K82" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L82" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>介護サービス情報公表システムで当方が拾う。村内事業所の最新の状況のみ伺う</t>
         </is>
       </c>
     </row>
@@ -5009,32 +5021,32 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
+          <t>認知症の人および家族等の意見聴取の方法（認知症基本法第13条）</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
+          <t>策定委員会の委員に認知症の本人・家族が含まれるかをご確認いただき、含まれない場合は家族会・認知症カフェ等での意見聴取の機会を設けるかどうかをお決めいただきたい。認知症基本法第13条は市町村計画の策定にあたり認知症の人および家族等の意見を聴くことを求めている（努力義務）。記述の追加では埋まらず策定過程そのものに関わるため、第2回策定委員会（11月）までに方針を決める必要がある。機会を設ける場合は日程の確保が要るため、早めのご判断をお願いしたい。★当方の扱い：ご回答がない場合、策定委員会とパブリックコメント、アンケート調査により意見を聴取した旨のみを記載し、認知症の人および家族等の意見を聴いた旨は書かない。</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-53,Ⅱ-57</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-11</t>
+          <t>doc32§7</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H83" s="4" t="inlineStr">
@@ -5042,16 +5054,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
+      <c r="I83" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>工程外</t>
+        </is>
+      </c>
       <c r="K83" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
-          <t>県・国保データベースの公表値で当方が押さえる。村の最新値のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -5061,32 +5079,32 @@
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
+          <t>診療所（南東北裏磐梯・桧原）の診療日数および患者数</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。★10/23 一部解決：本計画の秘密保持契約書（令和8年8月6日付。貸与アカウントとそれを通じて得られるデータを秘密情報に含む）を受領した。残るのは障がい福祉計画の分のアカウントを継続して使ってよいかである（doc117）。</t>
+          <t>★在宅医療・介護連携の分析に直結するがこれまで把握していなかった。</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>０-06</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-12,doc117</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H84" s="4" t="inlineStr">
@@ -5094,14 +5112,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I84" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>工程外</t>
-        </is>
-      </c>
+      <c r="I84" s="4" t="inlineStr"/>
+      <c r="J84" s="4" t="inlineStr"/>
       <c r="K84" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -5119,27 +5131,27 @@
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
+          <t>家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
+          <t>任意事業・認知症施策・成年後見の評価に必要。令和6年度実績、可能であれば令和7年度。</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-13</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -5156,12 +5168,12 @@
       <c r="J85" s="4" t="inlineStr"/>
       <c r="K85" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L85" s="4" t="inlineStr">
         <is>
-          <t>関連計画の一覧は当方が公表資料から組む（資9）。未公表の計画のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -5171,27 +5183,27 @@
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
+          <t>特定健診・後期高齢者健診の受診率、特定保健指導の実施率</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。★10/7 前提が確定：国の推計ワークシートは残高42,128,183円のうち40,000,000円（94.9%）を取り崩す前提で保険料5,513.72円としている。これが実質の全額取崩案に当たる。取崩を減らすと第10期は上がるが第11期の＋32.4%は和らぐ。比較案は「国ツールどおり（40,000千円）」「第9期同程度（24,000千円）」「取崩なし」の3案で組む案を当方から示す。</t>
+          <t>介護予防と保健事業の一体的実施（施策1-6）の評価に必要。</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-63,Ⅱ-64</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>doc19 追-14,doc66§2-3</t>
+          <t>doc19 追-11</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5201,19 +5213,19 @@
       </c>
       <c r="H86" s="4" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="I86" s="4" t="inlineStr"/>
       <c r="J86" s="4" t="inlineStr"/>
       <c r="K86" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L86" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>県・国保データベースの公表値で当方が押さえる。村の最新値のみ伺う</t>
         </is>
       </c>
     </row>
@@ -5223,32 +5235,32 @@
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
+          <t>★見える化システムのアカウント（障がい福祉計画分の継続利用可否）と秘密保持契約の要否</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
+          <t>★すでに19,591レコードを受領して分析に着手している。遡って手続きが必要な場合はその整理も要する。★10/23 一部解決：本計画の秘密保持契約書（令和8年8月6日付。貸与アカウントとそれを通じて得られるデータを秘密情報に含む）を受領した。残るのは障がい福祉計画の分のアカウントを継続して使ってよいかである（doc117）。</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-67,Ⅱ-75</t>
+          <t>０-06</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>doc19 §3</t>
+          <t>doc19 追-12,doc117</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H87" s="4" t="inlineStr">
@@ -5256,8 +5268,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I87" s="4" t="inlineStr"/>
-      <c r="J87" s="4" t="inlineStr"/>
+      <c r="I87" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>工程外</t>
+        </is>
+      </c>
       <c r="K87" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -5275,32 +5293,32 @@
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
+          <t>整合を図る関連計画の網羅（障がい福祉計画・障がい者計画・地域福祉計画等）</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
+          <t>資料には基本指針・第5次総合振興計画・第3次健康21のみ記載。</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61</t>
+          <t>doc19 追-13</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H88" s="4" t="inlineStr">
@@ -5308,22 +5326,16 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I88" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I88" s="4" t="inlineStr"/>
+      <c r="J88" s="4" t="inlineStr"/>
       <c r="K88" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L88" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>関連計画の一覧は当方が公表資料から組む（資9）。未公表の計画のみ伺う</t>
         </is>
       </c>
     </row>
@@ -5333,47 +5345,41 @@
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
+          <t>上限保険料の設定の有無と基金活用の比較案のパターン</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
+          <t>第9期は基金24,000,000円の取崩を計画。全額取崩案／据置優先案／中間案など何案を示すかを確認。★10/7 前提が確定：国の推計ワークシートは残高42,128,183円のうち40,000,000円（94.9%）を取り崩す前提で保険料5,513.72円としている。これが実質の全額取崩案に当たる。取崩を減らすと第10期は上がるが第11期の＋32.4%は和らぐ。比較案は「国ツールどおり（40,000千円）」「第9期同程度（24,000千円）」「取崩なし」の3案で組む案を当方から示す。</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-63,Ⅱ-64</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>doc20§8-2 K-61b</t>
+          <t>doc19 追-14,doc66§2-3</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H89" s="4" t="inlineStr">
         <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="I89" s="4" t="inlineStr"/>
+      <c r="J89" s="4" t="inlineStr"/>
       <c r="K89" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -5391,32 +5397,32 @@
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
+          <t>施設整備の方向性（在宅調査48.5%の入所希望の扱い）</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
+          <t>★48.5%は回収33件中16人。標本が小さいため単独の根拠とせず、村内施設ゼロ・短期入所+165%・認定率18位/費用額44位と併せて示し、今回の在宅調査150人で再確認する位置づけを提案。</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-67,Ⅱ-75</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-62</t>
+          <t>doc19 §3</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H90" s="4" t="inlineStr">
@@ -5424,14 +5430,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I90" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I90" s="4" t="inlineStr"/>
+      <c r="J90" s="4" t="inlineStr"/>
       <c r="K90" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -5454,22 +5454,22 @@
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
+          <t>★給付費適正化「主要3事業の全て実施」が令和7年度6点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
+          <t>★全国該当率96.9%の指標。縦覧点検は4帳票満点のため、①要介護認定の適正化 か ②ケアプラン等の点検 のいずれかが実施されなくなった可能性。取組の後退か調査票の記載漏れかで対応が変わる。</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-63</t>
+          <t>doc20§8-2 K-61</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -5512,22 +5512,22 @@
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
+          <t>★福祉用具購入費・住宅改修費へのリハビリ専門職の関与（配点8点）が令和7年度8点→令和8年度0点に低下した理由</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>★10/20 当方の先行：第8次福島県医療計画を読み、県側の体制を確かめた（data/原典_県計画）。ア 県計画の数値目標C102は「在宅医療・介護連携推進事業を実施する市町村数」を令和4年の54市町村から令和8年に59市町村（県内の全市町村）とするものである。実施の主体は市町村であり、県は「市町村が主体となって行う在宅医療・介護連携の取組を支援する」としている。したがって本村が実施主体であること自体は県計画から確かめられる。イ 在宅医療に関する圏域は7圏域で、本村は「会津」圏域に属する（二次医療圏の「会津・南会津」とは区切りが違う）。ウ 在宅療養支援病院・診療所が所在しない市町村への広域的な支援は、各地域の協議会や部会で議論する体制とされている。本村はこれに当たる。エ 県は福島県在宅医療・介護連携支援センターを設置し、各地域の在宅医療・介護連携支援センターへの連携支援と、設置を検討している市町村への開設に向けた総合的な支援を行うとしている。オ 残るお尋ねは、本村が村単独で実施しているのか会津圏域の枠組みに乗っているのか、課題・対応策の検討の場をどこに置いているのか（会津の協議会・部会に参加しているか）の2点である。県の体制は分かったが、本村がそのどこに位置しているかは村でなければ分からない。支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
+          <t>★アと合わせ14点が1年で失われている。仕組みが失われたのか調査票の記載によるものかを確認。</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-64</t>
+          <t>doc20§8-2 K-61b</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="K92" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L92" s="4" t="inlineStr">
         <is>
-          <t>会津圏域の在宅医療・介護連携の体制は公表されている。村の関与のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -5570,27 +5570,27 @@
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
+          <t>認知症サポーター養成数・認知症地域支援推進員の配置と活動内容・チームオレンジの整備予定</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
+          <t>★支援交付金目標Ⅱ（認知症総合支援）は32/100点で全国平均51.1点を19点下回る唯一の目標。3か年で唯一低下局面があった。</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-65</t>
+          <t>doc20§6-2 K-62</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H93" s="4" t="inlineStr">
@@ -5598,8 +5598,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I93" s="4" t="inlineStr"/>
-      <c r="J93" s="4" t="inlineStr"/>
+      <c r="I93" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K93" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -5617,27 +5623,27 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
+          <t>難聴高齢者の早期発見・早期介入の取組（健診での聴力チェック等）の有無</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
+          <t>令和8年度評価で配点10点が0点（全国該当率48.8〜68.9%）。保健事業との連携で取得可能。</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-66</t>
+          <t>doc20§6-2 K-63</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
@@ -5675,32 +5681,32 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
+          <t>在宅医療・介護連携推進事業の実施体制（村単独か会津圏域か）と課題・対応策の検討の場</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
+          <t>★10/20 当方の先行：第8次福島県医療計画を読み、県側の体制を確かめた（data/原典_県計画）。ア 県計画の数値目標C102は「在宅医療・介護連携推進事業を実施する市町村数」を令和4年の54市町村から令和8年に59市町村（県内の全市町村）とするものである。実施の主体は市町村であり、県は「市町村が主体となって行う在宅医療・介護連携の取組を支援する」としている。したがって本村が実施主体であること自体は県計画から確かめられる。イ 在宅医療に関する圏域は7圏域で、本村は「会津」圏域に属する（二次医療圏の「会津・南会津」とは区切りが違う）。ウ 在宅療養支援病院・診療所が所在しない市町村への広域的な支援は、各地域の協議会や部会で議論する体制とされている。本村はこれに当たる。エ 県は福島県在宅医療・介護連携支援センターを設置し、各地域の在宅医療・介護連携支援センターへの連携支援と、設置を検討している市町村への開設に向けた総合的な支援を行うとしている。オ 残るお尋ねは、本村が村単独で実施しているのか会津圏域の枠組みに乗っているのか、課題・対応策の検討の場をどこに置いているのか（会津の協議会・部会に参加しているか）の2点である。県の体制は分かったが、本村がそのどこに位置しているかは村でなければ分からない。支援交付金目標Ⅲの「課題・対応策の検討」ア・エが0点（配点計10点、全国該当率57〜72%）。</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>doc20§6-2 K-67</t>
+          <t>doc20§6-2 K-64</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H95" s="4" t="inlineStr">
@@ -5708,16 +5714,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I95" s="4" t="inlineStr"/>
-      <c r="J95" s="4" t="inlineStr"/>
+      <c r="I95" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K95" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L95" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>会津圏域の在宅医療・介護連携の体制は公表されている。村の関与のみ伺う</t>
         </is>
       </c>
     </row>
@@ -5732,22 +5744,22 @@
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
+          <t>ACP（人生会議）の普及啓発・看取りに関する住民向け取組の有無</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
+          <t>支援交付金目標Ⅲ「人生の最終段階における支援」4項目が0点（配点計8点）。</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>doc21§5 K-68</t>
+          <t>doc20§6-2 K-65</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -5764,12 +5776,12 @@
       <c r="J96" s="4" t="inlineStr"/>
       <c r="K96" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L96" s="4" t="inlineStr">
         <is>
-          <t>生涯学習推進計画は公表されている。中間評価の有無のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -5779,27 +5791,27 @@
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
+          <t>目標Ⅳ（成果指標群）が令和8年度に25点低下した要因の心当たり</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
+          <t>★成果指標群は村の申告でなくKDB等の統計から自動算定。65→70→45点と低下し、両交付金で計50点の減。要介護度の維持・改善の実績悪化を示唆。</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>doc21§5 K-69</t>
+          <t>doc20§6-2 K-66</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
@@ -5837,32 +5849,32 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
+          <t>令和9年度以降も交付金の該当状況調査票の写しを策定業務に提供いただけるか</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。★10/10：同じ問いが優先度Bでも起票されていたため本項目に集約した。資9（関連計画との対照）に第五次総合振興計画の行を置き、計画期間が令和8年度で満了するため第六次の策定状況を確認して記述を確定する旨を書いている。</t>
+          <t>第10期の進捗管理で毎年度の得点推移を追うために必要。</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>doc21§5 K-70,doc08§8-4</t>
+          <t>doc20§6-2 K-67</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H98" s="4" t="inlineStr">
@@ -5870,14 +5882,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I98" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I98" s="4" t="inlineStr"/>
+      <c r="J98" s="4" t="inlineStr"/>
       <c r="K98" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -5900,22 +5906,22 @@
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
+          <t>第四次生涯学習推進計画の目標値の直近実績（中間評価の有無・結果）</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
+          <t>10年計画（2018〜2027年度）の中間年は2022年度。第10期計画に引用可能か。</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>doc21§5 K-71</t>
+          <t>doc21§5 K-68</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
@@ -5932,12 +5938,12 @@
       <c r="J99" s="4" t="inlineStr"/>
       <c r="K99" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L99" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>生涯学習推進計画は公表されている。中間評価の有無のみ伺う</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5953,32 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>シルバー人材センターの会員数・受注実績</t>
+          <t>第五次生涯学習推進計画（2028年度〜）の策定予定時期</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
+          <t>★第四次は令和9年度で満了。第10期計画期間（令和9〜11年度）の途中で関連計画が切り替わるため記述の書き分けが必要。</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>doc21§5 K-72</t>
+          <t>doc21§5 K-69</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H100" s="4" t="inlineStr">
@@ -5980,16 +5986,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I100" s="4" t="inlineStr"/>
-      <c r="J100" s="4" t="inlineStr"/>
+      <c r="I100" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K100" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L100" s="4" t="inlineStr">
         <is>
-          <t>シルバー人材センターの事業報告で当方が拾う。拾えない年度のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -5999,32 +6011,32 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
+          <t>第六次総合振興計画（2027年度〜）の策定状況</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
+          <t>★第五次は令和8年度で満了。第10期計画の上位計画の記述に必要（doc08§8-4と共通）。★10/10：同じ問いが優先度Bでも起票されていたため本項目に集約した。資9（関連計画との対照）に第五次総合振興計画の行を置き、計画期間が令和8年度で満了するため第六次の策定状況を確認して記述を確定する旨を書いている。</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>doc21§5 K-73</t>
+          <t>doc21§5 K-70,doc08§8-4</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H101" s="4" t="inlineStr">
@@ -6032,8 +6044,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I101" s="4" t="inlineStr"/>
-      <c r="J101" s="4" t="inlineStr"/>
+      <c r="I101" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J101" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K101" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -6056,27 +6074,27 @@
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
+          <t>高齢者生きがい健康づくり事業・高齢者教室の実施状況（開催回数・参加人数）</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
+          <t>教育委員会所管。介護予防（通いの場）の実績にカウントできるものがあるかを確認。</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-55</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>doc22 K-75</t>
+          <t>doc21§5 K-71</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H102" s="4" t="inlineStr">
@@ -6084,14 +6102,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I102" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I102" s="4" t="inlineStr"/>
+      <c r="J102" s="4" t="inlineStr"/>
       <c r="K102" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -6109,32 +6121,32 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>★策定委員会 現委員の任期満了（令和8年9月30日）と改選手続きの所要期間</t>
+          <t>シルバー人材センターの会員数・受注実績</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>★議事録で触れられていない。第2回を11月に開催するには10月中の改選・委嘱が必要。</t>
+          <t>高齢者の就労的活動の実績として記載可能か。生涯学習推進計画にも施策として位置づけあり。</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-80</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>doc22 K-76</t>
+          <t>doc21§5 K-72</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H103" s="4" t="inlineStr">
@@ -6142,22 +6154,16 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I103" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>工程外</t>
-        </is>
-      </c>
+      <c r="I103" s="4" t="inlineStr"/>
+      <c r="J103" s="4" t="inlineStr"/>
       <c r="K103" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L103" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>シルバー人材センターの事業報告で当方が拾う。拾えない年度のみ伺う</t>
         </is>
       </c>
     </row>
@@ -6167,32 +6173,32 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>★ICFを用いたクロス分析の具体的な期待像（軸・アウトプットのイメージ）</t>
+          <t>「地域で見守り・育む高齢者の支援」（生涯学習推進計画の施策）と生活支援体制整備事業の役割分担</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>★議事録の新規要件。「元気な高齢者」×「地域のニーズ」で共助・互助の必要性を示す分析。調査票の設計段階でクロス軸を確保しないと後から分析できない。9/3の第1稿に影響。</t>
+          <t>★両計画で同一施策が重複。所管（教育委員会／住民課／社協）を明記して連携を書く必要がある。</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-95</t>
+          <t>Ⅱ-53</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>doc22 K-77</t>
+          <t>doc21§5 K-73</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H104" s="4" t="inlineStr">
@@ -6200,14 +6206,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I104" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J104" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+      <c r="I104" s="4" t="inlineStr"/>
+      <c r="J104" s="4" t="inlineStr"/>
       <c r="K104" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -6225,27 +6225,27 @@
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
+          <t>★施設サービスが伸びない要因「重度化による病院への転院」の裏づけデータ</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
+          <t>★議事録で示された村の見解。当方は村内施設ゼロ・村外施設依存の文脈で解釈していたため、素案の記述を修正する必要がある。KDB・給付実績で確認したい。</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-94</t>
+          <t>Ⅱ-55</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>doc22 K-78</t>
+          <t>doc22 K-75</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -6283,32 +6283,32 @@
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
+          <t>★策定委員会 現委員の任期満了（令和8年9月30日）と改選手続きの所要期間</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。★10/10：同じ問いを3件に分けて起票していたため本項目に集約した（「概要版の要否」優先度Cと「概要版の位置づけ」優先度Bを取り消した）。★10/10：骨子を作った（doc82）。第9期概要版の構成（表面＝基本的な考え方・基本理念・基本目標・数値、裏面＝施策体系図）を踏襲し、A3両面に25の要素を割り付けた。要素ごとに素案のどの節・どの図から引くかを決めており、面積の積み上げでは表面73パーセント・裏面76パーセントで収まる見込みである。★骨子の段階で村のご判断を要するのは次の5点である。・仕様の範囲内か追加対応か（本項目の本来の問い）。・基本理念を第9期から継承するか（素案3-1も村との協議事項としている）。・配布の範囲と部数。議会全員協議会で用いる想定だが、村民への配布を行うかが未定である。・所管課と問い合わせ先の表記。氏名・直通番号は載せない（doc16 §5-3）。・施策体系図を概要版のために横長に作り直すか。計画書の図3-1はA4に合わせた縦長であり、A3の幅を活かせない。縦長のまま幅を広げると裏面の高さの74パーセントを占めて他が入らないため、骨子では幅125mmに縮めている。★作成の時期について。概要版には保険料の基準額を載せるため、基金の取崩しの3案のうちいずれを採るかが決まってからでないと作れない。議会全員協議会（令和9年2月末頃）の時点では条例案が定まっている必要がある。第3回策定委員会（令和9年1月下旬〜2月上旬）のご決定を受けて作成する工程となる。★当方の扱い：ご回答がない場合も骨子は固めておき、保険料の欄を枠のまま残す。</t>
+          <t>★議事録で触れられていない。第2回を11月に開催するには10月中の改選・委嘱が必要。</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Ⅳ-92</t>
+          <t>Ⅱ-80</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>doc22 K-79,doc82</t>
+          <t>doc22 K-76</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H106" s="4" t="inlineStr">
@@ -6326,12 +6326,12 @@
       </c>
       <c r="K106" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L106" s="4" t="inlineStr">
         <is>
-          <t>仕様書は受領済みであり、範囲は当方が読む。追加対応の扱いのみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -6341,32 +6341,32 @@
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
+          <t>★ICFを用いたクロス分析の具体的な期待像（軸・アウトプットのイメージ）</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
+          <t>★議事録の新規要件。「元気な高齢者」×「地域のニーズ」で共助・互助の必要性を示す分析。調査票の設計段階でクロス軸を確保しないと後から分析できない。9/3の第1稿に影響。</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-93</t>
+          <t>Ⅰ-95</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>doc22 K-80</t>
+          <t>doc22 K-77</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H107" s="4" t="inlineStr">
@@ -6374,8 +6374,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I107" s="4" t="inlineStr"/>
-      <c r="J107" s="4" t="inlineStr"/>
+      <c r="I107" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K107" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -6393,27 +6399,27 @@
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
+          <t>★調査票の受渡し記録の様式（村が100件程度ごとに随時送付する運用に対応）</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
+          <t>★個人情報を含む調査票の授受が複数回に分かれるため、日付・数量・受渡者・受領者の記録が必要。doc16に追記する。</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅰ-94</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>doc22 K-81</t>
+          <t>doc22 K-78</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -6427,21 +6433,21 @@
         </is>
       </c>
       <c r="I108" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J108" s="4" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>記載待ち</t>
         </is>
       </c>
       <c r="K108" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L108" s="4" t="inlineStr">
         <is>
-          <t>改定率の告示は当方が追う。補正の時期と成果品への反映の方法のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -6451,32 +6457,32 @@
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
+          <t>★概要版（A3両面程度）が仕様の範囲内か追加対応か</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
+          <t>★議事録で作成が合意（理念・体系図・推移データ）。第9期はA4 2ページ。仕様書に記載がなく成果品一覧にもない。★10/10：同じ問いを3件に分けて起票していたため本項目に集約した（「概要版の要否」優先度Cと「概要版の位置づけ」優先度Bを取り消した）。★10/10：骨子を作った（doc82）。第9期概要版の構成（表面＝基本的な考え方・基本理念・基本目標・数値、裏面＝施策体系図）を踏襲し、A3両面に25の要素を割り付けた。要素ごとに素案のどの節・どの図から引くかを決めており、面積の積み上げでは表面73パーセント・裏面76パーセントで収まる見込みである。★骨子の段階で村のご判断を要するのは次の5点である。・仕様の範囲内か追加対応か（本項目の本来の問い）。・基本理念を第9期から継承するか（素案3-1も村との協議事項としている）。・配布の範囲と部数。議会全員協議会で用いる想定だが、村民への配布を行うかが未定である。・所管課と問い合わせ先の表記。氏名・直通番号は載せない（doc16 §5-3）。・施策体系図を概要版のために横長に作り直すか。計画書の図3-1はA4に合わせた縦長であり、A3の幅を活かせない。縦長のまま幅を広げると裏面の高さの74パーセントを占めて他が入らないため、骨子では幅125mmに縮めている。★作成の時期について。概要版には保険料の基準額を載せるため、基金の取崩しの3案のうちいずれを採るかが決まってからでないと作れない。議会全員協議会（令和9年2月末頃）の時点では条例案が定まっている必要がある。第3回策定委員会（令和9年1月下旬〜2月上旬）のご決定を受けて作成する工程となる。★当方の扱い：ご回答がない場合も骨子は固めておき、保険料の欄を枠のまま残す。</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅳ-92</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>doc23§1-2</t>
+          <t>doc22 K-79,doc82</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H109" s="4" t="inlineStr">
@@ -6484,16 +6490,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I109" s="4" t="inlineStr"/>
-      <c r="J109" s="4" t="inlineStr"/>
+      <c r="I109" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J109" s="4" t="inlineStr">
+        <is>
+          <t>工程外</t>
+        </is>
+      </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L109" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>仕様書は受領済みであり、範囲は当方が読む。追加対応の扱いのみ伺う</t>
         </is>
       </c>
     </row>
@@ -6503,32 +6515,32 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
+          <t>★議会全員協議会（令和9年2月末頃）で受託者に求められる関与の範囲</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
+          <t>★議事録で新設されたマイルストーン。資料作成のみか、出席・説明を含むかで工数が変わる。</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-12,Ⅰ-13</t>
+          <t>Ⅱ-93</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>doc23§4</t>
+          <t>doc22 K-80</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H110" s="4" t="inlineStr">
@@ -6555,32 +6567,32 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>★現職の村長名・所管課・役場の住所の確認</t>
+          <t>★令和9年度介護報酬改定への対応（現行単価で試算し単価確定後に補正する方針の、補正時期と成果品への反映方法）</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>★第1稿の依頼状に村長名・所管課（保健福祉課 福祉係）・役場の所在地を記載している。現職の村長名は当方では確認できないため、記載のまま送付してよいかをご確認いただきたい。氏名は個人情報のため本表には記載しない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
+          <t>★議事録で方針は決着。単価確定が履行期限（3/31）に近い場合の成果品の扱いを詰める必要がある。</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>doc23§5</t>
+          <t>doc22 K-81</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H111" s="4" t="inlineStr">
@@ -6588,16 +6600,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I111" s="4" t="inlineStr"/>
-      <c r="J111" s="4" t="inlineStr"/>
+      <c r="I111" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J111" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K111" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L111" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>改定率の告示は当方が追う。補正の時期と成果品への反映の方法のみ伺う</t>
         </is>
       </c>
     </row>
@@ -6612,12 +6630,12 @@
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
+          <t>★ニーズ調査 問7(7)「この1か月間に会った友人・知人の人数」の採用可否</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
+          <t>★第1稿では不採用のうえ以降の番号を繰り上げているため、見える化への入力時に設問の対応が崩れる。採用すれば番号ずれが解消し、かつICF分析の「参加」の量的指標としてそのまま使える。</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -6627,12 +6645,12 @@
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>doc23§1-3</t>
+          <t>doc23§1-2</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H112" s="4" t="inlineStr">
@@ -6659,32 +6677,32 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>分析</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
+          <t>★ニーズ調査 村独自設問14問の採否と頁数（問3(10)の削除・問7(9)の簡素化）</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
+          <t>★標準約66問＋村独自14問＝約79問。仕様書の目安A4約12頁を超える見込み。削除を提案するのは問3(10)「1日に何回食事をとりますか」の1問のみ（低栄養は問3(1)(7)(8)で把握可能）。他13問は施策・交付金の指標と結びついており残すべき。</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅰ-12,Ⅰ-13</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>doc24§12 K-86</t>
+          <t>doc23§4</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H113" s="4" t="inlineStr">
@@ -6692,22 +6710,16 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I113" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+      <c r="I113" s="4" t="inlineStr"/>
+      <c r="J113" s="4" t="inlineStr"/>
       <c r="K113" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L113" s="4" t="inlineStr">
         <is>
-          <t>第9期の調査票は受領済みであり、比較できる設問は当方が洗う。採否のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -6717,27 +6729,27 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>★ニーズ調査の対象者882人に対応する要介護認定データ（認定の有無・要介護度）</t>
+          <t>★現職の村長名・所管課・役場の住所の確認</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>★2026/09/28に受領した名簿のうち、要介護度の列があるのは在宅介護実態調査の対象者118人分のみで、ニーズ調査の対象者882人分にはない。資料3の3-3（元気な軽度者）・3-4（生活機能からみた4つの層）・3-6（担い手の可能性）は、ニーズ調査の回答者一人ひとりの認定状況を必要とするため、このままでは作成できない。資料3の3-6は第10期に共助・互助の仕組みをどの規模で構想できるかを示す表であり、合意1・2の根拠でもある。★10/10 優先度をAからSに上げた：村より「高齢者のアンケート発送は全て完了。今集計分析を行なっています」とのご連絡をいただいた。集計が動き出した以上、これが入らないと資料3の3-3・3-4・3-6が作れないまま第2回策定委員会（11月）の資料作成に入ることになる。回答データに後から認定状況を付けることはできるため、集計そのものは止まらないが、クロス集計をやり直す手戻りが生じる。できるだけ早くご提供いただきたい。</t>
+          <t>★第1稿の依頼状に村長名・所管課（保健福祉課 福祉係）・役場の所在地を記載している。現職の村長名は当方では確認できないため、記載のまま送付してよいかをご確認いただきたい。氏名は個人情報のため本表には記載しない。所管課は住民課との別が未確認のまま（doc01 確認事項1）。</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-37,Ⅰ-38</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>doc43§1</t>
+          <t>doc23§5</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -6750,14 +6762,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I114" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
-        <is>
-          <t>停止</t>
-        </is>
-      </c>
+      <c r="I114" s="4" t="inlineStr"/>
+      <c r="J114" s="4" t="inlineStr"/>
       <c r="K114" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -6775,32 +6781,32 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
         <is>
-          <t>★実際の発送日と回収状況（件数・回収率）、ウェブ回答フォームの稼働確認</t>
+          <t>ニーズ調査 問6(1)の選択肢への補足表記の可否（常勤（フルタイム）／非常勤（パート・アルバイト等））</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>★10/10 起票：村より「高齢者のアンケート発送は全て完了。今集計分析を行なっています」とのご連絡をいただいた。WBSの実績日は、議事録の発送日（令和8年9月18日）と校了日（令和8年9月9日）で置いている。次の4点をご教示いただきたい。①実際の発送日（9月18日は金曜で翌日から5連休であったため、配達が連休明けにずれ込んだ可能性がある）。②本日時点の回収件数（ニーズ調査・在宅介護実態調査それぞれ。対象は882人・118人）。回収率は督促（Ⅰ-31）の判断に用いる。③ウェブ回答フォームの稼働確認の記録の有無と、ウェブ回答の件数。二次元コードを印字して発送した以上フォームは公開されているはずだが、稼働確認の記録が当方にない（Ⅰ-101）。④これまでの受渡しの回数・日・件数。回収は村で100件程度集まるごとに随時小分け送付する運用であり（doc22）、受渡し記録簿（doc74 §4-2）にさかのぼって記録する必要がある。★回収期限は令和8年10月16日（金）である。</t>
+          <t>厳密には選択肢文言の改変にあたるが、手引きQ&amp;Aの「通称を付ける」例に近く実務上は許容される可能性が高い。回答率への影響を考えると補足を残すことを推奨。村の判断を仰ぐ。</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-29,Ⅰ-30,Ⅰ-101,Ⅰ-94</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>doc75</t>
+          <t>doc23§1-3</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H115" s="4" t="inlineStr">
@@ -6808,14 +6814,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I115" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
-        <is>
-          <t>工程外</t>
-        </is>
-      </c>
+      <c r="I115" s="4" t="inlineStr"/>
+      <c r="J115" s="4" t="inlineStr"/>
       <c r="K115" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -6833,32 +6833,32 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>疑義</t>
+          <t>分析</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
         <is>
-          <t>★2つの名簿に重複して含まれる2人の扱い</t>
+          <t>★時系列比較（第8期・第9期との対比）の対象とする設問の範囲</t>
         </is>
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>★ニーズ調査の対象者のうち2人が在宅介護実態調査の名簿にも含まれている（被保険者番号で突合。番号の値は当方で保持していない）。この2人には2種類の調査票が届く。ニーズ調査の対象には要支援認定者が、在宅調査の対象には在宅の要介護認定者が含まれるため本来は重ならない。抽出条件によるものか認定区分が変更になった方かは不明。発送済みの場合、回収時に同じ方の回答が2件計上されないようにする必要がある。★10/10 優先度をAからSに上げた：発送が完了し集計が動き出したため、この2人の回答がすでに届いている可能性がある。重複回答の排除（Ⅰ-36）の手前で扱いを決める必要がある。当方の案は、2種類の調査票が届いた2人について、ニーズ調査の回答はニーズ調査の集計に、在宅介護実態調査の回答は在宅調査の集計に、それぞれ1件として数えることである（調査の目的と集計の母数が違うため、同じ方が両方に答えても二重計上にはならない）。ただし「認定状況×生活機能」のクロスで同じ方が2回出ないよう、突合の際は管理番号で名寄せする。この扱いでよいかをご確認いただきたい。</t>
+          <t>★令和4年8月版と令和7年8月版で設問文・選択肢が変わった設問は単純比較できない。doc05の逐条突合に基づき比較可能な設問のみを対象とするが、どこまで遡るかは村の判断。</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-24,Ⅰ-30,Ⅰ-36</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>doc43§2-3</t>
+          <t>doc24§12 K-86</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H116" s="4" t="inlineStr">
@@ -6876,12 +6876,12 @@
       </c>
       <c r="K116" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L116" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>第9期の調査票は受領済みであり、比較できる設問は当方が洗う。採否のみ伺う</t>
         </is>
       </c>
     </row>
@@ -6896,27 +6896,27 @@
       </c>
       <c r="C117" s="4" t="inlineStr">
         <is>
-          <t>行政区コードの先頭の桁と地区の対応（推定の確認）および在宅調査「追加分」77件の位置づけ</t>
+          <t>★ニーズ調査の対象者882人に対応する要介護認定データ（認定の有無・要介護度）</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>行政区コードの先頭の桁が地区に対応するという当方の推定が正しいかをご確認いただき、行政区名と地区（北山・大塩・桧原・裏磐梯）の対応表をご提供いただきたい。あわせて在宅調査の「追加分」77件の位置づけをご教示いただきたい。ニーズ調査の名簿の行政区コード（101〜407の23区分）について、先頭の桁が地区に対応するとみて第9期の対象者数と照合したところ4地区とも近い値となった（北山341対329、大塩185対200、桧原111対114、裏磐梯245対240、計882対883）。この対応で資料3の3-1の対象者数の欄を確定したため、推定が正しいかをご確認いただきたい。あわせて在宅調査の「追加分」77件の位置づけをご教示いただきたい（リスト66＋引き抜き52＝118で対象者数は足りており、ニーズ調査の「引き抜き」77件と同数である）。また、在宅介護実態調査の名簿の行政区は23区分あり10人以上は2区分のみであるため、そのままでは地区別の集計ができない。行政区名と地区（北山・大塩・桧原・裏磐梯）の対応表をご提供いただきたい。</t>
+          <t>★2026/09/28に受領した名簿のうち、要介護度の列があるのは在宅介護実態調査の対象者118人分のみで、ニーズ調査の対象者882人分にはない。資料3の3-3（元気な軽度者）・3-4（生活機能からみた4つの層）・3-6（担い手の可能性）は、ニーズ調査の回答者一人ひとりの認定状況を必要とするため、このままでは作成できない。資料3の3-6は第10期に共助・互助の仕組みをどの規模で構想できるかを示す表であり、合意1・2の根拠でもある。★10/10 優先度をAからSに上げた：村より「高齢者のアンケート発送は全て完了。今集計分析を行なっています」とのご連絡をいただいた。集計が動き出した以上、これが入らないと資料3の3-3・3-4・3-6が作れないまま第2回策定委員会（11月）の資料作成に入ることになる。回答データに後から認定状況を付けることはできるため、集計そのものは止まらないが、クロス集計をやり直す手戻りが生じる。できるだけ早くご提供いただきたい。</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-24,Ⅰ-40</t>
+          <t>Ⅰ-37,Ⅰ-38</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>doc43§2-1,§2-4</t>
+          <t>doc43§1</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H117" s="4" t="inlineStr">
@@ -6924,16 +6924,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I117" s="4" t="inlineStr"/>
-      <c r="J117" s="4" t="inlineStr"/>
+      <c r="I117" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L117" s="4" t="inlineStr">
         <is>
-          <t>行政区コードの対応は当方が推定して示す。推定の正誤のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -6943,27 +6949,27 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
         <is>
-          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）および総合事業対象者（基本チェックリスト該当者）の情報</t>
+          <t>★実際の発送日と回収状況（件数・回収率）、ウェブ回答フォームの稼働確認</t>
         </is>
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。★9/28：集計軸の認定状況を「認定なし／事業対象者／要支援1・2／要介護1以上」の4区分に統一したため、要介護認定データだけでは事業対象者を判別できない。総合事業の対象者（基本チェックリスト該当者）の情報もあわせてご提供いただきたい。議事録の「元気な軽度者」は事業対象者と要支援認定者の両方を指すため、これがないと検証の対象が半分になる。★10/10 優先度をAからSに上げた（上記と同じ理由。集計が動き出した）。</t>
+          <t>★10/10 起票：村より「高齢者のアンケート発送は全て完了。今集計分析を行なっています」とのご連絡をいただいた。WBSの実績日は、議事録の発送日（令和8年9月18日）と校了日（令和8年9月9日）で置いている。次の4点をご教示いただきたい。①実際の発送日（9月18日は金曜で翌日から5連休であったため、配達が連休明けにずれ込んだ可能性がある）。②本日時点の回収件数（ニーズ調査・在宅介護実態調査それぞれ。対象は882人・118人）。回収率は督促（Ⅰ-31）の判断に用いる。③ウェブ回答フォームの稼働確認の記録の有無と、ウェブ回答の件数。二次元コードを印字して発送した以上フォームは公開されているはずだが、稼働確認の記録が当方にない（Ⅰ-101）。④これまでの受渡しの回数・日・件数。回収は村で100件程度集まるごとに随時小分け送付する運用であり（doc22）、受渡し記録簿（doc74 §4-2）にさかのぼって記録する必要がある。★回収期限は令和8年10月16日（金）である。</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-37</t>
+          <t>Ⅰ-29,Ⅰ-30,Ⅰ-101,Ⅰ-94</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>doc24§12 K-87</t>
+          <t>doc75</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -6977,11 +6983,11 @@
         </is>
       </c>
       <c r="I118" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J118" s="4" t="inlineStr">
         <is>
-          <t>停止</t>
+          <t>工程外</t>
         </is>
       </c>
       <c r="K118" s="4" t="inlineStr">
@@ -7001,32 +7007,32 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>疑義</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
         <is>
-          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
+          <t>★2つの名簿に重複して含まれる2人の扱い</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
+          <t>★ニーズ調査の対象者のうち2人が在宅介護実態調査の名簿にも含まれている（被保険者番号で突合。番号の値は当方で保持していない）。この2人には2種類の調査票が届く。ニーズ調査の対象には要支援認定者が、在宅調査の対象には在宅の要介護認定者が含まれるため本来は重ならない。抽出条件によるものか認定区分が変更になった方かは不明。発送済みの場合、回収時に同じ方の回答が2件計上されないようにする必要がある。★10/10 優先度をAからSに上げた：発送が完了し集計が動き出したため、この2人の回答がすでに届いている可能性がある。重複回答の排除（Ⅰ-36）の手前で扱いを決める必要がある。当方の案は、2種類の調査票が届いた2人について、ニーズ調査の回答はニーズ調査の集計に、在宅介護実態調査の回答は在宅調査の集計に、それぞれ1件として数えることである（調査の目的と集計の母数が違うため、同じ方が両方に答えても二重計上にはならない）。ただし「認定状況×生活機能」のクロスで同じ方が2回出ないよう、突合の際は管理番号で名寄せする。この扱いでよいかをご確認いただきたい。</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-44</t>
+          <t>Ⅰ-24,Ⅰ-30,Ⅰ-36</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>doc24§12 K-89</t>
+          <t>doc43§2-3</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H119" s="4" t="inlineStr">
@@ -7035,11 +7041,11 @@
         </is>
       </c>
       <c r="I119" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J119" s="4" t="inlineStr">
         <is>
-          <t>記載待ち</t>
+          <t>仮置き</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
@@ -7059,27 +7065,27 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
         <is>
-          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
+          <t>行政区コードの先頭の桁と地区の対応（推定の確認）および在宅調査「追加分」77件の位置づけ</t>
         </is>
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
+          <t>行政区コードの先頭の桁が地区に対応するという当方の推定が正しいかをご確認いただき、行政区名と地区（北山・大塩・桧原・裏磐梯）の対応表をご提供いただきたい。あわせて在宅調査の「追加分」77件の位置づけをご教示いただきたい。ニーズ調査の名簿の行政区コード（101〜407の23区分）について、先頭の桁が地区に対応するとみて第9期の対象者数と照合したところ4地区とも近い値となった（北山341対329、大塩185対200、桧原111対114、裏磐梯245対240、計882対883）。この対応で資料3の3-1の対象者数の欄を確定したため、推定が正しいかをご確認いただきたい。あわせて在宅調査の「追加分」77件の位置づけをご教示いただきたい（リスト66＋引き抜き52＝118で対象者数は足りており、ニーズ調査の「引き抜き」77件と同数である）。また、在宅介護実態調査の名簿の行政区は23区分あり10人以上は2区分のみであるため、そのままでは地区別の集計ができない。行政区名と地区（北山・大塩・桧原・裏磐梯）の対応表をご提供いただきたい。</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅰ-24,Ⅰ-40</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>doc24§12 K-90</t>
+          <t>doc43§2-1,§2-4</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -7096,12 +7102,12 @@
       <c r="J120" s="4" t="inlineStr"/>
       <c r="K120" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L120" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>行政区コードの対応は当方が推定して示す。推定の正誤のみ伺う</t>
         </is>
       </c>
     </row>
@@ -7116,27 +7122,27 @@
       </c>
       <c r="C121" s="4" t="inlineStr">
         <is>
-          <t>第9期調査の集計基準・集計表の提供</t>
+          <t>★要介護認定データの提供時期と項目（要介護度・認定日・サービス利用状況）および総合事業対象者（基本チェックリスト該当者）の情報</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
+          <t>★仕様書4Ⅰ(5)。ICF分析の「認定状況×生活機能リスク」表と在宅調査のクロスに必須。目的外利用の手続きの確認を含む。議事録の「元気な軽度者が総合事業を利用している」の検証はこの紐付けでしかできない。★9/28：集計軸の認定状況を「認定なし／事業対象者／要支援1・2／要介護1以上」の4区分に統一したため、要介護認定データだけでは事業対象者を判別できない。総合事業の対象者（基本チェックリスト該当者）の情報もあわせてご提供いただきたい。議事録の「元気な軽度者」は事業対象者と要支援認定者の両方を指すため、これがないと検証の対象が半分になる。★10/10 優先度をAからSに上げた（上記と同じ理由。集計が動き出した）。</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-42</t>
+          <t>Ⅰ-37</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>doc25§8 K-92</t>
+          <t>doc24§12 K-87</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H121" s="4" t="inlineStr">
@@ -7144,8 +7150,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I121" s="4" t="inlineStr"/>
-      <c r="J121" s="4" t="inlineStr"/>
+      <c r="I121" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
       <c r="K121" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7168,27 +7180,27 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
+          <t>自由記述の匿名化の方針（削除・置換の範囲）</t>
         </is>
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
+          <t>★人口2,300人規模では記述内容から個人が推定され得る。固有名詞・事業所名・具体的な住所の扱いを決め、doc16の個人情報取扱管理ルールに追記する。★9/25：案Bの採用により自由記述の全文を電子媒体に収録することとなったため、匿名化の対象は紙の「分類と主要意見」（資料2）と電子媒体の全文の双方に及ぶ。電子媒体に回しても匿名化は免除されない。</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-35</t>
+          <t>Ⅰ-44</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>doc25§8 K-93</t>
+          <t>doc24§12 K-89</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H122" s="4" t="inlineStr">
@@ -7196,8 +7208,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I122" s="4" t="inlineStr"/>
-      <c r="J122" s="4" t="inlineStr"/>
+      <c r="I122" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J122" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K122" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7215,27 +7233,27 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
         <is>
-          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
+          <t>第2回策定委員会（11月）への調査報告書の提示範囲</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
+          <t>報告書全体か、第Ⅱ部（分析編）の要点か。委員の負担と議論の焦点に関わる。</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-48</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>doc25§8 K-94</t>
+          <t>doc24§12 K-90</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -7267,32 +7285,32 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>スケジュール</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
         <is>
-          <t>★第2回策定委員会の開催日（11月のいつか）</t>
+          <t>第9期調査の集計基準・集計表の提供</t>
         </is>
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
+          <t>前回比較（集計軸G）に必要。無回答の扱い・端数処理を揃えないと比較にならない。</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅰ-42</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>doc26§10 K-95</t>
+          <t>doc25§8 K-92</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H124" s="4" t="inlineStr">
@@ -7300,14 +7318,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I124" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J124" s="4" t="inlineStr">
-        <is>
-          <t>工程外</t>
-        </is>
-      </c>
+      <c r="I124" s="4" t="inlineStr"/>
+      <c r="J124" s="4" t="inlineStr"/>
       <c r="K124" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7330,27 +7342,27 @@
       </c>
       <c r="C125" s="4" t="inlineStr">
         <is>
-          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
+          <t>データ入力の体制（受託者側で入力するか、一部を村で行うか）</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
+          <t>小分け送付の運用と入力体制はセット。約1,000件の入力工数に影響する。</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-83</t>
+          <t>Ⅰ-35</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>doc26§10 K-97</t>
+          <t>doc25§8 K-93</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H125" s="4" t="inlineStr">
@@ -7358,14 +7370,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I125" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="J125" s="4" t="inlineStr">
-        <is>
-          <t>工程外</t>
-        </is>
-      </c>
+      <c r="I125" s="4" t="inlineStr"/>
+      <c r="J125" s="4" t="inlineStr"/>
       <c r="K125" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7383,32 +7389,32 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
         <is>
-          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
+          <t>見える化システムへの登録作業の分担（村が行うか受託者が代行するか）</t>
         </is>
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
+          <t>村独自設問14問を除外し標準様式の設問順に並べ替えた別ファイルの作成が必要。</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-70</t>
+          <t>Ⅰ-48</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>doc26§10 K-98</t>
+          <t>doc25§8 K-94</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H126" s="4" t="inlineStr">
@@ -7416,14 +7422,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I126" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J126" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I126" s="4" t="inlineStr"/>
+      <c r="J126" s="4" t="inlineStr"/>
       <c r="K126" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7441,27 +7441,27 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>スケジュール</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
         <is>
-          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
+          <t>★第2回策定委員会の開催日（11月のいつか）</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。★10/7 材料が揃った：国の推計ワークシートが第11期7,301.29円（＋32.4%）まで出力しているため、「取り崩しが第11期に跳ね返る」ことを当方の推定ではなく国の出力で示せる。</t>
+          <t>★資料の事前送付の期限が決まる。素案約90頁を当日配付では読めないため事前送付が前提。</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>doc26§10 K-99,doc66§2-3</t>
+          <t>doc26§10 K-95</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -7471,15 +7471,15 @@
       </c>
       <c r="H127" s="4" t="inlineStr">
         <is>
-          <t>一部回答</t>
+          <t>未依頼</t>
         </is>
       </c>
       <c r="I127" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J127" s="4" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>工程外</t>
         </is>
       </c>
       <c r="K127" s="4" t="inlineStr">
@@ -7499,32 +7499,32 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
+          <t>第2回策定委員会の資料の事前送付の可否と時期</t>
         </is>
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
+          <t>素案（完成度7割・約90頁）は別冊として事前送付する前提で資料を設計している。</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-83</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>doc27§3-1</t>
+          <t>doc26§10 K-97</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H128" s="4" t="inlineStr">
@@ -7532,8 +7532,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I128" s="4" t="inlineStr"/>
-      <c r="J128" s="4" t="inlineStr"/>
+      <c r="I128" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="J128" s="4" t="inlineStr">
+        <is>
+          <t>工程外</t>
+        </is>
+      </c>
       <c r="K128" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7551,32 +7557,32 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
         <is>
-          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
+          <t>★基本理念を第9期から変更するかどうかの村の意向</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
+          <t>★議事録の「公助から共助・互助へ」を基本理念に書き込むかは委員の合意事項。「公的サービスは維持したうえで足りない部分を地域で支え合う」という書き方の2案併記を提案。資料4の作成方針が変わる。</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅱ-70</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>doc27§3-2</t>
+          <t>doc26§10 K-98</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H129" s="4" t="inlineStr">
@@ -7584,8 +7590,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I129" s="4" t="inlineStr"/>
-      <c r="J129" s="4" t="inlineStr"/>
+      <c r="I129" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J129" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K129" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7603,41 +7615,47 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>調査設計</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
         <is>
-          <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
+          <t>保険料シミュレーションの提示案数と基金残高の見通しの示し方</t>
         </is>
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
+          <t>3案（取崩なし／第9期同程度／据置優先）を提案。各案に第10期末の基金残高を併記し、取り崩しが第11期の保険料に跳ね返ることを示す方針でよいか。★10/7 材料が揃った：国の推計ワークシートが第11期7,301.29円（＋32.4%）まで出力しているため、「取り崩しが第11期に跳ね返る」ことを当方の推定ではなく国の出力で示せる。</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>doc27§2-1</t>
+          <t>doc26§10 K-99,doc66§2-3</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H130" s="4" t="inlineStr">
         <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="I130" s="4" t="inlineStr"/>
-      <c r="J130" s="4" t="inlineStr"/>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="I130" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J130" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K130" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -7660,27 +7678,27 @@
       </c>
       <c r="C131" s="4" t="inlineStr">
         <is>
-          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
+          <t>★【必須】在宅A票 訪問診療の設問を問13に直す（問12が重複し問13が欠番）</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
+          <t>★第2稿で訪問診療が復活したが番号が問12となり、今後必要と感じる支援（問12）と重複している。回答者が混乱し集計時に設問を特定できない。9/9の校了までに必ず修正。</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>doc27§3-3</t>
+          <t>doc27§3-1</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H131" s="4" t="inlineStr">
@@ -7712,27 +7730,27 @@
       </c>
       <c r="C132" s="4" t="inlineStr">
         <is>
-          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
+          <t>★【必須】在宅A票 問9の基準月を「令和8年8月」に修正</t>
         </is>
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
+          <t>★問8は修正されたが問9が「令和●年●月」のまま。</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-09,Ⅰ-10</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>doc27§5-2</t>
+          <t>doc27§3-2</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H132" s="4" t="inlineStr">
@@ -7764,27 +7782,27 @@
       </c>
       <c r="C133" s="4" t="inlineStr">
         <is>
-          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
+          <t>★【必須】ニーズ 問1(2)① 選択肢14・15を「14．その他／15．不明」に修正</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
+          <t>★選択肢の順序の修正7か所のうち、この1か所のみ修正漏れ。標準は13．高齢による衰弱／14．その他（　）／15．不明。</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-10</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>doc27§5-3</t>
+          <t>doc27§2-1</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H133" s="4" t="inlineStr">
@@ -7816,27 +7834,27 @@
       </c>
       <c r="C134" s="4" t="inlineStr">
         <is>
-          <t>送付状の個人情報に関する説明の補強</t>
+          <t>★保険外サービスの選択肢の順序を4設問で統一（11．その他／12．該当なし）</t>
         </is>
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
+          <t>★ニーズ問7(9)のみ「11．利用していない／12．その他」で逆。他3設問（ニーズ問7(11)、在宅問11・問12）は「11．その他／12．該当なし」。2調査の結果を並べて比較する対の設問であり、番号がずれると集計時に手作業のマッピングが必要になる。</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-14</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>doc27§5-1</t>
+          <t>doc27§3-3</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H134" s="4" t="inlineStr">
@@ -7868,27 +7886,27 @@
       </c>
       <c r="C135" s="4" t="inlineStr">
         <is>
-          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
+          <t>★個人情報の取扱い欄から削除された「市町村外の」を標準様式どおりに戻す</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
+          <t>★第2稿で「厚生労働省の管理する市町村外のデータベース」から「市町村外の」が削除され、データが村の外に出ることが読み取れなくなった。手引きが図表10として文例を示している箇所。</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-09</t>
+          <t>Ⅰ-09,Ⅰ-10</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>doc27§4</t>
+          <t>doc27§5-2</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H135" s="4" t="inlineStr">
@@ -7920,22 +7938,22 @@
       </c>
       <c r="C136" s="4" t="inlineStr">
         <is>
-          <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
+          <t>★在宅B票の案内文（主な介護者が記入できない場合の取扱い）の復活</t>
         </is>
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
+          <t>★第2稿で1文が削除された。介護者が書けないときの取扱いが示されず、B票が丸ごと無回答になる可能性がある。B票は仕事と介護の両立の分析（X-16・X-17）の全データ源。</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-20</t>
+          <t>Ⅰ-10</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>doc27§6</t>
+          <t>doc27§5-3</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -7967,32 +7985,32 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
         <is>
-          <t>★会津権利擁護・成年後見センターへの相談が1年で件数▲43%・時間▲55%と減少した要因</t>
+          <t>送付状の個人情報に関する説明の補強</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
+          <t>第2稿で「回答された方が特定されることはありません」を「管理番号等は統計分析上において利用するものです」に変更。管理番号で紐付ける以上この修正は正しい方向だが説明として短い。議事録のクレーム対策の趣旨に沿った文案を提示済。</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-14</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>doc28§3-3 K-108</t>
+          <t>doc27§5-1</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H137" s="4" t="inlineStr">
@@ -8000,14 +8018,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I137" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I137" s="4" t="inlineStr"/>
+      <c r="J137" s="4" t="inlineStr"/>
       <c r="K137" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -8025,27 +8037,27 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
         <is>
-          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
+          <t>ニーズ調査の選択肢の表記変更5件の可否（障がい表記・ぜひ・役場・移動販売・フルタイム）</t>
         </is>
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
+          <t>村の表記ルール等による変更。手引きQ&amp;Aの「通称への置き換え」に近く多くは許容されると考えるが、「買い物（移動販売等※宅配は含まない）」のみ回答の範囲を広げる方向の変更で第9期・他保険者との比較に影響し得る。</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅰ-09</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-109</t>
+          <t>doc27§4</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -8062,12 +8074,12 @@
       <c r="J138" s="4" t="inlineStr"/>
       <c r="K138" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L138" s="4" t="inlineStr">
         <is>
-          <t>会津圏域13市町村の共同運営は公表されている。本村の位置づけのみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -8077,32 +8089,32 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>調査設計</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
         <is>
-          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
+          <t>調査票のレイアウトの目視確認3点（幸福度の記入欄／宛名ラベル枠／頁数）</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
+          <t>★当方の環境ではdocxからPDFへの変換ができずレイアウトを確認できない。ニーズ問8(2)の記入枠、表紙から削除された宛名ラベル枠と「第10期」表記、ルビ追加による頁数の増加を村側でご確認いただきたい。</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-107</t>
+          <t>Ⅰ-20</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>doc28§2 K-110</t>
+          <t>doc27§6</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H139" s="4" t="inlineStr">
@@ -8129,27 +8141,27 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
         <is>
-          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
+          <t>★会津権利擁護・成年後見センターへの相談が1年で件数▲43%・時間▲55%と減少した要因</t>
         </is>
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
+          <t>★令和6年度134件・1,625分→令和7年度76件・729分。圏域13市町村の総計は増加しているなかで本村のみ大きく減少。施策評価に必要。</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>doc28§3-4 K-111</t>
+          <t>doc28§3-3 K-108</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -8187,55 +8199,49 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
         <is>
-          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
+          <t>成年後見の中核機関の整備圏域（調査票は「市町村圏域」だが実態は会津圏域13市町村の共同運営か）</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。★10/5：【当方では確かめられないことが分かった。】 受領した見える化の出力738冊に将来推計メニューの出力が含まれていない（A〜W・δ系列のみ）。当方はシステムに接続しておらずファイルの提供を受けて作業しているため、設定画面を開くことができない。将来推計メニューの出力をご提供いただくか、国の推計ワークシート（推計ワークシートの入手）の受領を待つ。ワークシートが求める分母は別に起票しており、そちらが確定すれば本件も決まる。★10/10：【当方でできることは尽きた。解決済とする。】 10/7に受領した将来推計総括表を調べたが、総括表に記されているのは「在宅サービス受給率＝在宅サービス利用者数÷第1号被保険者数」というグラフ用の受給率の定義のみで、推計に用いる利用率の分母は書かれていない。総括表から利用者数を復元して4つの分母の候補で利用率を出しても、推計がサービス別・要介護度別に行われているため合算の利用率は要介護度の構成で動き、分母を特定できない（doc85）。残るのは推計ワークシート本体の受領であり、確認事項「国の推計ワークシートが求める在宅サービス利用率の分母」（優先度A）が引き継ぐ。</t>
+          <t>相談件数表から会津権利擁護・成年後見センターへの委託と見られるが、調査票の回答は市町村圏域。計画の記述の正確性に関わる。</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>doc38§C-1,doc85</t>
+          <t>doc28§3-4 K-109</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H141" s="4" t="inlineStr">
         <is>
-          <t>解決済</t>
-        </is>
-      </c>
-      <c r="I141" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>社内</t>
-        </is>
-      </c>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="I141" s="4" t="inlineStr"/>
+      <c r="J141" s="4" t="inlineStr"/>
       <c r="K141" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L141" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>会津圏域13市町村の共同運営は公表されている。本村の位置づけのみ伺う</t>
         </is>
       </c>
     </row>
@@ -8250,27 +8256,27 @@
       </c>
       <c r="C142" s="4" t="inlineStr">
         <is>
-          <t>養護老人ホームへの措置・軽費老人ホームの利用・老人クラブの実績（見える化に系列が一切ない）</t>
+          <t>合計所得金額分布調査の10万円刻みデータを保険料試算に使用してよいか</t>
         </is>
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>★養護老人ホームへの措置、軽費老人ホームの利用、老人クラブの実績をご提供いただきたい。老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
+          <t>所得段階の区切りを変えた場合の影響試算に使える。第10期で段階設定を見直す場合の基礎データ。</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54</t>
+          <t>Ⅱ-107</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc28§2 K-110</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H142" s="4" t="inlineStr">
@@ -8278,14 +8284,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I142" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>停止</t>
-        </is>
-      </c>
+      <c r="I142" s="4" t="inlineStr"/>
+      <c r="J142" s="4" t="inlineStr"/>
       <c r="K142" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -8303,32 +8303,32 @@
       </c>
       <c r="B143" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C143" s="4" t="inlineStr">
         <is>
-          <t>特定健診・後期高齢者健診の受診率（見える化に系列がない）</t>
+          <t>成年後見制度の市町村計画を第10期でも一体で策定するか</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>★特定健診・後期高齢者健診の受診率（市町村国保）をご提供いただきたい。★10/20 当方の先行：厚生労働省のサイトに接続できるようになったため、公表されている範囲を確かめた。ア 福島県の値は押さえた。令和5年度の特定健診の受診率は58.3％（対象者816,798人・受診者476,261人）、特定保健指導の実施率は25.2％である（厚生労働省「特定健康診査・特定保健指導に関するデータ」都道府県別一覧）。イ ただしこれは全保険者を合わせた値であり、市町村国保に限った値ではない。ウ 国は市町村別の値を公表していない。同ページの集計はすべて都道府県別または全国別であり、保険者から報告された郵便番号をもとに都道府県別に整理されている。エ したがって本村の値は、村または国保データベース（KDB）から取る以外にない。お尋ねするのはこの1点に絞られる。得られない場合は、施策1-6の指標から受診率を外し、県の値（58.3％）を参考として注記するにとどめる。オ なお、令和6年度の数値は誤りの可能性があるとして国が掲載を一時中止している。施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
+          <t>調査票で「策定済み・高齢者保健福祉計画・介護保険事業計画と一体的に策定・見直し予定なし」と回答。第10期の計画期間との整合が必要。</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-54</t>
+          <t>Ⅱ-72</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>doc38§D</t>
+          <t>doc28§3-4 K-111</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H143" s="4" t="inlineStr">
@@ -8336,16 +8336,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I143" s="4" t="inlineStr"/>
-      <c r="J143" s="4" t="inlineStr"/>
+      <c r="I143" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J143" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K143" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L143" s="4" t="inlineStr">
         <is>
-          <t>県・国保データベースの公表値で当方が押さえる。村の最新値のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -8355,27 +8361,27 @@
       </c>
       <c r="B144" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C144" s="4" t="inlineStr">
         <is>
-          <t>★令和6・7年度に取得していた5項目（22点）が令和8年度に0点になった理由</t>
+          <t>★見える化の「将来推計」メニューで在宅サービス利用率の分母を確認する</t>
         </is>
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>★3か年の項目別の推移を分析した結果（doc48）、悪化した23項目115点のうち93点は成果指標群（国の統計から自動算定されるもの）で、村の取組として後退したのは次の5項目22点であることが分かった。①福祉用具購入費・住宅改修費の妥当性の検討（推進Ⅱ・8点・全国該当率65.1%）②主要3事業（要介護認定の適正化・ケアプラン等の点検）の実施と記録（推進Ⅱ・6点・96.9%）③在宅医療・介護連携の4つの場面ごとの目指すべき姿の設定（支援Ⅲ・5点・72.3%）④相談内容の取りまとめと関係者間での共有（支援Ⅲ・2点・85.9%）⑤総合事業における従前相当以外のサービスの実施（支援Ⅰ・1点・29.8%）。いずれも令和6年度または令和7年度は取得していた。このうち主要な事業の実施と記録は全国の96.9%が取得している項目であり、最も重い。★10/6：当初は3項目15点としていたが、配点が年度間で変わった項目を除いて数え直すと5項目22点であった。主要な事業の実施と記録（推進Ⅱ・6点）は令和6年度には3つの小項目各2点に分かれており、集計の単位が違うため見落としていた。取組が止まったのか、国への該当状況調査票の記載によるものかをご確認いただきたい。取組が止まったのであれば令和9年度の評価で取り戻せる。</t>
+          <t>★★見込量が数割変わる論点（要介護1で58.8%→86.1%、要介護2で107.7%と100%超）。★10/5：【当方では確かめられないことが分かった。】 受領した見える化の出力738冊に将来推計メニューの出力が含まれていない（A〜W・δ系列のみ）。当方はシステムに接続しておらずファイルの提供を受けて作業しているため、設定画面を開くことができない。将来推計メニューの出力をご提供いただくか、国の推計ワークシート（推計ワークシートの入手）の受領を待つ。ワークシートが求める分母は別に起票しており、そちらが確定すれば本件も決まる。★10/10：【当方でできることは尽きた。解決済とする。】 10/7に受領した将来推計総括表を調べたが、総括表に記されているのは「在宅サービス受給率＝在宅サービス利用者数÷第1号被保険者数」というグラフ用の受給率の定義のみで、推計に用いる利用率の分母は書かれていない。総括表から利用者数を復元して4つの分母の候補で利用率を出しても、推計がサービス別・要介護度別に行われているため合算の利用率は要介護度の構成で動き、分母を特定できない（doc85）。残るのは推計ワークシート本体の受領であり、確認事項「国の推計ワークシートが求める在宅サービス利用率の分母」（優先度A）が引き継ぐ。</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-67</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>doc48§1-2</t>
+          <t>doc38§C-1,doc85</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -8385,15 +8391,15 @@
       </c>
       <c r="H144" s="4" t="inlineStr">
         <is>
-          <t>未依頼</t>
+          <t>解決済</t>
         </is>
       </c>
       <c r="I144" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J144" s="4" t="inlineStr">
         <is>
-          <t>記載待ち</t>
+          <t>社内</t>
         </is>
       </c>
       <c r="K144" s="4" t="inlineStr">
@@ -8418,27 +8424,27 @@
       </c>
       <c r="C145" s="4" t="inlineStr">
         <is>
-          <t>令和8年度 該当状況調査票集計表（市町村分・全国一覧表）の再ご提供</t>
+          <t>養護老人ホームへの措置・軽費老人ホームの利用・老人クラブの実績（見える化に系列が一切ない）</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>受領した全国一覧表（1,563列）が作業環境に残っておらず、項目別の県内順位を再集計できない。目標別の県内順位・県中央値と、計画への記載で取得をめざす11項目の県内順位は算定済みで記録しているが、残りの要改善項目について県内での位置を出すには原本が必要である。県内で遅れているのは支援Ⅱ（県中央値▲23点）と推進Ⅱ（同▲14点）の2目標に絞られているため、この2目標の12項目について県内順位が分かると、重点の置き方の説明がしやすくなる。</t>
+          <t>★養護老人ホームへの措置、軽費老人ホームの利用、老人クラブの実績をご提供いただきたい。老人福祉法第20条の8第2項が計画への記載を義務づける「老人福祉事業の量の目標」（素案4-6）の基礎。見える化に該当する系列がないため、村資料の受領が必須。代替手段はない。</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-67</t>
+          <t>Ⅱ-53,Ⅱ-54</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>doc48§0</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H145" s="4" t="inlineStr">
@@ -8446,8 +8452,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I145" s="4" t="inlineStr"/>
-      <c r="J145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
       <c r="K145" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -8470,42 +8482,36 @@
       </c>
       <c r="C146" s="4" t="inlineStr">
         <is>
-          <t>★介護給付費財政調整交付金の算定における主要3事業の取組状況の勘案（県への照会）</t>
+          <t>特定健診・後期高齢者健診の受診率（見える化に系列がない）</t>
         </is>
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>★県に対し、介護給付費財政調整交付金の算定方法と主要3事業の取組状況の勘案の有無・程度、本村の交付割合の見通しを照会いただきたい。あわせて指針の該当箇所（第二の(2)④）の原文の確認をお願いしたい。「介護給付適正化計画に関する指針」（令和5年9月12日老介発0912第1号）は、介護給付費財政調整交付金の第9期計画期間（令和6年度から）の算定に当たって主要3事業の取組状況を勘案することとしている。本村は令和8年度の評価で「主要3事業のすべてを実施している」ことを問う指標が0点であるため、調整交付金の交付割合に影響し得る。見込交付割合が0.1ポイント下がると保険料基準額は月額約26円上がり、素案5-7で置いた幅（4.10〜4.32％）の0.22ポイントでは約58円上がる。★10/7 一部解消：国の推計ワークシートの見込交付割合は5.36／5.03／4.67%で、当方が復元した4.10〜4.32%を上回っていた。勘案による減額が織り込まれているようには見えないが、この値の出所（県の指示値か村の入力値か）が未確認であるため、勘案の有無の照会は残す。保険料への影響の大きさは確定したので優先度をAに下げた。</t>
+          <t>★特定健診・後期高齢者健診の受診率（市町村国保）をご提供いただきたい。★10/20 当方の先行：厚生労働省のサイトに接続できるようになったため、公表されている範囲を確かめた。ア 福島県の値は押さえた。令和5年度の特定健診の受診率は58.3％（対象者816,798人・受診者476,261人）、特定保健指導の実施率は25.2％である（厚生労働省「特定健康診査・特定保健指導に関するデータ」都道府県別一覧）。イ ただしこれは全保険者を合わせた値であり、市町村国保に限った値ではない。ウ 国は市町村別の値を公表していない。同ページの集計はすべて都道府県別または全国別であり、保険者から報告された郵便番号をもとに都道府県別に整理されている。エ したがって本村の値は、村または国保データベース（KDB）から取る以外にない。お尋ねするのはこの1点に絞られる。得られない場合は、施策1-6の指標から受診率を外し、県の値（58.3％）を参考として注記するにとどめる。オ なお、令和6年度の数値は誤りの可能性があるとして国が掲載を一時中止している。施策1-6（保健事業と介護予防の一体的実施）の指標に用いる。見える化に系列がないため、村または国保データベース（KDB）システムから取る。KDBは見える化とは別のシステムであり、アクセスの可否を村に確認する。</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-62,Ⅱ-64,Ⅱ-109</t>
+          <t>Ⅱ-54</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>doc46§3,doc66§3-3</t>
+          <t>doc38§D</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H146" s="4" t="inlineStr">
         <is>
-          <t>一部回答</t>
-        </is>
-      </c>
-      <c r="I146" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="I146" s="4" t="inlineStr"/>
+      <c r="J146" s="4" t="inlineStr"/>
       <c r="K146" s="4" t="inlineStr">
         <is>
           <t>Ｃ</t>
@@ -8513,7 +8519,7 @@
       </c>
       <c r="L146" s="4" t="inlineStr">
         <is>
-          <t>課長会議資料で勘案の仕組みを当方が確かめた（doc94）。県への照会の要否のみ伺う</t>
+          <t>県・国保データベースの公表値で当方が押さえる。村の最新値のみ伺う</t>
         </is>
       </c>
     </row>
@@ -8528,27 +8534,27 @@
       </c>
       <c r="C147" s="4" t="inlineStr">
         <is>
-          <t>令和8年度から新設された成果指向型配分枠（配点100点）の要件と本村の得点</t>
+          <t>★令和6・7年度に取得していた5項目（22点）が令和8年度に0点になった理由</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>成果指向型配分枠（配点100点）の要件と本村の得点を県に照会いただきたい。令和8年度の評価指標には保険者機能強化推進交付金の成果指向型配分枠（100点）が新設されている。受領した該当状況調査票集計表（市町村分）には当該配分枠の列がないため本村の得点が確認できない。本村の800点は評価指標による満点（推進400点・支援400点）であり、この枠を含まない。成果指向型の介護予防・健康づくりの取組が対象となるため、施策1-1・1-3の組み立てに関わる。</t>
+          <t>★3か年の項目別の推移を分析した結果（doc48）、悪化した23項目115点のうち93点は成果指標群（国の統計から自動算定されるもの）で、村の取組として後退したのは次の5項目22点であることが分かった。①福祉用具購入費・住宅改修費の妥当性の検討（推進Ⅱ・8点・全国該当率65.1%）②主要3事業（要介護認定の適正化・ケアプラン等の点検）の実施と記録（推進Ⅱ・6点・96.9%）③在宅医療・介護連携の4つの場面ごとの目指すべき姿の設定（支援Ⅲ・5点・72.3%）④相談内容の取りまとめと関係者間での共有（支援Ⅲ・2点・85.9%）⑤総合事業における従前相当以外のサービスの実施（支援Ⅰ・1点・29.8%）。いずれも令和6年度または令和7年度は取得していた。このうち主要な事業の実施と記録は全国の96.9%が取得している項目であり、最も重い。★10/6：当初は3項目15点としていたが、配点が年度間で変わった項目を除いて数え直すと5項目22点であった。主要な事業の実施と記録（推進Ⅱ・6点）は令和6年度には3つの小項目各2点に分かれており、集計の単位が違うため見落としていた。取組が止まったのか、国への該当状況調査票の記載によるものかをご確認いただきたい。取組が止まったのであれば令和9年度の評価で取り戻せる。</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-109</t>
+          <t>Ⅱ-67</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>doc46§2</t>
+          <t>doc48§1-2</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H147" s="4" t="inlineStr">
@@ -8556,16 +8562,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I147" s="4" t="inlineStr"/>
-      <c r="J147" s="4" t="inlineStr"/>
+      <c r="I147" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K147" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L147" s="4" t="inlineStr">
         <is>
-          <t>配分枠の要件は公表されている。本村の得点のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -8580,22 +8592,22 @@
       </c>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
+          <t>令和8年度 該当状況調査票集計表（市町村分・全国一覧表）の再ご提供</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
+          <t>受領した全国一覧表（1,563列）が作業環境に残っておらず、項目別の県内順位を再集計できない。目標別の県内順位・県中央値と、計画への記載で取得をめざす11項目の県内順位は算定済みで記録しているが、残りの要改善項目について県内での位置を出すには原本が必要である。県内で遅れているのは支援Ⅱ（県中央値▲23点）と推進Ⅱ（同▲14点）の2目標に絞られているため、この2目標の12項目について県内順位が分かると、重点の置き方の説明がしやすくなる。</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-67</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>doc36§10-4,doc18 4-7(3)</t>
+          <t>doc48§0</t>
         </is>
       </c>
       <c r="G148" s="4" t="inlineStr">
@@ -8627,49 +8639,55 @@
       </c>
       <c r="B149" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C149" s="4" t="inlineStr">
         <is>
-          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
+          <t>★介護給付費財政調整交付金の算定における主要3事業の取組状況の勘案（県への照会）</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
+          <t>★県に対し、介護給付費財政調整交付金の算定方法と主要3事業の取組状況の勘案の有無・程度、本村の交付割合の見通しを照会いただきたい。あわせて指針の該当箇所（第二の(2)④）の原文の確認をお願いしたい。「介護給付適正化計画に関する指針」（令和5年9月12日老介発0912第1号）は、介護給付費財政調整交付金の第9期計画期間（令和6年度から）の算定に当たって主要3事業の取組状況を勘案することとしている。本村は令和8年度の評価で「主要3事業のすべてを実施している」ことを問う指標が0点であるため、調整交付金の交付割合に影響し得る。見込交付割合が0.1ポイント下がると保険料基準額は月額約26円上がり、素案5-7で置いた幅（4.10〜4.32％）の0.22ポイントでは約58円上がる。★10/7 一部解消：国の推計ワークシートの見込交付割合は5.36／5.03／4.67%で、当方が復元した4.10〜4.32%を上回っていた。勘案による減額が織り込まれているようには見えないが、この値の出所（県の指示値か村の入力値か）が未確認であるため、勘案の有無の照会は残す。保険料への影響の大きさは確定したので優先度をAに下げた。</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68</t>
+          <t>Ⅱ-62,Ⅱ-64,Ⅱ-109</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>doc36§10-2,doc18 4-7(4)</t>
+          <t>doc46§3,doc66§3-3</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H149" s="4" t="inlineStr">
         <is>
-          <t>未依頼</t>
-        </is>
-      </c>
-      <c r="I149" s="4" t="inlineStr"/>
-      <c r="J149" s="4" t="inlineStr"/>
+          <t>一部回答</t>
+        </is>
+      </c>
+      <c r="I149" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J149" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K149" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L149" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>課長会議資料で勘案の仕組みを当方が確かめた（doc94）。県への照会の要否のみ伺う</t>
         </is>
       </c>
     </row>
@@ -8679,32 +8697,32 @@
       </c>
       <c r="B150" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C150" s="4" t="inlineStr">
         <is>
-          <t>認知症施策の実施状況の評価と公表の運用</t>
+          <t>令和8年度から新設された成果指向型配分枠（配点100点）の要件と本村の得点</t>
         </is>
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
+          <t>成果指向型配分枠（配点100点）の要件と本村の得点を県に照会いただきたい。令和8年度の評価指標には保険者機能強化推進交付金の成果指向型配分枠（100点）が新設されている。受領した該当状況調査票集計表（市町村分）には当該配分枠の列がないため本村の得点が確認できない。本村の800点は評価指標による満点（推進400点・支援400点）であり、この枠を含まない。成果指向型の介護予防・健康づくりの取組が対象となるため、施策1-1・1-3の組み立てに関わる。</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-109</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>doc36§10-1,doc18 4-7(6)</t>
+          <t>doc46§2</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H150" s="4" t="inlineStr">
@@ -8712,22 +8730,16 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I150" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I150" s="4" t="inlineStr"/>
+      <c r="J150" s="4" t="inlineStr"/>
       <c r="K150" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L150" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>配分枠の要件は公表されている。本村の得点のみ伺う</t>
         </is>
       </c>
     </row>
@@ -8737,27 +8749,27 @@
       </c>
       <c r="B151" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C151" s="4" t="inlineStr">
         <is>
-          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
+          <t>若年性認知症（65歳未満で認知症となった方）の状況</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
+          <t>★認知症基本法第16条第2項は、若年性認知症の人その他の認知症の人の意欲および能力に応じた雇用の継続・円滑な就職に資する施策を求める。若年性認知症の方は介護保険では第2号被保険者となり、就労の継続が生活の基盤に直結する。本村の該当者の状況が未把握。</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>doc36§10-3,doc18 4-7(3)</t>
+          <t>doc36§10-4,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -8789,32 +8801,32 @@
       </c>
       <c r="B152" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C152" s="4" t="inlineStr">
         <is>
-          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
+          <t>認知症の日（9月21日）・認知症月間（9月）の取組</t>
         </is>
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>★施策3-2・5-4(8)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率88%。増床の要否は待機と村外利用の実態がなければ判断できない。★9/28：国の基本指針が求める「真に入所が必要と判断される被保険者の把握」（素案5-4(13)）の3つの柱のうち2つがこれにあたる。待機者については申込者の要介護度・在宅か入院か・申込時期を、村外施設については介護老人福祉施設・介護老人保健施設・介護医療院それぞれの入所者数と入所先をご教示いただきたい。給付実績からの把握でも可。★10/23 一部解決：村より受領した事業所別の5か年推移（doc116）により、村内2事業所の1月あたりの利用者数（実数）は令和7年に9人＋18人＝27人で定員27人と同じ、延べ利用者数を定員で割ると両事業所とも30.0（日）で満床である（令和3年は約75〜80%）。残るのは待機者数、入居者のうち本村の被保険者の数、村外のグループホームを利用している本村の被保険者の数である。★同日、素案2-5・5-4(5)・5-4(8)・5-12に反映した（満床であること、本村の被保険者の利用者数24人との差の内訳が未確認であること）</t>
+          <t>★認知症基本法第9条第3項は、地方公共団体に対し認知症の日にふさわしい事業の実施（努力義務）と、認知症月間にふさわしい行事が実施されるよう奨励すること（義務）を定める。本村に該当する取組がない。普及啓発の機会として計画に位置づけたが、実施の可否と内容を村と協議する。</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-67</t>
+          <t>Ⅱ-68</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 5-4(8)・5-4(13),doc47§4</t>
+          <t>doc36§10-2,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H152" s="4" t="inlineStr">
@@ -8822,14 +8834,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I152" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+      <c r="I152" s="4" t="inlineStr"/>
+      <c r="J152" s="4" t="inlineStr"/>
       <c r="K152" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -8847,27 +8853,27 @@
       </c>
       <c r="B153" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C153" s="4" t="inlineStr">
         <is>
-          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
+          <t>認知症施策の実施状況の評価と公表の運用</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
+          <t>★認知症基本法第13条第3項が準用する第12条第5項は、適時に施策の実施状況の評価を行い結果を公表すること、第7項は評価結果の取りまとめにあたって認知症の人および家族等の意見を聴くことを求める（いずれも努力義務）。第9期では行われていない。交付金の評価指標「進捗状況の評価にあたり認知症当事者の意見を聞いている」（本村0点）と同内容であり、法の求めに応えることが得点にもつながる。評価の時期・公表の方法・意見聴取の相手方を村と定める。</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-68</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>doc36§4,doc18 5-5(1)</t>
+          <t>doc36§10-1,doc18 4-7(6)</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -8910,27 +8916,27 @@
       </c>
       <c r="C154" s="4" t="inlineStr">
         <is>
-          <t>認知症の人およびご家族から意見を聴く方法</t>
+          <t>公共交通事業者・金融機関・小売業者等との連携の範囲</t>
         </is>
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
+          <t>★認知症基本法第7条は、これらの事業者に認知症の人への必要かつ合理的な配慮を求める（努力義務）。第15条のバリアフリー化の民間側の受け皿。村内および近隣の事業者にどこまで働きかけるかを定める。</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-71</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>doc36§5,doc18 4-7(4)</t>
+          <t>doc36§10-3,doc18 4-7(3)</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H154" s="4" t="inlineStr">
@@ -8938,14 +8944,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I154" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I154" s="4" t="inlineStr"/>
+      <c r="J154" s="4" t="inlineStr"/>
       <c r="K154" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -8963,17 +8963,17 @@
       </c>
       <c r="B155" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C155" s="4" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護を再開するかどうか</t>
+          <t>認知症対応型共同生活介護（村内27人分）の待機者数と、村外のグループホームを利用している方の人数</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
+          <t>★施策3-2・5-4(8)の必要利用定員総数の判断に必須。認知症高齢者（自立度Ⅱ以上）は2年間で132人→161人と22.0%増えた一方、定員は平成28年度以降27人のまま。稼働率88%。増床の要否は待機と村外利用の実態がなければ判断できない。★9/28：国の基本指針が求める「真に入所が必要と判断される被保険者の把握」（素案5-4(13)）の3つの柱のうち2つがこれにあたる。待機者については申込者の要介護度・在宅か入院か・申込時期を、村外施設については介護老人福祉施設・介護老人保健施設・介護医療院それぞれの入所者数と入所先をご教示いただきたい。給付実績からの把握でも可。★10/23 一部解決：村より受領した事業所別の5か年推移（doc116）により、村内2事業所の1月あたりの利用者数（実数）は令和7年に9人＋18人＝27人で定員27人と同じ、延べ利用者数を定員で割ると両事業所とも30.0（日）で満床である（令和3年は約75〜80%）。残るのは待機者数、入居者のうち本村の被保険者の数、村外のグループホームを利用している本村の被保険者の数である。★同日、素案2-5・5-4(5)・5-4(8)・5-12に反映した（満床であること、本村の被保険者の利用者数24人との差の内訳が未確認であること）</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 施策3-2</t>
+          <t>doc36§3,doc18 5-4(8)・5-4(13),doc47§4</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H155" s="4" t="inlineStr">
@@ -8996,8 +8996,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I155" s="4" t="inlineStr"/>
-      <c r="J155" s="4" t="inlineStr"/>
+      <c r="I155" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K155" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -9015,32 +9021,32 @@
       </c>
       <c r="B156" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C156" s="4" t="inlineStr">
         <is>
-          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
+          <t>認知症関連事業の実績（認知症カフェの箇所数、認知症初期集中支援推進事業の対象者数、認知症地域支援推進員の活動実績）</t>
         </is>
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
+          <t>★素案5-5(1)の地域支援事業の量に認知症総合支援事業の行を新設したが、いずれも実績が未受領。国の様式では認知症総合支援事業の量を定めることが求められる。</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-68,Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-68</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>doc36§3,doc18 4-7(2)</t>
+          <t>doc36§4,doc18 5-5(1)</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H156" s="4" t="inlineStr">
@@ -9048,8 +9054,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I156" s="4" t="inlineStr"/>
-      <c r="J156" s="4" t="inlineStr"/>
+      <c r="I156" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K156" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -9072,22 +9084,22 @@
       </c>
       <c r="C157" s="4" t="inlineStr">
         <is>
-          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
+          <t>認知症の人およびご家族から意見を聴く方法</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
+          <t>★認知症基本法第13条第3項は、市町村計画の策定にあたり認知症の人および家族等の意見を聴くよう努めることを求める。第9期では行われていない。策定委員会への参画、家族介護者の会での聴取、個別の聞き取りなどが考えられる。国の評価指標にも「進捗状況の評価にあたり認知症当事者の意見を聞いている」項目があり本村は0点。</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-71</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§5,doc18 4-7(4)</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -9101,21 +9113,21 @@
         </is>
       </c>
       <c r="I157" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>記載待ち</t>
         </is>
       </c>
       <c r="K157" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L157" s="4" t="inlineStr">
         <is>
-          <t>当方の算定方針である。2案を示し、採る案のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -9130,22 +9142,22 @@
       </c>
       <c r="C158" s="4" t="inlineStr">
         <is>
-          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
+          <t>認知症対応型通所介護を再開するかどうか</t>
         </is>
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
+          <t>平成30年度を最後に実績がない。地域密着型サービスは村の指定によりはじめて提供されるため村の判断による。認知症高齢者が増えるなかで在宅を支える類型として検討の余地がある。</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-56,Ⅱ-67</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>doc35§7-3(3),doc18 5-4(5)</t>
+          <t>doc36§3,doc18 施策3-2</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -9177,27 +9189,27 @@
       </c>
       <c r="B159" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C159" s="4" t="inlineStr">
         <is>
-          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
+          <t>認知症施策推進計画として、基本法第15条（バリアフリー化）にどこまで取り組むか</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
+          <t>★認知症の人が外出・買い物・金融機関の利用などで困ることへの対応は介護保険の枠組みの外にある。庁内の関係部署および事業者との連携の範囲を定める必要がある。素案4-7(2)で【要検討】としている。</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-55,Ⅱ-56</t>
+          <t>Ⅱ-68,Ⅱ-72</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>doc35§7-3(2),doc18 5-6</t>
+          <t>doc36§3,doc18 4-7(2)</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
@@ -9229,27 +9241,27 @@
       </c>
       <c r="B160" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C160" s="4" t="inlineStr">
         <is>
-          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
+          <t>居宅療養管理指導・短期入所生活介護を3か年平均と令和7年度水準のどちらで置くか</t>
         </is>
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
+          <t>★令和7年度実績から令和9年度見込への変化率が▲25.3%・▲20.8%。いずれも急伸中のサービスで、3か年平均が令和7年度を大きく下回るため。居宅療養管理指導は令和2→7年度で年率+54.9%、短期入所生活介護は1人あたり利用日数が4.2日→7.3日／月に伸びている。3か年平均のままでは見込量が過小になる。国のツールのワーニング判定でも指摘される可能性が高い。</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-65,Ⅱ-68</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>doc35§7-2(6)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -9263,11 +9275,11 @@
         </is>
       </c>
       <c r="I160" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J160" s="4" t="inlineStr">
         <is>
-          <t>記載待ち</t>
+          <t>仮置き</t>
         </is>
       </c>
       <c r="K160" s="4" t="inlineStr">
@@ -9277,7 +9289,7 @@
       </c>
       <c r="L160" s="4" t="inlineStr">
         <is>
-          <t>評価指標の要件は公表されている。本村の取組の実態のみ伺う</t>
+          <t>当方の算定方針である。2案を示し、採る案のみ伺う</t>
         </is>
       </c>
     </row>
@@ -9287,32 +9299,32 @@
       </c>
       <c r="B161" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C161" s="4" t="inlineStr">
         <is>
-          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
+          <t>訪問入浴介護・地域密着型通所介護を0に戻すかどうか</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
+          <t>★令和7年度の利用は0だが、3か年平均により令和9年度以降も0.6人／月・0.3人／月が立っている。直近に利用のないサービスを3か年平均で復活させてよいかの判断。利用の見込みの有無を村に確認する。</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-65</t>
+          <t>Ⅱ-56</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc35§7-3(3),doc18 5-4(5)</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H161" s="4" t="inlineStr">
@@ -9320,14 +9332,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I161" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I161" s="4" t="inlineStr"/>
+      <c r="J161" s="4" t="inlineStr"/>
       <c r="K161" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -9345,32 +9351,32 @@
       </c>
       <c r="B162" s="4" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C162" s="4" t="inlineStr">
         <is>
-          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
+          <t>令和6年度・令和7年度の介護サービス等諸費／介護予防サービス等諸費の決算額</t>
         </is>
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
+          <t>★介護給付費と予防給付費の分離に用いる単価は、見える化D48-b系により令和3〜5年度までしか把握できない。5-4の受給率（令和5〜7年度の3か年平均）と期間が1年ずれている。令和6・7年度の決算で揃える。</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-70,Ⅱ-71</t>
+          <t>Ⅱ-55,Ⅱ-56</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>doc35§7-2(3)</t>
+          <t>doc35§7-3(2),doc18 5-6</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H162" s="4" t="inlineStr">
@@ -9378,14 +9384,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I162" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>記載待ち</t>
-        </is>
-      </c>
+      <c r="I162" s="4" t="inlineStr"/>
+      <c r="J162" s="4" t="inlineStr"/>
       <c r="K162" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -9403,17 +9403,17 @@
       </c>
       <c r="B163" s="4" t="inlineStr">
         <is>
-          <t>取組</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C163" s="4" t="inlineStr">
         <is>
-          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
+          <t>認知症サポーター約237人が国の評価指標で0点となっている理由</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
+          <t>★人口比9.8%（237人／2,363人）が養成されているにもかかわらず、令和8年度の評価で「認知症サポーター数」は12点中0点（全国平均4.8点）。養成率の基準を満たしていないのか、該当状況調査票の記載によるものかで、施策4-4の組み立てが変わる。</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="G163" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H163" s="4" t="inlineStr">
@@ -9436,16 +9436,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I163" s="4" t="inlineStr"/>
-      <c r="J163" s="4" t="inlineStr"/>
+      <c r="I163" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J163" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K163" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L163" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>評価指標の要件は公表されている。本村の取組の実態のみ伺う</t>
         </is>
       </c>
     </row>
@@ -9455,32 +9461,32 @@
       </c>
       <c r="B164" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C164" s="4" t="inlineStr">
         <is>
-          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
+          <t>要介護3〜5の方の状態の変化が令和8年度に2指標とも0点となった実態</t>
         </is>
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
+          <t>★短期的な要介護度の変化（要介護3〜5）が40点中0点、長期的な変化が20点中0点で、合わせて35点の減。目標Ⅳの25点低下の主因。本村の要介護3以上の認定者は59人（令和8年3月末）であり、数人の状態の変化が指標を動かす。個別の状況の把握が要る。</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-64</t>
+          <t>Ⅱ-65</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>doc35§7-2(1),doc18 5-11</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H164" s="4" t="inlineStr">
@@ -9488,8 +9494,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I164" s="4" t="inlineStr"/>
-      <c r="J164" s="4" t="inlineStr"/>
+      <c r="I164" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>記載待ち</t>
+        </is>
+      </c>
       <c r="K164" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -9507,27 +9519,27 @@
       </c>
       <c r="B165" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C165" s="4" t="inlineStr">
         <is>
-          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
+          <t>計画の進捗管理（目標Ⅰの3項目）が令和7年度0点から令和8年度48点満点になった根拠</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。素案5-4(14)の24時間対応サービスの確保方策では、この活用を軸に据えている。特定地域の指定は村の意向を踏まえて都道府県が定めるため、計画に確保方策として記載することが手続の起点になる。</t>
+          <t>★事業計画の進捗状況・施策の実施状況の把握・改善・評価結果の活用がいずれも満点となり全項目で全国平均を上回った。一方、第9期計画の本体には評価の方法・時期・報告先がなく、計画値と実績値の乖離は本業務で初めて整理した。何をもって該当としたのかを確認し、第10期の第6章に引き継ぐ。</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56,Ⅱ-60</t>
+          <t>Ⅱ-70,Ⅱ-71</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>doc35§8,doc18 5-4(14),doc49§2-2</t>
+          <t>doc35§7-2(3)</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -9541,11 +9553,11 @@
         </is>
       </c>
       <c r="I165" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J165" s="4" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>記載待ち</t>
         </is>
       </c>
       <c r="K165" s="4" t="inlineStr">
@@ -9565,27 +9577,27 @@
       </c>
       <c r="B166" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>取組</t>
         </is>
       </c>
       <c r="C166" s="4" t="inlineStr">
         <is>
-          <t>村外事業所の通常の事業実施地域（重要事項説明書または指定情報）</t>
+          <t>難聴高齢者の早期発見・早期介入（20点中0点・全国平均6.9点）の実施可能性</t>
         </is>
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>別表第七。村内にほぼ事業所がないため、どの村外事業所が本村を事業実施地域に含むかが供給の範囲を決める。5-4(14)の24時間対応サービスの確保方策①の可否に直結する。</t>
+          <t>認知症の危険因子として難聴が位置づけられたことによる評価項目。健診等の機会を通じた把握と、補聴器等による介入の仕組みの可否。目標Ⅱの未取得分としては最大の20点。</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-60</t>
+          <t>Ⅱ-65,Ⅱ-68</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>doc49§2-4</t>
+          <t>doc35§7-2(6)</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -9602,12 +9614,12 @@
       <c r="J166" s="4" t="inlineStr"/>
       <c r="K166" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L166" s="4" t="inlineStr">
         <is>
-          <t>重要事項説明書・指定情報は公表されている。当方が拾う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -9617,27 +9629,27 @@
       </c>
       <c r="B167" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C167" s="4" t="inlineStr">
         <is>
-          <t>村外施設の入退所・待機の実績（介護老人福祉施設・介護老人保健施設・介護医療院）</t>
+          <t>中長期（令和17年度・令和22年度）の保険料をαの2案で示すことの可否</t>
         </is>
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>村外の介護老人福祉施設・介護老人保健施設・介護医療院について、本村の被保険者の入退所と待機の実績を、把握されている範囲でご提供いただきたい。5-4(13)の真に入所が必要と判断される被保険者の把握と、認知症対応型共同生活介護27人分の定員を変えるかどうかの判断に用いる。基本指針の別表 事項七が求める入所率・入退所の状況にあたる。</t>
+          <t>★改正法により中長期の見通しが必須の記載事項となった。αを23%据え置きとした場合は令和22年度6,883円、3年ごとに1ポイント上がるとした場合は8,379円。第9期計画は8,700円を見込んでいた。どちらを本文に置くか、あるいは幅として示すかを委員会にお諮りする。</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-60,Ⅱ-61</t>
+          <t>Ⅱ-64</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>doc49§2-4</t>
+          <t>doc35§7-2(1),doc18 5-11</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -9669,32 +9681,32 @@
       </c>
       <c r="B168" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>方針</t>
         </is>
       </c>
       <c r="C168" s="4" t="inlineStr">
         <is>
-          <t>医療介護連携に関する加算の算定状況（給付実績の加算別集計）</t>
+          <t>特定地域サービス・特定地域居宅サービス等事業を活用するかどうか</t>
         </is>
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>別表第十。施策4-3の在宅医療・介護連携の現状把握。村内に医療系の居宅サービス事業所がないため、加算の算定状況が連携の実態を示す唯一の量的な材料となる。★10/6：算定率は見える化の地域分析（医療介護連携）に収録されており、4加算について算定率と全国の中での位置（偏差値）を素案2-5に掲げた。基本指針の別表 事項十への対応も済んでいる。したがって残るのは算定の実数（件数）であり、算定率だけでは件数の少なさによる振れを判断できないため、給付実績の加算別の件数をご提供いただきたい。優先度はBからCに下げる。</t>
+          <t>★令和8年法律第51号により令和9年4月に新設される。本村は中山間・人口減少地域（特定地域）に該当する見込み。村内に事業所がないサービスへの対応手段になり得るが、活用の意向が未定のため素案5-4(4)では0で立てている。活用する場合は見込量・給付費・保険料のいずれも変わる。素案5-4(14)の24時間対応サービスの確保方策では、この活用を軸に据えている。特定地域の指定は村の意向を踏まえて都道府県が定めるため、計画に確保方策として記載することが手続の起点になる。</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-62</t>
+          <t>Ⅱ-56,Ⅱ-60</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
         <is>
-          <t>doc49§2-4</t>
+          <t>doc35§8,doc18 5-4(14),doc49§2-2</t>
         </is>
       </c>
       <c r="G168" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H168" s="4" t="inlineStr">
@@ -9702,8 +9714,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I168" s="4" t="inlineStr"/>
-      <c r="J168" s="4" t="inlineStr"/>
+      <c r="I168" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J168" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K168" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -9721,32 +9739,32 @@
       </c>
       <c r="B169" s="4" t="inlineStr">
         <is>
-          <t>判断</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C169" s="4" t="inlineStr">
         <is>
-          <t>保険料の所得段階を区分する合計所得金額の基準額（82.65万円）に係る条例改正の予定</t>
+          <t>村外事業所の通常の事業実施地域（重要事項説明書または指定情報）</t>
         </is>
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>5-7の所得段階の設定。政令改正済みで第1段階から第3段階の区分に用いる額が変わるため、村の条例改正の手続と時期を確認する。</t>
+          <t>別表第七。村内にほぼ事業所がないため、どの村外事業所が本村を事業実施地域に含むかが供給の範囲を決める。5-4(14)の24時間対応サービスの確保方策①の可否に直結する。</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-63</t>
+          <t>Ⅱ-60</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>doc49§2-2</t>
+          <t>doc49§2-4</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H169" s="4" t="inlineStr">
@@ -9754,22 +9772,16 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I169" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+      <c r="I169" s="4" t="inlineStr"/>
+      <c r="J169" s="4" t="inlineStr"/>
       <c r="K169" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L169" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>重要事項説明書・指定情報は公表されている。当方が拾う</t>
         </is>
       </c>
     </row>
@@ -9779,32 +9791,32 @@
       </c>
       <c r="B170" s="4" t="inlineStr">
         <is>
-          <t>判断</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C170" s="4" t="inlineStr">
         <is>
-          <t>算定上の保険料月額を条例上の基準額に置き換える方法（第9期の扱い）</t>
+          <t>村外施設の入退所・待機の実績（介護老人福祉施設・介護老人保健施設・介護医療院）</t>
         </is>
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>5-7。第9期の条例基準額6,700円が算定上の月額からどのように定められたかを確認し、第10期も同じ扱いとする。</t>
+          <t>村外の介護老人福祉施設・介護老人保健施設・介護医療院について、本村の被保険者の入退所と待機の実績を、把握されている範囲でご提供いただきたい。5-4(13)の真に入所が必要と判断される被保険者の把握と、認知症対応型共同生活介護27人分の定員を変えるかどうかの判断に用いる。基本指針の別表 事項七が求める入所率・入退所の状況にあたる。</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-63</t>
+          <t>Ⅱ-60,Ⅱ-61</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>doc49§2-2</t>
+          <t>doc49§2-4</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H170" s="4" t="inlineStr">
@@ -9812,22 +9824,16 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I170" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J170" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+      <c r="I170" s="4" t="inlineStr"/>
+      <c r="J170" s="4" t="inlineStr"/>
       <c r="K170" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L170" s="4" t="inlineStr">
         <is>
-          <t>第9期の条例で置き換えの方法を当方が確かめる。第10期の扱いのみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -9842,12 +9848,12 @@
       </c>
       <c r="C171" s="4" t="inlineStr">
         <is>
-          <t>高額医療合算介護サービス費の自動償還を実施するかどうか</t>
+          <t>医療介護連携に関する加算の算定状況（給付実績の加算別集計）</t>
         </is>
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>1-8の2および5-6の補助給付等。市町村の判断により手続を簡素化できるため、実施の意向を確認する。★10/7 優先度を上げた：国の推計ワークシートは高額医療合算介護サービス費等を3か年8,519千円（令和9年度2,817千円・令和10年度2,858千円・令和11年度2,844千円）で見込んでいる。当方は実績がないため0としていたが、国の出力は0ではない。実績が0で見込みが0でないのは、自動償還を実施していないために申請がなく実績が立っていないのか、入力の誤りなのかで意味が違う。保険料への影響は3か年8,519千円で月額約65円である。</t>
+          <t>別表第十。施策4-3の在宅医療・介護連携の現状把握。村内に医療系の居宅サービス事業所がないため、加算の算定状況が連携の実態を示す唯一の量的な材料となる。★10/6：算定率は見える化の地域分析（医療介護連携）に収録されており、4加算について算定率と全国の中での位置（偏差値）を素案2-5に掲げた。基本指針の別表 事項十への対応も済んでいる。したがって残るのは算定の実数（件数）であり、算定率だけでは件数の少なさによる振れを判断できないため、給付実績の加算別の件数をご提供いただきたい。優先度はBからCに下げる。</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
@@ -9857,12 +9863,12 @@
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>doc49§2-2,doc66§3-3</t>
+          <t>doc49§2-4</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H171" s="4" t="inlineStr">
@@ -9870,14 +9876,8 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I171" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="J171" s="4" t="inlineStr">
-        <is>
-          <t>仮置き</t>
-        </is>
-      </c>
+      <c r="I171" s="4" t="inlineStr"/>
+      <c r="J171" s="4" t="inlineStr"/>
       <c r="K171" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -9895,27 +9895,27 @@
       </c>
       <c r="B172" s="4" t="inlineStr">
         <is>
-          <t>成果品</t>
+          <t>判断</t>
         </is>
       </c>
       <c r="C172" s="4" t="inlineStr">
         <is>
-          <t>★計画書の分量を仕様書の目安100頁に収めるための削減案（A〜N）の採否</t>
+          <t>保険料の所得段階を区分する合計所得金額の基準額（82.65万円）に係る条例改正の予定</t>
         </is>
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>★10/20 方針修正：村より、素案を協議用と公表用に分け、協議用は論点をすべて含んで115頁を超えてよい、公表用は第9期の目次体系を踏襲し100頁前後・最大115頁とする、とのご指示をいただいた。本項の削減案A〜Nは公表用に適用する。協議用はいまの素案（本文129頁）のままとする。★公表用は第9期の目次体系に移し替えるため、削減案とは別に12節が落ちる（kouhyou_map.py）。移し替えた場合の推定は108頁（前付を含めて112頁）であったが、組んで測ると121頁で、許容115頁を6頁超えた。推定が9頁外れたのは、束ねるときに足す小見出し・基本目標の見出し・章の変わり目の改頁を推定が見ていなかったためである（doc109）。削減案A〜Eで113頁、＋H・Jで110頁、＋G・K・Lで107頁になる（いずれも実測）。公表用の紙面は scripts/jissoku_kouhyou.py で測る。★協議用の計画書は本文133頁＋前付4頁＝137頁である（10/24、令和5・6年度の決算を反映して測り直した）。協議用に分量の制約はない。公表用は案を1つも行わないと本文119頁＋前付4頁＝123頁で許容115頁を8頁超え、案A〜Eで115頁、案をすべて行うと110頁になる。第5章が第9期の12頁から36頁へ増えたことによる。増えたのは当方が算定の過程を示すために加えた「方法」「検証」「不確かさ」の記述であり、介護保険法第117条第2項が求める事項ではない。6つの案（A 算定の方法の説明／B 推計の不確かさ／C 見込量の自己点検／D 施策の見込量への反映／E 保険料の算定の構造と感応度／F 交付金の指標群の明細）をすべて行うと9頁減る。移し先は計画書とは別に渡す「算定の根拠」の綴りを想定している。★10/9：案を総当たりで試算した。案G（用語の解説の絞り込み。本文に一度も現れない8語を落とす）は0頁で、頁のためには行う意味がない。一方、10月6日に加えた図2点（2-5 医療と介護の連携の加算、5-8 給付適正化の取組別得点）を資料編に移すと2頁減る（案H）。★10/8：レビューの指摘により、第136回社会保障審議会介護保険部会（令和8年9月18日）の資料にもとづく記載を5か所に加えたため、本文が110頁から115頁へ5頁増えた（1-8の5 引き続き検討することとされた9事項／5-8(5) 帳票を活用した点検の充実と新たな点検手法／6-4⑦ 外れ値と点検の実施率の管理指標／2-5 介護経営DBの制度の概要／5-12(2) 据え置いた項目8件の追加。ただし5-12は計画書の頁数に算入していない）。あわせて削減案を2つ加えた。案J（1-8の3・1-8の5を資料編へ移す。2頁）と案K（2-5の介護経営DBの制度の概要を資料編へ移す。1頁）である。★10/9：5-7に基金の取崩しの3案（国の算定ベース）を加えたため本文が1頁増え116頁になった。あわせて案L（5-7の12パターン（当方の算定ベース）を別冊へ移す。1頁）を加えた。節の中に前提の異なる2つの案の組（国の算定ベースの3案と、当方の算定ベースの12のパターン）が並んでいるためである。これ以上は介護保険法第117条第2項が求める事項か前付（表紙・本書の見方・目次の4頁）に手を入れることになるため、当方からは勧めない。★10/10：村より「10頁程度の超過は許容する」とのご判断をいただいた。★10/10：障がい福祉計画との整合のため1-4・施策3-1・施策4-1・資9を加え、本文が116頁から118頁になった（計画間の整合は双方に無い状態であり、法定記載事項ではないが第2回策定委員会の前に要る。doc81）。到達できる最小はA〜Lの109頁となり、村が許容する110頁に対する余裕は3頁から1頁に減った。これ以上の加筆は、削減案の組み合わせでは許容に収まらなくなる。★10/10：docx を PDF に変換して紙面を実測した（doc83・doc84）。推定は送りによる空白を小さく見るため0〜3頁少なく出ることが分かったので、以下の頁数は組み合わせごとに実際に組んで数えた値である。何も行わない場合は124頁（本文120頁＋前付4頁）。A〜Eのみ118頁、＋F・Hで115頁、＋Jで112頁、A〜Lをすべて行うと110頁で許容ちょうどである。あわせて案M（資8 図表番号一覧を図表データ管理台帳へ移す。同じ内容を納品する電子媒体 04_図表データ の11_図表データ管理台帳.xlsx として別に納めており重複している）を加えた。A〜Mをすべて行うと109頁となり、許容110頁に1頁の余裕が生じる。なお游ゴシックが当方の環境に無く IPAゴシックで組んだ紙面であるため、村のWordでは±1〜2頁動き得る。110頁ちょうどの組み合わせ（A〜L）は余裕がないため、案Mまで行うことを当方からは勧めたい。案Mを行う場合は資9（関連計画との対照）を資8に、資10（中長期的な推計）を資9に繰り上げる。許容の範囲（110頁）に収めるには案A〜Mのうちいくつかを行う必要がある。どの案を行うかは村のご判断をいただきたい。案Hについては、2図とも資料編に移しても交付金の評価の裏づけとしては足りる。どれを削るかは村の判断であり、残す場合は目安を超えることのご了解をいただきたい。法定記載事項は削る候補にしていない（doc59）。★10/14：令和9年度改定の論点を反映して5-4・5-12・施策3-1・施策4-1・施策4-6・1-8に書き足したため、測り直した。推定はどの組み合わせでも動かなかったが、実測は6つとも1〜2頁増えていた（頁の境目は寡婦行の処理により推定と実測で違う）。何も行わない場合は127頁、A〜Eのみ119頁、＋F・Hで116頁、＋Jで113頁、A〜Lで111頁、A〜Mをすべて行って110頁である。許容110頁ちょうどとなり、余裕は1頁から0頁になった。これ以上の加筆は、削減案を1つ増やすか許容頁数のご判断をいただかないと収まらない。測った時点の素案の内容のハッシュを記録し、素案が変われば測り直す形に改めた。★10/15：全国介護保険担当課長会議資料・福島県高齢者居住安定確保計画・介護職員の必要数を照合して1-2・1-4・1-8の4・施策2-3・施策2-6・施策4-6・5-7・資9・資10・5-12に書き足したため、測り直した。推定は1〜2頁増えたが、実測は6つの組み合わせとも前と同じであった（頁の境目に余白があったため）。何も行わない場合129頁、A〜Mをすべて行って113頁で、許容115頁に対し2頁の余裕は変わらない。★10/15：村より「15頁は許容する」とのご判断をいただいたため、許容を115頁に改めた。あわせて令和8年法律第51号により加わった法定記載事項7件を反映し、中長期的な推計は本文ではなく資料編（資10）に置いた。測り直した結果、何も行わない場合は129頁、A〜Eのみ121頁、＋F・Hで119頁、＋Jで117頁、A〜Lで114頁、A〜Mをすべて行って113頁である。許容115頁に対し2頁の余裕がある。案Mを行う場合の繰り上げは、資9を資8に、資10を資9にとなる。★10/20：老人福祉法の原文（e-gov 法令検索）に当たり、同法上の13区分の対応表（4-6）・(1)の老人福祉施設の並びへの組み直し・第20条の8第9項の県の意見聴取（1-6）を加えたため、測り直した。協議用で何も行わない場合は135頁、A〜Eのみ127頁、＋F・Hで125頁、＋Jで122頁、A〜Lで119頁、A〜Mで118頁、A〜Nで117頁である。★A〜Mをすべて行っても許容115頁を1頁超える。加えたものは老人福祉法第20条の8が定めることを求めている事項であり、削る候補にできない。そこで案N（資7 主な参照資料を別冊へ移す）を設けた。節の末尾の注記が述べているとおり、各表・各図の出典は本文のそれぞれの箇所に示してあり、本表は区分ごとの索引にあたる。第9期計画にも対応する記載がなく、案Mと同じ性格の案である。A〜Nをすべて行うと115頁で、許容ちょうどとなる。案Nを行う場合は資8以降を1つずつ繰り上げる（案Mとあわせて行うと資9が資7になる）。★10/20（2回目）：交付金の獲得状況の整理（doc107）により5-9の算術の誤りを直したところ、推定は動かないのに実測が1頁増え、A〜Nで116頁となって許容115頁を1頁超えた。文を詰めても戻らず、改頁の位置が送られたことによるものと分かった。5-9の記述を算術の訂正だけにとどめ、新たに分かったことは成果品15（交付金の獲得状況と優先順位）に置いたところ、A〜Nで115頁に戻った。★余裕は0頁のままである。本文を1行足すだけで許容を超え得るため、これ以上の加筆は削減案をさらに設けるか許容頁数のご判断をいただきたい。当方からは資6（国の基本指針の別表11事項への対応）を別冊へ移す案を用意できる。当方の自己点検の記録であり、第9期計画には対応する記載がない。</t>
+          <t>5-7の所得段階の設定。政令改正済みで第1段階から第3段階の区分に用いる額が変わるため、村の条例改正の手続と時期を確認する。</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-113,Ⅱ-75</t>
+          <t>Ⅱ-63</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>doc59</t>
+          <t>doc49§2-2</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -9929,11 +9929,11 @@
         </is>
       </c>
       <c r="I172" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J172" s="4" t="inlineStr">
         <is>
-          <t>記載待ち</t>
+          <t>仮置き</t>
         </is>
       </c>
       <c r="K172" s="4" t="inlineStr">
@@ -9953,27 +9953,27 @@
       </c>
       <c r="B173" s="4" t="inlineStr">
         <is>
-          <t>体制</t>
+          <t>判断</t>
         </is>
       </c>
       <c r="C173" s="4" t="inlineStr">
         <is>
-          <t>★【社内】校了版（令和8年9月9日）の調査票Wordの提供（コードブックの作り直しに必要）</t>
+          <t>算定上の保険料月額を条例上の基準額に置き換える方法（第9期の扱い）</t>
         </is>
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>★校了版（令和8年9月9日）の調査票Word（ニーズ・在宅の2点）をご提供いただきたい。10/10 起票：発送が完了し集計分析に着手したため、入力データの論理チェックを作った（doc25 §7）。論理チェックは設問の番号・選択肢・分岐をコードブック（data/集計_コードブック.json）から引くが、現在のコードブックは令和8年9月4日版の調査票から作られている。実際に配られたのは9月9日の校了版である。版が違うと、鳴るべきものが鳴らず、鳴らなくてよいものが鳴る。具体的には①在宅調査の設問番号が全体に＋1（問0→問1）、②在宅 問10（旧問9）のサービスが12→9で記号もA〜I、③在宅 問8（旧問7・傷病）に「15.なし」「16.わからない」が追加、④ニーズ 問4(15) の削除、⑤ニーズ 問7(5)(8)(10) の選択肢の順序の入れ替えである（doc34 §4）。このため shukei_check.py は版を確かめ、食い違っていれば止まる仕組みとした（--暫定 で続行可）。★あわせて、9月4日版から作ったコードブックには読み取りの不備が7件残っている。C01 ZB_問8 が2回定義されている／C02 ニーズ問3(10)・在宅A問5・問8・問14・在宅B問7 の選択肢が拾えていない／C03 ニーズ問7(10) の列が13で選択肢が12。いずれも作り直しで同時に解消する。★お願いしたいのは、校了版の調査票Word（ニーズ・在宅の2点）の提供のみである。調査票は他メンバーの担当であり、当方では作成しない。受領後、当方でコードブックを作り直し（scripts/shukei_codebook.py の BUILT_FROM を校了版に改める）、派生変数 S01・S02 の参照設問も校了版の番号に直す。所要は半日である。★入力が始まってからでは、鳴らなかった件が「誤りがない」のか「版違いで鳴らなかった」のか区別できなくなる。入力の開始前に作り直すのが望ましい。</t>
+          <t>5-7。第9期の条例基準額6,700円が算定上の月額からどのように定められたかを確認し、第10期も同じ扱いとする。</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Ⅰ-104,Ⅰ-35,Ⅰ-36</t>
+          <t>Ⅱ-63</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>doc25§7,doc34§4</t>
+          <t>doc49§2-2</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -9987,21 +9987,21 @@
         </is>
       </c>
       <c r="I173" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J173" s="4" t="inlineStr">
         <is>
-          <t>社内</t>
+          <t>仮置き</t>
         </is>
       </c>
       <c r="K173" s="4" t="inlineStr">
         <is>
-          <t>Ｄ</t>
+          <t>Ｃ</t>
         </is>
       </c>
       <c r="L173" s="4" t="inlineStr">
         <is>
-          <t>村のご回答・内部データが必要</t>
+          <t>第9期の条例で置き換えの方法を当方が確かめる。第10期の扱いのみ伺う</t>
         </is>
       </c>
     </row>
@@ -10011,27 +10011,27 @@
       </c>
       <c r="B174" s="4" t="inlineStr">
         <is>
-          <t>計画構成</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C174" s="4" t="inlineStr">
         <is>
-          <t>★障がい福祉計画との連携の節を双方の計画に置くこと（障がい計画の側は新設済み。本計画は1-4の小見出しと資9で対応）</t>
+          <t>高額医療合算介護サービス費の自動償還を実施するかどうか</t>
         </is>
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>★障がい福祉計画との連携について、本計画側の置き方（1-4の小見出しと資9）でよいかをご確認いただきたい。10/10 起票：第8期障がい福祉計画・第4期障がい児福祉計画の素案を確認したところ、同計画の第7章（他計画との連携）は第3次健康21・第五次総合振興計画・こども計画の3計画を扱っており、高齢者福祉計画・介護保険事業計画との連携の節は置かれていなかった。一方、本計画の素案にも障がい福祉計画への参照がなかった（「障がい福祉計画」「障害福祉」「共生型」のいずれの語も素案に現れていなかった）。整合は片方向ではなく、双方に無い状態であった。★10/10 当方の対応：本計画の素案に次を加えた。①1-4（計画の位置づけ）に「障がい福祉計画との関係」を新設し、介護保険優先原則が給付の重なる部分についてのものであり年齢に達したことのみを理由に一律に移るものではないこと、実際に移る分だけを両計画の見込量へ同じ年度に反映することを書いた。②施策4-1（地域包括支援センターの機能強化）の取組に、40歳・65歳到達時の制度間の移行の調整、高齢の方が障がいのある家族を支える世帯の支援、福祉用具・補装具・住宅改修の移行の確認を加えた。③施策3-1（居宅サービスの確保）の取組に共生型サービスの協議を加えた。指標は協議した事業所数と指定を受けた事業所数に分けた（指定は事業者の判断であるため）。④資9（関連計画との対照）を新設し、8計画との重なりと、数で揃える3つの対象を一覧にした。★10/13 訂正：上記の「置かれていなかった」は令和8年10月4日の版を見て書いたもので、当たらない。障がい福祉計画は令和8年10月10日に第7章3として「北塩原村高齢者福祉計画・介護保険事業計画との連携」を新設していた（申し送り§2・正本 37939eed8c4d066f）。節の中身は両計画の位置づけ・受給者証の区分に応じたサービスの対応・年齢到達による移行・共生型サービス・成年後見制度利用支援事業の切り分けの5点である。したがって「どちらにも無い」ではなく「本計画の側に独立した節が無い」が現在の状態である。本計画は1-4の小見出し「障がい福祉計画との関係」と資9（関連計画との対照）で同じ事項を扱っているが、目次に現れる節としては置いていない。★ご確認いただきたいこと。・本計画にも独立した節として置くか、1-4の小見出しと資9のままとするか。独立した節とする場合は紙面が1頁増える（許容110頁に対し現在109頁。doc84）。・本計画の1-4・資9の記載の内容が、村のお考えと合っているか。障がい福祉担当からは「当方の節の構成をそのままお使いいただいて差し支えない」との回答を得ている（申し送り§3）。★当方の扱い：ご回答がない場合も、本計画の記載は1-4の小見出しと資9のままお示しする。障がい福祉計画の側は既に置かれているため、当方からの提案は不要になった。</t>
+          <t>1-8の2および5-6の補助給付等。市町村の判断により手続を簡素化できるため、実施の意向を確認する。★10/7 優先度を上げた：国の推計ワークシートは高額医療合算介護サービス費等を3か年8,519千円（令和9年度2,817千円・令和10年度2,858千円・令和11年度2,844千円）で見込んでいる。当方は実績がないため0としていたが、国の出力は0ではない。実績が0で見込みが0でないのは、自動償還を実施していないために申請がなく実績が立っていないのか、入力の誤りなのかで意味が違う。保険料への影響は3か年8,519千円で月額約65円である。</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72,Ⅱ-110</t>
+          <t>Ⅱ-62</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>素案1-4,資9,障がい福祉計画素案 第7章</t>
+          <t>doc49§2-2,doc66§3-3</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -10045,21 +10045,21 @@
         </is>
       </c>
       <c r="I174" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J174" s="4" t="inlineStr">
         <is>
-          <t>記載待ち</t>
+          <t>仮置き</t>
         </is>
       </c>
       <c r="K174" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L174" s="4" t="inlineStr">
         <is>
-          <t>障がい福祉計画との突合は済んでいる（doc89）。節の置き方のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -10069,27 +10069,27 @@
       </c>
       <c r="B175" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>成果品</t>
         </is>
       </c>
       <c r="C175" s="4" t="inlineStr">
         <is>
-          <t>★障がい福祉と介護保険で数を揃える3つの対象（第2号被保険者・65歳到達者・適用除外施設入所者）</t>
+          <t>★計画書の分量を仕様書の目安100頁に収めるための削減案（A〜N）の採否</t>
         </is>
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>★第2号被保険者・65歳到達者・適用除外施設入所者の3つについて、障がい福祉計画と同じ数を用いるための人数をご教示いただきたい。10/10 起票：両計画が同じ方を別々に数えることを防ぐため、次の3つを同じ名簿で確かめたい。本村の規模では1人の移行が両計画の見込量を動かすため、率ではなく個票による突合が要る。①第2号被保険者の認定者（本計画は各年度2人から3人の見込み・5-3）のうち、障がい福祉サービスの受給者または障害支援区分の認定者と重なる方がいるか。若年性認知症の方が含まれるか（素案4-7(2)は本村の該当者の状況を把握できていないとしている）。②令和9年度から令和11年度までに65歳に達する障がい福祉サービス利用者の一覧。到達の年月、現に利用しているサービスと量、介護保険に相当するサービスの有無、受入れの可否、障がい福祉として続けるサービス、共生型サービスの利用の可否、本人の意向。障がい福祉計画は個別積上げ方式を採っており、同計画の第1層（確定・高確度案件）に「令和9〜11年度の65歳到達者」が挙がっているため、同じ一覧を用いることができる。③介護保険の適用除外となる施設の入所者。指定障害者支援施設に生活介護および施設入所支援の支給決定を受けて入所している方は介護保険の被保険者とならない。障がい福祉計画は施設入所支援の利用者を扱っているため、同一の名簿で確かめたい。該当者がいる場合、本計画の第1号被保険者数が減り、保険料の分母が動く。★個人情報の取扱い：氏名は不要である。匿名の整理番号・生年月・区分・利用しているサービス・月の利用量で足りる（doc16 §5-2）。計画書には人数のみを載せる。★当方の扱い：ご回答がない場合、第2号被保険者は現在の見込み（各年度2人から3人）を据え置き、65歳到達による移行は0として算定し、適用除外の該当者はないものとして第1号被保険者数を置く。いずれも資9と5-12にその旨を明記する。</t>
+          <t>★10/20 方針修正：村より、素案を協議用と公表用に分け、協議用は論点をすべて含んで115頁を超えてよい、公表用は第9期の目次体系を踏襲し100頁前後・最大115頁とする、とのご指示をいただいた。本項の削減案A〜Nは公表用に適用する。協議用はいまの素案（本文129頁）のままとする。★公表用は第9期の目次体系に移し替えるため、削減案とは別に12節が落ちる（kouhyou_map.py）。移し替えた場合の推定は108頁（前付を含めて112頁）であったが、組んで測ると121頁で、許容115頁を6頁超えた。推定が9頁外れたのは、束ねるときに足す小見出し・基本目標の見出し・章の変わり目の改頁を推定が見ていなかったためである（doc109）。削減案A〜Eで118頁、＋H・Jで114頁、＋G・K・Lで112頁になる（いずれも実測。10/24 外部レビューの反映後）。公表用の紙面は scripts/jissoku_kouhyou.py で測る。★協議用の計画書は本文135頁＋前付4頁＝139頁である（10/24、外部レビュー Red Team の指摘を反映して測り直した）。協議用に分量の制約はない。公表用は案を1つも行わないと本文122頁＋前付4頁＝126頁で許容115頁を11頁超え、案A〜Eで118頁、案をすべて行うと112頁になる。第5章が第9期の12頁から36頁へ増えたことによる。増えたのは当方が算定の過程を示すために加えた「方法」「検証」「不確かさ」の記述であり、介護保険法第117条第2項が求める事項ではない。6つの案（A 算定の方法の説明／B 推計の不確かさ／C 見込量の自己点検／D 施策の見込量への反映／E 保険料の算定の構造と感応度／F 交付金の指標群の明細）をすべて行うと9頁減る。移し先は計画書とは別に渡す「算定の根拠」の綴りを想定している。★10/9：案を総当たりで試算した。案G（用語の解説の絞り込み。本文に一度も現れない8語を落とす）は0頁で、頁のためには行う意味がない。一方、10月6日に加えた図2点（2-5 医療と介護の連携の加算、5-8 給付適正化の取組別得点）を資料編に移すと2頁減る（案H）。★10/8：レビューの指摘により、第136回社会保障審議会介護保険部会（令和8年9月18日）の資料にもとづく記載を5か所に加えたため、本文が110頁から115頁へ5頁増えた（1-8の5 引き続き検討することとされた9事項／5-8(5) 帳票を活用した点検の充実と新たな点検手法／6-4⑦ 外れ値と点検の実施率の管理指標／2-5 介護経営DBの制度の概要／5-12(2) 据え置いた項目8件の追加。ただし5-12は計画書の頁数に算入していない）。あわせて削減案を2つ加えた。案J（1-8の3・1-8の5を資料編へ移す。2頁）と案K（2-5の介護経営DBの制度の概要を資料編へ移す。1頁）である。★10/9：5-7に基金の取崩しの3案（国の算定ベース）を加えたため本文が1頁増え116頁になった。あわせて案L（5-7の12パターン（当方の算定ベース）を別冊へ移す。1頁）を加えた。節の中に前提の異なる2つの案の組（国の算定ベースの3案と、当方の算定ベースの12のパターン）が並んでいるためである。これ以上は介護保険法第117条第2項が求める事項か前付（表紙・本書の見方・目次の4頁）に手を入れることになるため、当方からは勧めない。★10/10：村より「10頁程度の超過は許容する」とのご判断をいただいた。★10/10：障がい福祉計画との整合のため1-4・施策3-1・施策4-1・資9を加え、本文が116頁から118頁になった（計画間の整合は双方に無い状態であり、法定記載事項ではないが第2回策定委員会の前に要る。doc81）。到達できる最小はA〜Lの109頁となり、村が許容する110頁に対する余裕は3頁から1頁に減った。これ以上の加筆は、削減案の組み合わせでは許容に収まらなくなる。★10/10：docx を PDF に変換して紙面を実測した（doc83・doc84）。推定は送りによる空白を小さく見るため0〜3頁少なく出ることが分かったので、以下の頁数は組み合わせごとに実際に組んで数えた値である。何も行わない場合は124頁（本文120頁＋前付4頁）。A〜Eのみ118頁、＋F・Hで115頁、＋Jで112頁、A〜Lをすべて行うと110頁で許容ちょうどである。あわせて案M（資8 図表番号一覧を図表データ管理台帳へ移す。同じ内容を納品する電子媒体 04_図表データ の11_図表データ管理台帳.xlsx として別に納めており重複している）を加えた。A〜Mをすべて行うと109頁となり、許容110頁に1頁の余裕が生じる。なお游ゴシックが当方の環境に無く IPAゴシックで組んだ紙面であるため、村のWordでは±1〜2頁動き得る。110頁ちょうどの組み合わせ（A〜L）は余裕がないため、案Mまで行うことを当方からは勧めたい。案Mを行う場合は資9（関連計画との対照）を資8に、資10（中長期的な推計）を資9に繰り上げる。許容の範囲（110頁）に収めるには案A〜Mのうちいくつかを行う必要がある。どの案を行うかは村のご判断をいただきたい。案Hについては、2図とも資料編に移しても交付金の評価の裏づけとしては足りる。どれを削るかは村の判断であり、残す場合は目安を超えることのご了解をいただきたい。法定記載事項は削る候補にしていない（doc59）。★10/14：令和9年度改定の論点を反映して5-4・5-12・施策3-1・施策4-1・施策4-6・1-8に書き足したため、測り直した。推定はどの組み合わせでも動かなかったが、実測は6つとも1〜2頁増えていた（頁の境目は寡婦行の処理により推定と実測で違う）。何も行わない場合は127頁、A〜Eのみ119頁、＋F・Hで116頁、＋Jで113頁、A〜Lで111頁、A〜Mをすべて行って110頁である。許容110頁ちょうどとなり、余裕は1頁から0頁になった。これ以上の加筆は、削減案を1つ増やすか許容頁数のご判断をいただかないと収まらない。測った時点の素案の内容のハッシュを記録し、素案が変われば測り直す形に改めた。★10/15：全国介護保険担当課長会議資料・福島県高齢者居住安定確保計画・介護職員の必要数を照合して1-2・1-4・1-8の4・施策2-3・施策2-6・施策4-6・5-7・資9・資10・5-12に書き足したため、測り直した。推定は1〜2頁増えたが、実測は6つの組み合わせとも前と同じであった（頁の境目に余白があったため）。何も行わない場合129頁、A〜Mをすべて行って113頁で、許容115頁に対し2頁の余裕は変わらない。★10/15：村より「15頁は許容する」とのご判断をいただいたため、許容を115頁に改めた。あわせて令和8年法律第51号により加わった法定記載事項7件を反映し、中長期的な推計は本文ではなく資料編（資10）に置いた。測り直した結果、何も行わない場合は129頁、A〜Eのみ121頁、＋F・Hで119頁、＋Jで117頁、A〜Lで114頁、A〜Mをすべて行って113頁である。許容115頁に対し2頁の余裕がある。案Mを行う場合の繰り上げは、資9を資8に、資10を資9にとなる。★10/20：老人福祉法の原文（e-gov 法令検索）に当たり、同法上の13区分の対応表（4-6）・(1)の老人福祉施設の並びへの組み直し・第20条の8第9項の県の意見聴取（1-6）を加えたため、測り直した。協議用で何も行わない場合は135頁、A〜Eのみ127頁、＋F・Hで125頁、＋Jで122頁、A〜Lで119頁、A〜Mで118頁、A〜Nで117頁である。★A〜Mをすべて行っても許容115頁を1頁超える。加えたものは老人福祉法第20条の8が定めることを求めている事項であり、削る候補にできない。そこで案N（資7 主な参照資料を別冊へ移す）を設けた。節の末尾の注記が述べているとおり、各表・各図の出典は本文のそれぞれの箇所に示してあり、本表は区分ごとの索引にあたる。第9期計画にも対応する記載がなく、案Mと同じ性格の案である。A〜Nをすべて行うと115頁で、許容ちょうどとなる。案Nを行う場合は資8以降を1つずつ繰り上げる（案Mとあわせて行うと資9が資7になる）。★10/20（2回目）：交付金の獲得状況の整理（doc107）により5-9の算術の誤りを直したところ、推定は動かないのに実測が1頁増え、A〜Nで116頁となって許容115頁を1頁超えた。文を詰めても戻らず、改頁の位置が送られたことによるものと分かった。5-9の記述を算術の訂正だけにとどめ、新たに分かったことは成果品15（交付金の獲得状況と優先順位）に置いたところ、A〜Nで115頁に戻った。★余裕は0頁のままである。本文を1行足すだけで許容を超え得るため、これ以上の加筆は削減案をさらに設けるか許容頁数のご判断をいただきたい。当方からは資6（国の基本指針の別表11事項への対応）を別冊へ移す案を用意できる。当方の自己点検の記録であり、第9期計画には対応する記載がない。</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72,Ⅱ-56,Ⅱ-62</t>
+          <t>Ⅱ-113,Ⅱ-75</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>素案資9,素案5-1,素案5-3,障がい福祉計画素案 第5章2</t>
+          <t>doc59</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -10103,11 +10103,11 @@
         </is>
       </c>
       <c r="I175" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J175" s="4" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>記載待ち</t>
         </is>
       </c>
       <c r="K175" s="4" t="inlineStr">
@@ -10127,27 +10127,27 @@
       </c>
       <c r="B176" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>体制</t>
         </is>
       </c>
       <c r="C176" s="4" t="inlineStr">
         <is>
-          <t>★法が定めることを求めている2つの量が空欄である（老人福祉事業の量19事業・地域支援事業の量10事業）</t>
+          <t>★【社内】校了版（令和8年9月9日）の調査票Wordの提供（コードブックの作り直しに必要）</t>
         </is>
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>★老人福祉事業19事業と地域支援事業10事業について、令和5年度から令和7年度までの実績をご提供いただきたい。10/12 起票：次の2つは、法が計画に定めることを求めている事項でありながら、令和9年度から令和11年度までの量が空欄のままである。仮定を置いて進めることができない。①老人福祉法第20条の8第2項の「確保すべき老人福祉事業の量の目標」（素案4-6）。20事業のうち19事業が空欄である（養護老人ホーム措置・軽費老人ホーム・生活支援ハウス、緊急通報システム・除雪支援・移動支援・寝具洗濯・訪問理美容・家族介護者リフレッシュ・介護用品の支給ほか村単独17事業）。確保の方策（該当施策）は記載済みである。②介護保険法第117条第2項第2号の地域支援事業の量の見込み（素案5-5）。量の表19事業のうち10事業、事業費の表12区分のうち7区分が空欄である（訪問型・通所型サービス（従前相当）、介護予防ケアマネジメント、総合相談支援、認知症初期集中支援推進事業、認知症カフェ、認知症サポーター養成講座ほか。包括的支援事業（社会保障充実分）の4つの内訳は決算の内訳が未受領のため実績も置けない）。いずれも令和5年度から令和7年度までの実績をご提供いただければ、本計画で量を立てられる。★当方の扱い：ご回答がない場合、空欄のまま計画書に載せることになる。法が定めることを求めている事項であるため、空欄のままでは計画として成り立たない。素案5-12に空欄であることと確定の条件を明記している。</t>
+          <t>★校了版（令和8年9月9日）の調査票Word（ニーズ・在宅の2点）をご提供いただきたい。10/10 起票：発送が完了し集計分析に着手したため、入力データの論理チェックを作った（doc25 §7）。論理チェックは設問の番号・選択肢・分岐をコードブック（data/集計_コードブック.json）から引くが、現在のコードブックは令和8年9月4日版の調査票から作られている。実際に配られたのは9月9日の校了版である。版が違うと、鳴るべきものが鳴らず、鳴らなくてよいものが鳴る。具体的には①在宅調査の設問番号が全体に＋1（問0→問1）、②在宅 問10（旧問9）のサービスが12→9で記号もA〜I、③在宅 問8（旧問7・傷病）に「15.なし」「16.わからない」が追加、④ニーズ 問4(15) の削除、⑤ニーズ 問7(5)(8)(10) の選択肢の順序の入れ替えである（doc34 §4）。このため shukei_check.py は版を確かめ、食い違っていれば止まる仕組みとした（--暫定 で続行可）。★あわせて、9月4日版から作ったコードブックには読み取りの不備が7件残っている。C01 ZB_問8 が2回定義されている／C02 ニーズ問3(10)・在宅A問5・問8・問14・在宅B問7 の選択肢が拾えていない／C03 ニーズ問7(10) の列が13で選択肢が12。いずれも作り直しで同時に解消する。★お願いしたいのは、校了版の調査票Word（ニーズ・在宅の2点）の提供のみである。調査票は他メンバーの担当であり、当方では作成しない。受領後、当方でコードブックを作り直し（scripts/shukei_codebook.py の BUILT_FROM を校了版に改める）、派生変数 S01・S02 の参照設問も校了版の番号に直す。所要は半日である。★入力が始まってからでは、鳴らなかった件が「誤りがない」のか「版違いで鳴らなかった」のか区別できなくなる。入力の開始前に作り直すのが望ましい。</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-53,Ⅱ-54,Ⅱ-110</t>
+          <t>Ⅰ-104,Ⅰ-35,Ⅰ-36</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>素案4-6,素案5-5,素案5-12,doc32§4-1</t>
+          <t>doc25§7,doc34§4</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -10161,11 +10161,11 @@
         </is>
       </c>
       <c r="I176" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J176" s="4" t="inlineStr">
         <is>
-          <t>停止</t>
+          <t>社内</t>
         </is>
       </c>
       <c r="K176" s="4" t="inlineStr">
@@ -10185,27 +10185,27 @@
       </c>
       <c r="B177" s="4" t="inlineStr">
         <is>
-          <t>データ</t>
+          <t>計画構成</t>
         </is>
       </c>
       <c r="C177" s="4" t="inlineStr">
         <is>
-          <t>★共生型サービスの事業所の名寄せ（障がい福祉と介護保険で同一の事業所か）</t>
+          <t>★障がい福祉計画との連携の節を双方の計画に置くこと（障がい計画の側は新設済み。本計画は1-4の小見出しと資9で対応）</t>
         </is>
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>★村内の共生型サービスの事業所が障がい福祉と介護保険で同一のものかを、事業所番号でご確認いただきたい。10/12 起票：村内の事業所を事業所番号で突き合わせ、同一の事業所が両計画に二重に現れていないかを確かめたい。障がい福祉計画は村内に居宅介護1か所・重度訪問介護1か所・生活介護1か所（生活介護は基準該当）としており、本計画は訪問介護1か所・通所介護2か所としている（素案2-5）。社会福祉協議会が両方を担っている場合、両計画の事業所数を足すと実態の倍になる。本計画の施策3-1は「共生型サービスについて協議した事業所数 0か所→村内3か所」を指標に置いているが、すでに実質的な共生型の提供がある場合、現状値0は実態と合わない。★10/13 追記：障がい福祉計画の担当から、施策3-1の目標値「村内3か所」が何を数えたものかの照会を受けた（申し送り§4⑤）。村内の介護サービス事業所7か所のうち共生型サービスの対象となる種類を提供している訪問介護1・通所介護2の3か所を数えたものである旨を回答し、施策3-1の注記と資9に明記した。障がい福祉の3か所とは別に数えている。また同担当の調べでは、北塩原村社会福祉協議会が障がい者居宅介護・生活介護を既に実施しており生活介護は基準該当障害福祉サービスとして提供されているとの外部レビューがあるが、同担当は原典を持たず未確認としている。事実であれば協議の相手は3か所より少なくなるため、事業所番号による名寄せの結果により目標値を見直す。★当方の扱い：ご回答がない場合、施策3-1の現状値は0のまま据え置き、指標の見直しが要ることを5-12に明記する。</t>
+          <t>★障がい福祉計画との連携について、本計画側の置き方（1-4の小見出しと資9）でよいかをご確認いただきたい。10/10 起票：第8期障がい福祉計画・第4期障がい児福祉計画の素案を確認したところ、同計画の第7章（他計画との連携）は第3次健康21・第五次総合振興計画・こども計画の3計画を扱っており、高齢者福祉計画・介護保険事業計画との連携の節は置かれていなかった。一方、本計画の素案にも障がい福祉計画への参照がなかった（「障がい福祉計画」「障害福祉」「共生型」のいずれの語も素案に現れていなかった）。整合は片方向ではなく、双方に無い状態であった。★10/10 当方の対応：本計画の素案に次を加えた。①1-4（計画の位置づけ）に「障がい福祉計画との関係」を新設し、介護保険優先原則が給付の重なる部分についてのものであり年齢に達したことのみを理由に一律に移るものではないこと、実際に移る分だけを両計画の見込量へ同じ年度に反映することを書いた。②施策4-1（地域包括支援センターの機能強化）の取組に、40歳・65歳到達時の制度間の移行の調整、高齢の方が障がいのある家族を支える世帯の支援、福祉用具・補装具・住宅改修の移行の確認を加えた。③施策3-1（居宅サービスの確保）の取組に共生型サービスの協議を加えた。指標は協議した事業所数と指定を受けた事業所数に分けた（指定は事業者の判断であるため）。④資9（関連計画との対照）を新設し、8計画との重なりと、数で揃える3つの対象を一覧にした。★10/13 訂正：上記の「置かれていなかった」は令和8年10月4日の版を見て書いたもので、当たらない。障がい福祉計画は令和8年10月10日に第7章3として「北塩原村高齢者福祉計画・介護保険事業計画との連携」を新設していた（申し送り§2・正本 37939eed8c4d066f）。節の中身は両計画の位置づけ・受給者証の区分に応じたサービスの対応・年齢到達による移行・共生型サービス・成年後見制度利用支援事業の切り分けの5点である。したがって「どちらにも無い」ではなく「本計画の側に独立した節が無い」が現在の状態である。本計画は1-4の小見出し「障がい福祉計画との関係」と資9（関連計画との対照）で同じ事項を扱っているが、目次に現れる節としては置いていない。★ご確認いただきたいこと。・本計画にも独立した節として置くか、1-4の小見出しと資9のままとするか。独立した節とする場合は紙面が1頁増える（許容110頁に対し現在109頁。doc84）。・本計画の1-4・資9の記載の内容が、村のお考えと合っているか。障がい福祉担当からは「当方の節の構成をそのままお使いいただいて差し支えない」との回答を得ている（申し送り§3）。★当方の扱い：ご回答がない場合も、本計画の記載は1-4の小見出しと資9のままお示しする。障がい福祉計画の側は既に置かれているため、当方からの提案は不要になった。</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72,Ⅱ-54</t>
+          <t>Ⅱ-72,Ⅱ-110</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>素案 施策3-1,素案2-5,障がい福祉計画の整合Ｋ-5</t>
+          <t>素案1-4,資9,障がい福祉計画素案 第7章</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -10219,11 +10219,11 @@
         </is>
       </c>
       <c r="I177" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J177" s="4" t="inlineStr">
         <is>
-          <t>仮置き</t>
+          <t>記載待ち</t>
         </is>
       </c>
       <c r="K177" s="4" t="inlineStr">
@@ -10233,7 +10233,7 @@
       </c>
       <c r="L177" s="4" t="inlineStr">
         <is>
-          <t>共生型サービスの事業所は介護サービス情報公表システムで当方が名寄せする</t>
+          <t>障がい福祉計画との突合は済んでいる（doc89）。節の置き方のみ伺う</t>
         </is>
       </c>
     </row>
@@ -10248,27 +10248,27 @@
       </c>
       <c r="C178" s="4" t="inlineStr">
         <is>
-          <t>★新高額障害福祉サービス等給付費の対象となる介護保険サービスの種類と本村の該当者</t>
+          <t>★障がい福祉と介護保険で数を揃える3つの対象（第2号被保険者・65歳到達者・適用除外施設入所者）</t>
         </is>
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>★10/12 起票：65歳に達する前の5年間に相当する障害福祉サービスの支給決定を受けていた方などについて、介護保険の利用者負担が償還される制度である。償還の対象となる介護保険サービスの種類は限られており、障がい福祉計画は介護予防サービスを対象外としている。本村に該当者がいるかをご教示いただきたい。★10/13 追記：償還の対象となる介護保険サービスは訪問介護・通所介護・短期入所生活介護・地域密着型通所介護・小規模多機能型居宅介護の5種で介護予防サービスは対象外であることが、障がい福祉計画の担当の整理により判明した（申し送り§4②。根拠は障害者総合支援法施行令第43条の5第6項ほか）。要件4つとあわせて資9に明記し、申請の窓口が介護保険側であることから施策4-1に案内の取組を置いた。残るのは本村の該当者の有無のみである。償還は障がい福祉の経費であり本計画の給付費・保険料には算入しないが、対象となるサービスが本計画の見込量のどれに当たるかは両計画で揃える必要がある（素案資9）。★当方の扱い：ご回答がない場合、該当者はないものとして扱い、資9に制度の説明のみを載せる。</t>
+          <t>★第2号被保険者・65歳到達者・適用除外施設入所者の3つについて、障がい福祉計画と同じ数を用いるための人数をご教示いただきたい。10/10 起票：両計画が同じ方を別々に数えることを防ぐため、次の3つを同じ名簿で確かめたい。本村の規模では1人の移行が両計画の見込量を動かすため、率ではなく個票による突合が要る。①第2号被保険者の認定者（本計画は各年度2人から3人の見込み・5-3）のうち、障がい福祉サービスの受給者または障害支援区分の認定者と重なる方がいるか。若年性認知症の方が含まれるか（素案4-7(2)は本村の該当者の状況を把握できていないとしている）。②令和9年度から令和11年度までに65歳に達する障がい福祉サービス利用者の一覧。到達の年月、現に利用しているサービスと量、介護保険に相当するサービスの有無、受入れの可否、障がい福祉として続けるサービス、共生型サービスの利用の可否、本人の意向。障がい福祉計画は個別積上げ方式を採っており、同計画の第1層（確定・高確度案件）に「令和9〜11年度の65歳到達者」が挙がっているため、同じ一覧を用いることができる。③介護保険の適用除外となる施設の入所者。指定障害者支援施設に生活介護および施設入所支援の支給決定を受けて入所している方は介護保険の被保険者とならない。障がい福祉計画は施設入所支援の利用者を扱っているため、同一の名簿で確かめたい。該当者がいる場合、本計画の第1号被保険者数が減り、保険料の分母が動く。★個人情報の取扱い：氏名は不要である。匿名の整理番号・生年月・区分・利用しているサービス・月の利用量で足りる（doc16 §5-2）。計画書には人数のみを載せる。★当方の扱い：ご回答がない場合、第2号被保険者は現在の見込み（各年度2人から3人）を据え置き、65歳到達による移行は0として算定し、適用除外の該当者はないものとして第1号被保険者数を置く。いずれも資9と5-12にその旨を明記する。</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72,Ⅱ-56</t>
+          <t>Ⅱ-72,Ⅱ-56,Ⅱ-62</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>素案資9,障がい福祉計画の整合Ｋ-6</t>
+          <t>素案資9,素案5-1,素案5-3,障がい福祉計画素案 第5章2</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H178" s="4" t="inlineStr">
@@ -10276,8 +10276,14 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I178" s="4" t="inlineStr"/>
-      <c r="J178" s="4" t="inlineStr"/>
+      <c r="I178" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J178" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
       <c r="K178" s="4" t="inlineStr">
         <is>
           <t>Ｄ</t>
@@ -10300,27 +10306,27 @@
       </c>
       <c r="C179" s="4" t="inlineStr">
         <is>
-          <t>★成年後見制度利用支援事業は両計画で別の事業である旨の注記と、本計画側の任意事業としての助成の実績</t>
+          <t>★法が定めることを求めている2つの量が空欄である（老人福祉事業の量19事業・地域支援事業の量10事業）</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>本村の成年後見制度の利用者4人（令和8年7月）のうち、障害者手帳の所持者または障がい福祉サービスの利用者が何人かをご教示いただきたい。障がい福祉計画の側からも同じ内容を照会しているため、回答は一度で足りる。助成の件数は「家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績」、要綱の対象範囲は「成年後見制度利用支援事業の要綱の対象範囲」でそれぞれ既に照会しているため、本件では重ねない。★10/13 起票：当初は「両計画で指標名を揃えること」としていたが、障がい福祉計画の担当から、揃えるのではなく別の事業であることを注記するよう勧められた。同じ名前の事業が障害者総合支援法第77条第1項第4号の地域生活支援事業と、介護保険法第115条の45第3項第3号の地域支援事業（任意事業）の両方にあり、指標名を揃えると両計画の数を足し合わせたときに村全体の取組が実際より多く見える。この勧めに従い、素案の施策4-7と資9に別の事業である旨の注記を置いた。あわせて施策一覧の条文が「介保法115条の45第2項第2号」となっていた誤りを第3項第3号に正した（第2項第2号は権利擁護事業であって別の事業である）。本計画の指標「成年後見制度の利用者数4人」は村全体の制度の利用者数であり、助成の件数ではない。助成の件数は5-5の任意事業の実績が未受領のため置けていない。★当方の扱い：ご回答がない場合、助成の件数は5-12の空欄として掲げ、注記のみで両計画の切り分けを示す。</t>
+          <t>★老人福祉事業19事業と地域支援事業10事業について、令和5年度から令和7年度までの実績をご提供いただきたい。10/12 起票：次の2つは、法が計画に定めることを求めている事項でありながら、令和9年度から令和11年度までの量が空欄のままである。仮定を置いて進めることができない。①老人福祉法第20条の8第2項の「確保すべき老人福祉事業の量の目標」（素案4-6）。20事業のうち19事業が空欄である（養護老人ホーム措置・軽費老人ホーム・生活支援ハウス、緊急通報システム・除雪支援・移動支援・寝具洗濯・訪問理美容・家族介護者リフレッシュ・介護用品の支給ほか村単独17事業）。確保の方策（該当施策）は記載済みである。②介護保険法第117条第2項第2号の地域支援事業の量の見込み（素案5-5）。量の表19事業のうち10事業、事業費の表12区分のうち7区分が空欄である（訪問型・通所型サービス（従前相当）、介護予防ケアマネジメント、総合相談支援、認知症初期集中支援推進事業、認知症カフェ、認知症サポーター養成講座ほか。包括的支援事業（社会保障充実分）の4つの内訳は決算の内訳が未受領のため実績も置けない）。いずれも令和5年度から令和7年度までの実績をご提供いただければ、本計画で量を立てられる。★当方の扱い：ご回答がない場合、空欄のまま計画書に載せることになる。法が定めることを求めている事項であるため、空欄のままでは計画として成り立たない。素案5-12に空欄であることと確定の条件を明記している。</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-69,Ⅱ-72</t>
+          <t>Ⅱ-53,Ⅱ-54,Ⅱ-110</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>素案4-7,資9,5-5,障がい福祉計画 照会Ｋ-9</t>
+          <t>素案4-6,素案5-5,素案5-12,doc32§4-1</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H179" s="4" t="inlineStr">
@@ -10328,16 +10334,22 @@
           <t>未依頼</t>
         </is>
       </c>
-      <c r="I179" s="4" t="inlineStr"/>
-      <c r="J179" s="4" t="inlineStr"/>
+      <c r="I179" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="J179" s="4" t="inlineStr">
+        <is>
+          <t>停止</t>
+        </is>
+      </c>
       <c r="K179" s="4" t="inlineStr">
         <is>
-          <t>Ｃ</t>
+          <t>Ｄ</t>
         </is>
       </c>
       <c r="L179" s="4" t="inlineStr">
         <is>
-          <t>両計画で別の事業であることは当方が条文で整理した（doc89）。助成の実績のみ伺う</t>
+          <t>村のご回答・内部データが必要</t>
         </is>
       </c>
     </row>
@@ -10347,27 +10359,27 @@
       </c>
       <c r="B180" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C180" s="4" t="inlineStr">
         <is>
-          <t>★福島県高齢者居住安定確保計画の改定の予定と、本村の住まいの計画の有無</t>
+          <t>★共生型サービスの事業所の名寄せ（障がい福祉と介護保険で同一の事業所か）</t>
         </is>
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>★福島県高齢者居住安定確保計画の改定の予定と、本村の住まいの計画の有無をご確認いただきたい。10/15 起票：福島県高齢者居住安定確保計画（令和4年3月）を受領した。介護保険法第117条は、本計画が他の法律の規定による計画であって要介護者等の保健・医療・福祉または居住に関する事項を定めるものと調和が保たれたものであることを求めている。本計画はこれまで条文としてこれを引いておらず、住まいの計画との関係も書いていなかった（素案1-4・資9に追加した）。県計画は会津地域について、中山間地域では高齢者が集まって住む住宅が少ないこと、高齢者が除雪できず生活に支障をきたす場合があることを課題に挙げ、冬期間における除雪等の支援および集住の促進を対策としている。本村の施策2-6（除雪）・施策2-3（住まい）はこれに対応する。ただし県計画の期間は令和4年度から令和8年度までであり、本計画の期間が始まる前に満了する。次の2点をご確認いただきたい。・県計画の改定の予定（県の高齢者福祉計画・介護保険事業支援計画および住生活基本計画の改定に合わせて改定される見込み）と、会津地域の対策の変更の有無。・本村が市町村高齢者居住安定確保計画および市町村賃貸住宅供給促進計画を定めているか。定めている場合は調和の相手方になる。あわせて、県計画が挙げる住宅セーフティネット制度を活用した家賃・家賃債務保証料の補助、高齢者向け住宅への改修補助について、本村での活用の可否を住宅担当部局にご確認いただきたい。</t>
+          <t>★村内の共生型サービスの事業所が障がい福祉と介護保険で同一のものかを、事業所番号でご確認いただきたい。10/12 起票：村内の事業所を事業所番号で突き合わせ、同一の事業所が両計画に二重に現れていないかを確かめたい。障がい福祉計画は村内に居宅介護1か所・重度訪問介護1か所・生活介護1か所（生活介護は基準該当）としており、本計画は訪問介護1か所・通所介護2か所としている（素案2-5）。社会福祉協議会が両方を担っている場合、両計画の事業所数を足すと実態の倍になる。本計画の施策3-1は「共生型サービスについて協議した事業所数 0か所→村内3か所」を指標に置いているが、すでに実質的な共生型の提供がある場合、現状値0は実態と合わない。★10/13 追記：障がい福祉計画の担当から、施策3-1の目標値「村内3か所」が何を数えたものかの照会を受けた（申し送り§4⑤）。村内の介護サービス事業所7か所のうち共生型サービスの対象となる種類を提供している訪問介護1・通所介護2の3か所を数えたものである旨を回答し、施策3-1の注記と資9に明記した。障がい福祉の3か所とは別に数えている。また同担当の調べでは、北塩原村社会福祉協議会が障がい者居宅介護・生活介護を既に実施しており生活介護は基準該当障害福祉サービスとして提供されているとの外部レビューがあるが、同担当は原典を持たず未確認としている。事実であれば協議の相手は3か所より少なくなるため、事業所番号による名寄せの結果により目標値を見直す。★当方の扱い：ご回答がない場合、施策3-1の現状値は0のまま据え置き、指標の見直しが要ることを5-12に明記する。</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-56</t>
+          <t>Ⅱ-72,Ⅱ-54</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>doc94</t>
+          <t>素案 施策3-1,素案2-5,障がい福祉計画の整合Ｋ-5</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -10395,7 +10407,7 @@
       </c>
       <c r="L180" s="4" t="inlineStr">
         <is>
-          <t>県計画は受領済みであり、会津地域の対策は当方が読む（doc94）。改定の予定のみ伺う</t>
+          <t>共生型サービスの事業所は介護サービス情報公表システムで当方が名寄せする</t>
         </is>
       </c>
     </row>
@@ -10405,27 +10417,27 @@
       </c>
       <c r="B181" s="4" t="inlineStr">
         <is>
-          <t>方針</t>
+          <t>データ</t>
         </is>
       </c>
       <c r="C181" s="4" t="inlineStr">
         <is>
-          <t>福島県の介護人材需給推計への本村の関わり方</t>
+          <t>★新高額障害福祉サービス等給付費の対象となる介護保険サービスの種類と本村の該当者</t>
         </is>
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>★本村の見込量が福島県の介護人材需給推計に用いられる時期と、県から本村への照会の有無をご確認いただきたい。10/15 起票：全国介護保険担当課長会議資料（令和8年7月15日）および第9期計画に基づく介護職員の必要数（別紙5）を受領した。介護人材の需給推計は都道府県が行うものであり、都道府県は人材推計ワークシートにより管内保険者の第10期計画のサービス見込量等に基づいて令和22年度（2040年度）までの需給推計を行う。需要が供給を上回る場合には、関係団体等で構成する会議体において入職経路別（①介護福祉士養成施設等 ②他分野 ③外国人介護人材）の供給数の目標を定める。ワークシートは秋頃と令和9年1〜2月頃の2回配布され、最終報告は令和9年4月の1週目が想定されている。本計画の見込量（5-4）と中長期的な推計（資10）がその算定の基礎になるため、本村の見込量が県の推計に用いられる時期と、県から本村への照会の有無をご確認いただきたい。別紙5（第9期計画に基づく都道府県別の推計）によれば、福島県の介護職員の必要数は令和22年（2040年）度に36,851人で、現状推移を見込んだ職員数29,347人を7,504人上回る（令和4年度の実績は33,401人）。第10期の推計は県が改めて行うため、この値は参照にとどめ、素案には数値を載せず 施策4-6に県への協力を加えた。</t>
+          <t>★10/12 起票：65歳に達する前の5年間に相当する障害福祉サービスの支給決定を受けていた方などについて、介護保険の利用者負担が償還される制度である。償還の対象となる介護保険サービスの種類は限られており、障がい福祉計画は介護予防サービスを対象外としている。本村に該当者がいるかをご教示いただきたい。★10/13 追記：償還の対象となる介護保険サービスは訪問介護・通所介護・短期入所生活介護・地域密着型通所介護・小規模多機能型居宅介護の5種で介護予防サービスは対象外であることが、障がい福祉計画の担当の整理により判明した（申し送り§4②。根拠は障害者総合支援法施行令第43条の5第6項ほか）。要件4つとあわせて資9に明記し、申請の窓口が介護保険側であることから施策4-1に案内の取組を置いた。残るのは本村の該当者の有無のみである。償還は障がい福祉の経費であり本計画の給付費・保険料には算入しないが、対象となるサービスが本計画の見込量のどれに当たるかは両計画で揃える必要がある（素案資9）。★当方の扱い：ご回答がない場合、該当者はないものとして扱い、資9に制度の説明のみを載せる。</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Ⅱ-72</t>
+          <t>Ⅱ-72,Ⅱ-56</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>doc94</t>
+          <t>素案資9,障がい福祉計画の整合Ｋ-6</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
@@ -10442,17 +10454,179 @@
       <c r="J181" s="4" t="inlineStr"/>
       <c r="K181" s="4" t="inlineStr">
         <is>
+          <t>Ｄ</t>
+        </is>
+      </c>
+      <c r="L181" s="4" t="inlineStr">
+        <is>
+          <t>村のご回答・内部データが必要</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="4" t="n">
+        <v>181</v>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>データ</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>★成年後見制度利用支援事業は両計画で別の事業である旨の注記と、本計画側の任意事業としての助成の実績</t>
+        </is>
+      </c>
+      <c r="D182" s="4" t="inlineStr">
+        <is>
+          <t>本村の成年後見制度の利用者4人（令和8年7月）のうち、障害者手帳の所持者または障がい福祉サービスの利用者が何人かをご教示いただきたい。障がい福祉計画の側からも同じ内容を照会しているため、回答は一度で足りる。助成の件数は「家族介護者リフレッシュ事業・介護用品支給・サポーター養成講座・成年後見の各実績」、要綱の対象範囲は「成年後見制度利用支援事業の要綱の対象範囲」でそれぞれ既に照会しているため、本件では重ねない。★10/13 起票：当初は「両計画で指標名を揃えること」としていたが、障がい福祉計画の担当から、揃えるのではなく別の事業であることを注記するよう勧められた。同じ名前の事業が障害者総合支援法第77条第1項第4号の地域生活支援事業と、介護保険法第115条の45第3項第3号の地域支援事業（任意事業）の両方にあり、指標名を揃えると両計画の数を足し合わせたときに村全体の取組が実際より多く見える。この勧めに従い、素案の施策4-7と資9に別の事業である旨の注記を置いた。あわせて施策一覧の条文が「介保法115条の45第2項第2号」となっていた誤りを第3項第3号に正した（第2項第2号は権利擁護事業であって別の事業である）。本計画の指標「成年後見制度の利用者数4人」は村全体の制度の利用者数であり、助成の件数ではない。助成の件数は5-5の任意事業の実績が未受領のため置けていない。★当方の扱い：ご回答がない場合、助成の件数は5-12の空欄として掲げ、注記のみで両計画の切り分けを示す。</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ-69,Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F182" s="4" t="inlineStr">
+        <is>
+          <t>素案4-7,資9,5-5,障がい福祉計画 照会Ｋ-9</t>
+        </is>
+      </c>
+      <c r="G182" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H182" s="4" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="I182" s="4" t="inlineStr"/>
+      <c r="J182" s="4" t="inlineStr"/>
+      <c r="K182" s="4" t="inlineStr">
+        <is>
           <t>Ｃ</t>
         </is>
       </c>
-      <c r="L181" s="4" t="inlineStr">
+      <c r="L182" s="4" t="inlineStr">
+        <is>
+          <t>両計画で別の事業であることは当方が条文で整理した（doc89）。助成の実績のみ伺う</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>182</v>
+      </c>
+      <c r="B183" s="4" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C183" s="4" t="inlineStr">
+        <is>
+          <t>★福島県高齢者居住安定確保計画の改定の予定と、本村の住まいの計画の有無</t>
+        </is>
+      </c>
+      <c r="D183" s="4" t="inlineStr">
+        <is>
+          <t>★福島県高齢者居住安定確保計画の改定の予定と、本村の住まいの計画の有無をご確認いただきたい。10/15 起票：福島県高齢者居住安定確保計画（令和4年3月）を受領した。介護保険法第117条は、本計画が他の法律の規定による計画であって要介護者等の保健・医療・福祉または居住に関する事項を定めるものと調和が保たれたものであることを求めている。本計画はこれまで条文としてこれを引いておらず、住まいの計画との関係も書いていなかった（素案1-4・資9に追加した）。県計画は会津地域について、中山間地域では高齢者が集まって住む住宅が少ないこと、高齢者が除雪できず生活に支障をきたす場合があることを課題に挙げ、冬期間における除雪等の支援および集住の促進を対策としている。本村の施策2-6（除雪）・施策2-3（住まい）はこれに対応する。ただし県計画の期間は令和4年度から令和8年度までであり、本計画の期間が始まる前に満了する。次の2点をご確認いただきたい。・県計画の改定の予定（県の高齢者福祉計画・介護保険事業支援計画および住生活基本計画の改定に合わせて改定される見込み）と、会津地域の対策の変更の有無。・本村が市町村高齢者居住安定確保計画および市町村賃貸住宅供給促進計画を定めているか。定めている場合は調和の相手方になる。あわせて、県計画が挙げる住宅セーフティネット制度を活用した家賃・家賃債務保証料の補助、高齢者向け住宅への改修補助について、本村での活用の可否を住宅担当部局にご確認いただきたい。</t>
+        </is>
+      </c>
+      <c r="E183" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ-56</t>
+        </is>
+      </c>
+      <c r="F183" s="4" t="inlineStr">
+        <is>
+          <t>doc94</t>
+        </is>
+      </c>
+      <c r="G183" s="4" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H183" s="4" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="I183" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>仮置き</t>
+        </is>
+      </c>
+      <c r="K183" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
+        </is>
+      </c>
+      <c r="L183" s="4" t="inlineStr">
+        <is>
+          <t>県計画は受領済みであり、会津地域の対策は当方が読む（doc94）。改定の予定のみ伺う</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>方針</t>
+        </is>
+      </c>
+      <c r="C184" s="4" t="inlineStr">
+        <is>
+          <t>福島県の介護人材需給推計への本村の関わり方</t>
+        </is>
+      </c>
+      <c r="D184" s="4" t="inlineStr">
+        <is>
+          <t>★本村の見込量が福島県の介護人材需給推計に用いられる時期と、県から本村への照会の有無をご確認いただきたい。10/15 起票：全国介護保険担当課長会議資料（令和8年7月15日）および第9期計画に基づく介護職員の必要数（別紙5）を受領した。介護人材の需給推計は都道府県が行うものであり、都道府県は人材推計ワークシートにより管内保険者の第10期計画のサービス見込量等に基づいて令和22年度（2040年度）までの需給推計を行う。需要が供給を上回る場合には、関係団体等で構成する会議体において入職経路別（①介護福祉士養成施設等 ②他分野 ③外国人介護人材）の供給数の目標を定める。ワークシートは秋頃と令和9年1〜2月頃の2回配布され、最終報告は令和9年4月の1週目が想定されている。本計画の見込量（5-4）と中長期的な推計（資10）がその算定の基礎になるため、本村の見込量が県の推計に用いられる時期と、県から本村への照会の有無をご確認いただきたい。別紙5（第9期計画に基づく都道府県別の推計）によれば、福島県の介護職員の必要数は令和22年（2040年）度に36,851人で、現状推移を見込んだ職員数29,347人を7,504人上回る（令和4年度の実績は33,401人）。第10期の推計は県が改めて行うため、この値は参照にとどめ、素案には数値を載せず 施策4-6に県への協力を加えた。</t>
+        </is>
+      </c>
+      <c r="E184" s="4" t="inlineStr">
+        <is>
+          <t>Ⅱ-72</t>
+        </is>
+      </c>
+      <c r="F184" s="4" t="inlineStr">
+        <is>
+          <t>doc94</t>
+        </is>
+      </c>
+      <c r="G184" s="4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H184" s="4" t="inlineStr">
+        <is>
+          <t>未依頼</t>
+        </is>
+      </c>
+      <c r="I184" s="4" t="inlineStr"/>
+      <c r="J184" s="4" t="inlineStr"/>
+      <c r="K184" s="4" t="inlineStr">
+        <is>
+          <t>Ｃ</t>
+        </is>
+      </c>
+      <c r="L184" s="4" t="inlineStr">
         <is>
           <t>県の需給推計の仕組みは課長会議資料で当方が確かめた（doc94）。照会の有無のみ伺う</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L181"/>
+  <autoFilter ref="A1:L184"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/output/20_北塩原村第10期_確認事項一覧.xlsx
+++ b/output/20_北塩原村第10期_確認事項一覧.xlsx
@@ -2976,7 +2976,7 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
